--- a/Site Cash Details/Englabs Site Cash.xlsx
+++ b/Site Cash Details/Englabs Site Cash.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D66C1E51-D1BB-4F36-B950-9932A9C60D01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B9DF200-438F-42E2-98B3-A3348C1B876C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="354">
   <si>
     <t>Cr.</t>
   </si>
@@ -824,12 +824,6 @@
     <t xml:space="preserve">Printer Repair Sky5 </t>
   </si>
   <si>
-    <t>Porter From Bajaj to …..............   (C5033, 500)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Porter From Fixpro to Airport </t>
-  </si>
-  <si>
     <t>Englabs IDFC</t>
   </si>
   <si>
@@ -851,9 +845,6 @@
     <t xml:space="preserve">RO Service + Candale Charge </t>
   </si>
   <si>
-    <t>Porter From Plastipack to …................... C5108</t>
-  </si>
-  <si>
     <t xml:space="preserve">Purchase to Delhot Expo Materials </t>
   </si>
   <si>
@@ -891,9 +882,6 @@
   </si>
   <si>
     <t xml:space="preserve">Verified Paytm Merchant </t>
-  </si>
-  <si>
-    <t>UPI by Ratnesh</t>
   </si>
   <si>
     <t xml:space="preserve">Purchase to MDF SHEET 6MM &amp; PATCH 3INCH &amp; GITTI &amp; RENT </t>
@@ -998,9 +986,6 @@
     <t>Zepto / Blinkit</t>
   </si>
   <si>
-    <t>Purchesed to Scrow For Delhi Expo by Anurag</t>
-  </si>
-  <si>
     <t xml:space="preserve">Emergency </t>
   </si>
   <si>
@@ -1025,39 +1010,9 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>Purchsed to Glash for Medical Device C…..</t>
-  </si>
-  <si>
-    <t>Purchase to Extension Fuse C…..........</t>
-  </si>
-  <si>
-    <t>Porter From Fix Pro to Airport  C….....</t>
-  </si>
-  <si>
-    <t>Porter From Tribune to Englabs ITL C-….........</t>
-  </si>
-  <si>
     <t>Zepto Account Transfer for  Milk etc</t>
   </si>
   <si>
-    <t>Porter From Talekar to Pune Airport C-….....</t>
-  </si>
-  <si>
-    <t>Porter From Adoroitec to AV Machining C-…....</t>
-  </si>
-  <si>
-    <t>Porter From Enertics to Englabs by Anurag C…......</t>
-  </si>
-  <si>
-    <t>Porter From Ultra Spark to Enertics  C….......</t>
-  </si>
-  <si>
-    <t>Porter From Rohit sir PA11 to Endureair C…....</t>
-  </si>
-  <si>
-    <t>Goel Parcel by Shubham C-….......</t>
-  </si>
-  <si>
     <t xml:space="preserve">Purchased to Panchkula graphics (Stickers) For Delhi Expo by Devanshu  </t>
   </si>
   <si>
@@ -1073,10 +1028,127 @@
     <t>Purchase to TV Stand For delhi Expo</t>
   </si>
   <si>
-    <t>Porter From Sonalika Delhi to Chandigarh C-…........</t>
-  </si>
-  <si>
     <t>Blinkit MILK UPI</t>
+  </si>
+  <si>
+    <r>
+      <t>Purchase to Milk )</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Cash</t>
+    </r>
+  </si>
+  <si>
+    <t>Porter From Faridabad to  Bajaj  (C5033)</t>
+  </si>
+  <si>
+    <t>Porter From Englabs to  Goel  C4929</t>
+  </si>
+  <si>
+    <t>C4929</t>
+  </si>
+  <si>
+    <t>Aebocode Visit Shubham Expo Delhi</t>
+  </si>
+  <si>
+    <t>Porter From Fixpro to Airport Expo Delhi</t>
+  </si>
+  <si>
+    <t>Porter From Fix Pro to Airport Expo Delhi</t>
+  </si>
+  <si>
+    <t>Porter From Rohit sir PA11 to Endureair C5098</t>
+  </si>
+  <si>
+    <t>Porter From Plastipack to 3D Paradise. C5108</t>
+  </si>
+  <si>
+    <t>Porter From Talekar to Pune Airport C5092</t>
+  </si>
+  <si>
+    <t>C5098</t>
+  </si>
+  <si>
+    <t>Porter From Sonalika Delhi to Chandigarh C5131</t>
+  </si>
+  <si>
+    <t>Porter From Tribune to Englabs ITL C5131</t>
+  </si>
+  <si>
+    <t>Porter From Faridabad to AV Machining Pune. C5014</t>
+  </si>
+  <si>
+    <t>Porter From Adoroitec to AV Machining C5014</t>
+  </si>
+  <si>
+    <t>Porter From Ultra Spark to Enertics  C4851</t>
+  </si>
+  <si>
+    <t>c4851</t>
+  </si>
+  <si>
+    <t>Porter From Enertics to Englabs by Anurag C4851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purchesed to Scrow For Delhi Expo </t>
+  </si>
+  <si>
+    <t>Purchase to Extension Fuse C4465</t>
+  </si>
+  <si>
+    <t>C4465</t>
+  </si>
+  <si>
+    <t>Purchsed to Glash for Medical Device Expo Delhi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Porter From CHD Paint to Englabs </t>
+  </si>
+  <si>
+    <t>Purchase to Faviquick Gel For C4950</t>
+  </si>
+  <si>
+    <t>C4950</t>
+  </si>
+  <si>
+    <t>C5142</t>
+  </si>
+  <si>
+    <t>C5135</t>
+  </si>
+  <si>
+    <t>Porter From Cadqua  to Rohit C5135</t>
+  </si>
+  <si>
+    <t>Porter From Amit Bhri  to Enclosure C-….......</t>
+  </si>
+  <si>
+    <t>Porter From Techno to Delhi C5142</t>
+  </si>
+  <si>
+    <t>Porter From Telekar to Pune Airport C5008</t>
+  </si>
+  <si>
+    <t>PORTER From Englabs  to Hella Dera  bassi C4950</t>
+  </si>
+  <si>
+    <t>C4851</t>
+  </si>
+  <si>
+    <t>Drone Survey</t>
+  </si>
+  <si>
+    <t>Porter From Ambala to Englabs by Indrive (Drone Survey Invoice)</t>
+  </si>
+  <si>
+    <t>Porter From Industrial area phase to Englabs C4851</t>
   </si>
 </sst>
 </file>
@@ -1197,7 +1269,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1267,6 +1339,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF76E3FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1642,7 +1720,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="144">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1929,6 +2007,53 @@
     <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="13" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="168" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1971,9 +2096,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1995,58 +2117,11 @@
     <xf numFmtId="165" fontId="12" fillId="7" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="4" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="10" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2463,7 +2538,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="104">
+      <c r="A6" s="121">
         <v>46024</v>
       </c>
       <c r="B6" s="17"/>
@@ -2482,7 +2557,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="106"/>
+      <c r="A7" s="123"/>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
@@ -2499,7 +2574,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="104">
+      <c r="A8" s="121">
         <v>46025</v>
       </c>
       <c r="B8" s="17"/>
@@ -2518,7 +2593,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="106"/>
+      <c r="A9" s="123"/>
       <c r="B9" s="17"/>
       <c r="C9" s="17"/>
       <c r="D9" s="17"/>
@@ -2562,7 +2637,7 @@
       </c>
     </row>
     <row r="11" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="104">
+      <c r="A11" s="121">
         <v>46028</v>
       </c>
       <c r="B11" s="17"/>
@@ -2583,7 +2658,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="106"/>
+      <c r="A12" s="123"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
       <c r="D12" s="17"/>
@@ -2600,7 +2675,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="104">
+      <c r="A13" s="121">
         <v>46029</v>
       </c>
       <c r="B13" s="18" t="s">
@@ -2627,7 +2702,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="105"/>
+      <c r="A14" s="122"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17"/>
       <c r="D14" s="17"/>
@@ -2644,7 +2719,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="106"/>
+      <c r="A15" s="123"/>
       <c r="B15" s="17"/>
       <c r="C15" s="17"/>
       <c r="D15" s="17"/>
@@ -2661,7 +2736,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="104">
+      <c r="A16" s="121">
         <v>46030</v>
       </c>
       <c r="B16" s="17"/>
@@ -2680,7 +2755,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="105"/>
+      <c r="A17" s="122"/>
       <c r="B17" s="17"/>
       <c r="C17" s="17"/>
       <c r="D17" s="17"/>
@@ -2697,7 +2772,7 @@
       </c>
     </row>
     <row r="18" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="105"/>
+      <c r="A18" s="122"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17"/>
       <c r="D18" s="17"/>
@@ -2714,7 +2789,7 @@
       </c>
     </row>
     <row r="19" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="105"/>
+      <c r="A19" s="122"/>
       <c r="B19" s="17"/>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
@@ -2731,7 +2806,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="105"/>
+      <c r="A20" s="122"/>
       <c r="B20" s="17"/>
       <c r="C20" s="17"/>
       <c r="D20" s="17"/>
@@ -2748,7 +2823,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="105"/>
+      <c r="A21" s="122"/>
       <c r="B21" s="17"/>
       <c r="C21" s="17"/>
       <c r="D21" s="17"/>
@@ -2765,7 +2840,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="106"/>
+      <c r="A22" s="123"/>
       <c r="B22" s="17"/>
       <c r="C22" s="17"/>
       <c r="D22" s="17"/>
@@ -2782,7 +2857,7 @@
       </c>
     </row>
     <row r="23" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="104">
+      <c r="A23" s="121">
         <v>46031</v>
       </c>
       <c r="B23" s="17"/>
@@ -2803,7 +2878,7 @@
       </c>
     </row>
     <row r="24" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="105"/>
+      <c r="A24" s="122"/>
       <c r="B24" s="18" t="s">
         <v>59</v>
       </c>
@@ -2828,7 +2903,7 @@
       </c>
     </row>
     <row r="25" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="106"/>
+      <c r="A25" s="123"/>
       <c r="B25" s="17"/>
       <c r="C25" s="17"/>
       <c r="D25" s="17"/>
@@ -2845,7 +2920,7 @@
       </c>
     </row>
     <row r="26" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="104">
+      <c r="A26" s="121">
         <v>46032</v>
       </c>
       <c r="B26" s="17"/>
@@ -2864,7 +2939,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="106"/>
+      <c r="A27" s="123"/>
       <c r="B27" s="17"/>
       <c r="C27" s="17"/>
       <c r="D27" s="17"/>
@@ -2900,7 +2975,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="104">
+      <c r="A29" s="121">
         <v>46035</v>
       </c>
       <c r="B29" s="17"/>
@@ -2919,7 +2994,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="105"/>
+      <c r="A30" s="122"/>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
@@ -2936,7 +3011,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="105"/>
+      <c r="A31" s="122"/>
       <c r="B31" s="18" t="s">
         <v>59</v>
       </c>
@@ -2961,7 +3036,7 @@
       </c>
     </row>
     <row r="32" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="105"/>
+      <c r="A32" s="122"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
@@ -2978,7 +3053,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="105"/>
+      <c r="A33" s="122"/>
       <c r="B33" s="17"/>
       <c r="C33" s="17"/>
       <c r="D33" s="17"/>
@@ -2995,7 +3070,7 @@
       </c>
     </row>
     <row r="34" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="105"/>
+      <c r="A34" s="122"/>
       <c r="B34" s="17"/>
       <c r="C34" s="17"/>
       <c r="D34" s="17"/>
@@ -3012,7 +3087,7 @@
       </c>
     </row>
     <row r="35" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="105"/>
+      <c r="A35" s="122"/>
       <c r="B35" s="17"/>
       <c r="C35" s="17"/>
       <c r="D35" s="17"/>
@@ -3029,7 +3104,7 @@
       </c>
     </row>
     <row r="36" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="105"/>
+      <c r="A36" s="122"/>
       <c r="B36" s="17"/>
       <c r="C36" s="17"/>
       <c r="D36" s="17"/>
@@ -3046,7 +3121,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="105"/>
+      <c r="A37" s="122"/>
       <c r="B37" s="17"/>
       <c r="C37" s="17"/>
       <c r="D37" s="17"/>
@@ -3063,7 +3138,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="105"/>
+      <c r="A38" s="122"/>
       <c r="B38" s="17"/>
       <c r="C38" s="17"/>
       <c r="D38" s="17"/>
@@ -3080,7 +3155,7 @@
       </c>
     </row>
     <row r="39" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="104">
+      <c r="A39" s="121">
         <v>46036</v>
       </c>
       <c r="B39" s="17"/>
@@ -3099,7 +3174,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" s="105"/>
+      <c r="A40" s="122"/>
       <c r="B40" s="25"/>
       <c r="C40" s="11"/>
       <c r="D40" s="11"/>
@@ -3116,7 +3191,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" s="105"/>
+      <c r="A41" s="122"/>
       <c r="B41" s="18"/>
       <c r="C41" s="17"/>
       <c r="D41" s="17"/>
@@ -3135,7 +3210,7 @@
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A42" s="105"/>
+      <c r="A42" s="122"/>
       <c r="B42" s="25"/>
       <c r="C42" s="11"/>
       <c r="D42" s="11"/>
@@ -3152,7 +3227,7 @@
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" s="105"/>
+      <c r="A43" s="122"/>
       <c r="B43" s="25"/>
       <c r="C43" s="11"/>
       <c r="D43" s="11"/>
@@ -3169,7 +3244,7 @@
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A44" s="105"/>
+      <c r="A44" s="122"/>
       <c r="B44" s="25"/>
       <c r="C44" s="11"/>
       <c r="D44" s="11"/>
@@ -3188,7 +3263,7 @@
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A45" s="105"/>
+      <c r="A45" s="122"/>
       <c r="B45" s="18"/>
       <c r="C45" s="18"/>
       <c r="D45" s="18"/>
@@ -3205,7 +3280,7 @@
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A46" s="105"/>
+      <c r="A46" s="122"/>
       <c r="B46" s="17"/>
       <c r="C46" s="11"/>
       <c r="D46" s="11"/>
@@ -3224,7 +3299,7 @@
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A47" s="106"/>
+      <c r="A47" s="123"/>
       <c r="B47" s="17"/>
       <c r="C47" s="11"/>
       <c r="D47" s="11"/>
@@ -3243,7 +3318,7 @@
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A48" s="104">
+      <c r="A48" s="121">
         <v>46037</v>
       </c>
       <c r="B48" s="18"/>
@@ -3264,7 +3339,7 @@
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A49" s="105"/>
+      <c r="A49" s="122"/>
       <c r="B49" s="18"/>
       <c r="C49" s="18"/>
       <c r="D49" s="18"/>
@@ -3283,7 +3358,7 @@
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A50" s="105"/>
+      <c r="A50" s="122"/>
       <c r="B50" s="17"/>
       <c r="C50" s="18"/>
       <c r="D50" s="18"/>
@@ -3302,7 +3377,7 @@
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A51" s="106"/>
+      <c r="A51" s="123"/>
       <c r="B51" s="18"/>
       <c r="C51" s="18"/>
       <c r="D51" s="18"/>
@@ -3319,7 +3394,7 @@
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A52" s="104">
+      <c r="A52" s="121">
         <v>46038</v>
       </c>
       <c r="B52" s="18" t="s">
@@ -3346,7 +3421,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A53" s="105"/>
+      <c r="A53" s="122"/>
       <c r="B53" s="18"/>
       <c r="C53" s="18"/>
       <c r="D53" s="18"/>
@@ -3363,7 +3438,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A54" s="106"/>
+      <c r="A54" s="123"/>
       <c r="B54" s="18"/>
       <c r="C54" s="18"/>
       <c r="D54" s="18"/>
@@ -3401,7 +3476,7 @@
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A56" s="104">
+      <c r="A56" s="121">
         <v>46040</v>
       </c>
       <c r="B56" s="18"/>
@@ -3420,7 +3495,7 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A57" s="106"/>
+      <c r="A57" s="123"/>
       <c r="B57" s="18"/>
       <c r="C57" s="18"/>
       <c r="D57" s="18"/>
@@ -3456,7 +3531,7 @@
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A59" s="104">
+      <c r="A59" s="121">
         <v>46042</v>
       </c>
       <c r="B59" s="18"/>
@@ -3477,7 +3552,7 @@
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A60" s="105"/>
+      <c r="A60" s="122"/>
       <c r="B60" s="18"/>
       <c r="C60" s="18"/>
       <c r="D60" s="18"/>
@@ -3496,7 +3571,7 @@
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A61" s="105"/>
+      <c r="A61" s="122"/>
       <c r="B61" s="10"/>
       <c r="C61" s="10"/>
       <c r="D61" s="10"/>
@@ -3515,7 +3590,7 @@
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A62" s="105"/>
+      <c r="A62" s="122"/>
       <c r="B62" s="10"/>
       <c r="C62" s="10"/>
       <c r="D62" s="10"/>
@@ -3534,7 +3609,7 @@
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A63" s="105"/>
+      <c r="A63" s="122"/>
       <c r="B63" s="10"/>
       <c r="C63" s="10"/>
       <c r="D63" s="10"/>
@@ -3551,7 +3626,7 @@
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A64" s="105"/>
+      <c r="A64" s="122"/>
       <c r="B64" s="10" t="s">
         <v>72</v>
       </c>
@@ -3576,7 +3651,7 @@
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A65" s="105"/>
+      <c r="A65" s="122"/>
       <c r="B65" s="10"/>
       <c r="C65" s="10"/>
       <c r="D65" s="10"/>
@@ -3593,7 +3668,7 @@
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A66" s="106"/>
+      <c r="A66" s="123"/>
       <c r="B66" s="18"/>
       <c r="C66" s="18"/>
       <c r="D66" s="18"/>
@@ -3612,7 +3687,7 @@
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A67" s="104">
+      <c r="A67" s="121">
         <v>46043</v>
       </c>
       <c r="B67" s="18" t="s">
@@ -3639,7 +3714,7 @@
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A68" s="105"/>
+      <c r="A68" s="122"/>
       <c r="B68" s="18"/>
       <c r="C68" s="18"/>
       <c r="D68" s="18"/>
@@ -3658,7 +3733,7 @@
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A69" s="105"/>
+      <c r="A69" s="122"/>
       <c r="B69" s="18"/>
       <c r="C69" s="18"/>
       <c r="D69" s="18"/>
@@ -3675,7 +3750,7 @@
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A70" s="105"/>
+      <c r="A70" s="122"/>
       <c r="B70" s="18"/>
       <c r="C70" s="18"/>
       <c r="D70" s="18"/>
@@ -3692,7 +3767,7 @@
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A71" s="106"/>
+      <c r="A71" s="123"/>
       <c r="B71" s="18"/>
       <c r="C71" s="18"/>
       <c r="D71" s="18"/>
@@ -3709,7 +3784,7 @@
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A72" s="104">
+      <c r="A72" s="121">
         <v>46044</v>
       </c>
       <c r="B72" s="18"/>
@@ -3728,7 +3803,7 @@
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A73" s="105"/>
+      <c r="A73" s="122"/>
       <c r="B73" s="18"/>
       <c r="C73" s="18"/>
       <c r="D73" s="18"/>
@@ -3745,7 +3820,7 @@
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A74" s="105"/>
+      <c r="A74" s="122"/>
       <c r="B74" s="18"/>
       <c r="C74" s="18"/>
       <c r="D74" s="18"/>
@@ -3762,7 +3837,7 @@
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A75" s="105"/>
+      <c r="A75" s="122"/>
       <c r="B75" s="18"/>
       <c r="C75" s="18"/>
       <c r="D75" s="18"/>
@@ -3779,7 +3854,7 @@
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A76" s="106"/>
+      <c r="A76" s="123"/>
       <c r="B76" s="18"/>
       <c r="C76" s="18"/>
       <c r="D76" s="18"/>
@@ -3796,7 +3871,7 @@
       </c>
     </row>
     <row r="77" spans="1:9" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A77" s="104">
+      <c r="A77" s="121">
         <v>46045</v>
       </c>
       <c r="B77" s="18"/>
@@ -3813,12 +3888,12 @@
         <f t="shared" si="0"/>
         <v>2439</v>
       </c>
-      <c r="I77" s="107" t="s">
+      <c r="I77" s="124" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A78" s="105"/>
+      <c r="A78" s="122"/>
       <c r="B78" s="18"/>
       <c r="C78" s="18"/>
       <c r="D78" s="18"/>
@@ -3835,10 +3910,10 @@
         <f t="shared" si="0"/>
         <v>2314</v>
       </c>
-      <c r="I78" s="107"/>
+      <c r="I78" s="124"/>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A79" s="105"/>
+      <c r="A79" s="122"/>
       <c r="B79" s="18"/>
       <c r="C79" s="18"/>
       <c r="D79" s="18"/>
@@ -3857,7 +3932,7 @@
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A80" s="106"/>
+      <c r="A80" s="123"/>
       <c r="B80" s="18"/>
       <c r="C80" s="18"/>
       <c r="D80" s="18"/>
@@ -3874,7 +3949,7 @@
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A81" s="104">
+      <c r="A81" s="121">
         <v>46046</v>
       </c>
       <c r="B81" s="18" t="s">
@@ -3901,7 +3976,7 @@
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A82" s="105"/>
+      <c r="A82" s="122"/>
       <c r="B82" s="18"/>
       <c r="C82" s="18"/>
       <c r="D82" s="18"/>
@@ -3918,7 +3993,7 @@
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A83" s="105"/>
+      <c r="A83" s="122"/>
       <c r="B83" s="18"/>
       <c r="C83" s="18"/>
       <c r="D83" s="18"/>
@@ -3935,7 +4010,7 @@
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A84" s="106"/>
+      <c r="A84" s="123"/>
       <c r="B84" s="18"/>
       <c r="C84" s="18"/>
       <c r="D84" s="18"/>
@@ -3952,7 +4027,7 @@
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A85" s="104">
+      <c r="A85" s="121">
         <v>46049</v>
       </c>
       <c r="B85" s="18"/>
@@ -3971,7 +4046,7 @@
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A86" s="105"/>
+      <c r="A86" s="122"/>
       <c r="B86" s="18"/>
       <c r="C86" s="18"/>
       <c r="D86" s="18"/>
@@ -3988,7 +4063,7 @@
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A87" s="106"/>
+      <c r="A87" s="123"/>
       <c r="B87" s="18"/>
       <c r="C87" s="18"/>
       <c r="D87" s="18"/>
@@ -4005,7 +4080,7 @@
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A88" s="104">
+      <c r="A88" s="121">
         <v>46050</v>
       </c>
       <c r="B88" s="18" t="s">
@@ -4032,7 +4107,7 @@
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A89" s="105"/>
+      <c r="A89" s="122"/>
       <c r="B89" s="18"/>
       <c r="C89" s="18"/>
       <c r="D89" s="18"/>
@@ -4049,7 +4124,7 @@
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A90" s="105"/>
+      <c r="A90" s="122"/>
       <c r="B90" s="18"/>
       <c r="C90" s="18"/>
       <c r="D90" s="18"/>
@@ -4066,7 +4141,7 @@
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A91" s="105"/>
+      <c r="A91" s="122"/>
       <c r="B91" s="18"/>
       <c r="C91" s="18"/>
       <c r="D91" s="18"/>
@@ -4085,7 +4160,7 @@
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A92" s="106"/>
+      <c r="A92" s="123"/>
       <c r="B92" s="18"/>
       <c r="C92" s="18"/>
       <c r="D92" s="18"/>
@@ -4102,7 +4177,7 @@
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A93" s="104">
+      <c r="A93" s="121">
         <v>46051</v>
       </c>
       <c r="B93" s="18"/>
@@ -4121,7 +4196,7 @@
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A94" s="105"/>
+      <c r="A94" s="122"/>
       <c r="B94" s="18"/>
       <c r="C94" s="18"/>
       <c r="D94" s="18"/>
@@ -4138,7 +4213,7 @@
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A95" s="106"/>
+      <c r="A95" s="123"/>
       <c r="B95" s="18"/>
       <c r="C95" s="18"/>
       <c r="D95" s="18"/>
@@ -4437,16 +4512,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="108" t="s">
+      <c r="A1" s="125" t="s">
         <v>177</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="109"/>
-      <c r="G1" s="109"/>
-      <c r="H1" s="110"/>
+      <c r="B1" s="126"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="126"/>
+      <c r="E1" s="126"/>
+      <c r="F1" s="126"/>
+      <c r="G1" s="126"/>
+      <c r="H1" s="127"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="69"/>
@@ -4531,7 +4606,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="111">
+      <c r="A6" s="128">
         <v>46055</v>
       </c>
       <c r="B6" s="17"/>
@@ -4552,7 +4627,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="111"/>
+      <c r="A7" s="128"/>
       <c r="B7" s="17"/>
       <c r="C7" s="76"/>
       <c r="D7" s="17"/>
@@ -4569,7 +4644,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="111"/>
+      <c r="A8" s="128"/>
       <c r="B8" s="17"/>
       <c r="C8" s="76"/>
       <c r="D8" s="17"/>
@@ -4586,7 +4661,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="111"/>
+      <c r="A9" s="128"/>
       <c r="B9" s="17"/>
       <c r="C9" s="76"/>
       <c r="D9" s="17"/>
@@ -4603,7 +4678,7 @@
       </c>
     </row>
     <row r="10" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="111">
+      <c r="A10" s="128">
         <v>46056</v>
       </c>
       <c r="B10" s="18"/>
@@ -4622,7 +4697,7 @@
       </c>
     </row>
     <row r="11" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="111"/>
+      <c r="A11" s="128"/>
       <c r="B11" s="17"/>
       <c r="C11" s="76"/>
       <c r="D11" s="17"/>
@@ -4639,7 +4714,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="111"/>
+      <c r="A12" s="128"/>
       <c r="B12" s="17"/>
       <c r="C12" s="76"/>
       <c r="D12" s="17"/>
@@ -4656,7 +4731,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="111"/>
+      <c r="A13" s="128"/>
       <c r="B13" s="18"/>
       <c r="C13" s="76"/>
       <c r="D13" s="17"/>
@@ -4673,7 +4748,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="111"/>
+      <c r="A14" s="128"/>
       <c r="B14" s="17"/>
       <c r="C14" s="76"/>
       <c r="D14" s="17"/>
@@ -4690,7 +4765,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="111">
+      <c r="A15" s="128">
         <v>46057</v>
       </c>
       <c r="B15" s="17"/>
@@ -4709,7 +4784,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="111"/>
+      <c r="A16" s="128"/>
       <c r="B16" s="17"/>
       <c r="C16" s="76"/>
       <c r="D16" s="17"/>
@@ -4726,7 +4801,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="111">
+      <c r="A17" s="128">
         <v>46058</v>
       </c>
       <c r="B17" s="17"/>
@@ -4745,7 +4820,7 @@
       </c>
     </row>
     <row r="18" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="111"/>
+      <c r="A18" s="128"/>
       <c r="B18" s="17"/>
       <c r="C18" s="76"/>
       <c r="D18" s="17"/>
@@ -4762,7 +4837,7 @@
       </c>
     </row>
     <row r="19" spans="1:8" s="15" customFormat="1" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A19" s="111">
+      <c r="A19" s="128">
         <v>46060</v>
       </c>
       <c r="B19" s="17" t="s">
@@ -4789,7 +4864,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" s="15" customFormat="1" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A20" s="111"/>
+      <c r="A20" s="128"/>
       <c r="B20" s="17" t="s">
         <v>121</v>
       </c>
@@ -4814,7 +4889,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="111"/>
+      <c r="A21" s="128"/>
       <c r="B21" s="17"/>
       <c r="C21" s="76"/>
       <c r="D21" s="17"/>
@@ -4831,7 +4906,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="111"/>
+      <c r="A22" s="128"/>
       <c r="B22" s="17"/>
       <c r="C22" s="76"/>
       <c r="D22" s="17"/>
@@ -4848,7 +4923,7 @@
       </c>
     </row>
     <row r="23" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="111"/>
+      <c r="A23" s="128"/>
       <c r="B23" s="17"/>
       <c r="C23" s="76"/>
       <c r="D23" s="17"/>
@@ -4865,7 +4940,7 @@
       </c>
     </row>
     <row r="24" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="111"/>
+      <c r="A24" s="128"/>
       <c r="B24" s="18"/>
       <c r="C24" s="76"/>
       <c r="D24" s="17"/>
@@ -4882,7 +4957,7 @@
       </c>
     </row>
     <row r="25" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="111"/>
+      <c r="A25" s="128"/>
       <c r="B25" s="17"/>
       <c r="C25" s="76"/>
       <c r="D25" s="17"/>
@@ -4899,7 +4974,7 @@
       </c>
     </row>
     <row r="26" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="111"/>
+      <c r="A26" s="128"/>
       <c r="B26" s="17"/>
       <c r="C26" s="76"/>
       <c r="D26" s="17"/>
@@ -4916,7 +4991,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="111">
+      <c r="A27" s="128">
         <v>46062</v>
       </c>
       <c r="B27" s="17"/>
@@ -4935,7 +5010,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="111"/>
+      <c r="A28" s="128"/>
       <c r="B28" s="17"/>
       <c r="C28" s="76"/>
       <c r="D28" s="17"/>
@@ -4952,7 +5027,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="111"/>
+      <c r="A29" s="128"/>
       <c r="B29" s="17"/>
       <c r="C29" s="76"/>
       <c r="D29" s="17"/>
@@ -4969,7 +5044,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="111">
+      <c r="A30" s="128">
         <v>46063</v>
       </c>
       <c r="B30" s="18"/>
@@ -4988,7 +5063,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="111"/>
+      <c r="A31" s="128"/>
       <c r="B31" s="17"/>
       <c r="C31" s="76"/>
       <c r="D31" s="17"/>
@@ -5005,7 +5080,7 @@
       </c>
     </row>
     <row r="32" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="111"/>
+      <c r="A32" s="128"/>
       <c r="B32" s="17"/>
       <c r="C32" s="76"/>
       <c r="D32" s="17"/>
@@ -5022,7 +5097,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="111"/>
+      <c r="A33" s="128"/>
       <c r="B33" s="17"/>
       <c r="C33" s="76"/>
       <c r="D33" s="17"/>
@@ -5039,7 +5114,7 @@
       </c>
     </row>
     <row r="34" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="111">
+      <c r="A34" s="128">
         <v>46064</v>
       </c>
       <c r="B34" s="17"/>
@@ -5058,7 +5133,7 @@
       </c>
     </row>
     <row r="35" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="111"/>
+      <c r="A35" s="128"/>
       <c r="B35" s="17"/>
       <c r="C35" s="76"/>
       <c r="D35" s="17"/>
@@ -5075,7 +5150,7 @@
       </c>
     </row>
     <row r="36" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="111"/>
+      <c r="A36" s="128"/>
       <c r="B36" s="17"/>
       <c r="C36" s="76"/>
       <c r="D36" s="17"/>
@@ -5092,7 +5167,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="111"/>
+      <c r="A37" s="128"/>
       <c r="B37" s="17"/>
       <c r="C37" s="76"/>
       <c r="D37" s="17"/>
@@ -5109,7 +5184,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="111">
+      <c r="A38" s="128">
         <v>46065</v>
       </c>
       <c r="B38" s="17"/>
@@ -5128,7 +5203,7 @@
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A39" s="111"/>
+      <c r="A39" s="128"/>
       <c r="B39" s="25"/>
       <c r="C39" s="77"/>
       <c r="D39" s="11"/>
@@ -5145,7 +5220,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" s="111"/>
+      <c r="A40" s="128"/>
       <c r="B40" s="18"/>
       <c r="C40" s="76"/>
       <c r="D40" s="17"/>
@@ -5181,7 +5256,7 @@
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A42" s="111">
+      <c r="A42" s="128">
         <v>46067</v>
       </c>
       <c r="B42" s="25"/>
@@ -5200,7 +5275,7 @@
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" s="111"/>
+      <c r="A43" s="128"/>
       <c r="B43" s="25"/>
       <c r="C43" s="77"/>
       <c r="D43" s="11"/>
@@ -5217,7 +5292,7 @@
       </c>
     </row>
     <row r="44" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A44" s="111"/>
+      <c r="A44" s="128"/>
       <c r="B44" s="17" t="s">
         <v>120</v>
       </c>
@@ -5263,7 +5338,7 @@
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A46" s="111">
+      <c r="A46" s="128">
         <v>46071</v>
       </c>
       <c r="B46" s="17"/>
@@ -5282,7 +5357,7 @@
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A47" s="111"/>
+      <c r="A47" s="128"/>
       <c r="B47" s="17"/>
       <c r="C47" s="77"/>
       <c r="D47" s="11"/>
@@ -5299,7 +5374,7 @@
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A48" s="111">
+      <c r="A48" s="128">
         <v>46072</v>
       </c>
       <c r="B48" s="18"/>
@@ -5318,7 +5393,7 @@
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A49" s="111"/>
+      <c r="A49" s="128"/>
       <c r="B49" s="18"/>
       <c r="C49" s="76"/>
       <c r="D49" s="18"/>
@@ -5335,7 +5410,7 @@
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A50" s="111"/>
+      <c r="A50" s="128"/>
       <c r="B50" s="17"/>
       <c r="C50" s="76"/>
       <c r="D50" s="18"/>
@@ -5352,7 +5427,7 @@
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A51" s="111"/>
+      <c r="A51" s="128"/>
       <c r="B51" s="18"/>
       <c r="C51" s="76"/>
       <c r="D51" s="18"/>
@@ -5369,7 +5444,7 @@
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A52" s="111">
+      <c r="A52" s="128">
         <v>46073</v>
       </c>
       <c r="B52" s="18"/>
@@ -5388,7 +5463,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A53" s="111"/>
+      <c r="A53" s="128"/>
       <c r="B53" s="18"/>
       <c r="C53" s="76"/>
       <c r="D53" s="18"/>
@@ -5405,7 +5480,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A54" s="111"/>
+      <c r="A54" s="128"/>
       <c r="B54" s="18"/>
       <c r="C54" s="76"/>
       <c r="D54" s="18"/>
@@ -5422,7 +5497,7 @@
       </c>
     </row>
     <row r="55" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A55" s="111">
+      <c r="A55" s="128">
         <v>46076</v>
       </c>
       <c r="B55" s="17" t="s">
@@ -5449,7 +5524,7 @@
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A56" s="111"/>
+      <c r="A56" s="128"/>
       <c r="B56" s="18"/>
       <c r="C56" s="76"/>
       <c r="D56" s="18"/>
@@ -5466,7 +5541,7 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A57" s="111"/>
+      <c r="A57" s="128"/>
       <c r="B57" s="18"/>
       <c r="C57" s="76"/>
       <c r="D57" s="18"/>
@@ -5483,7 +5558,7 @@
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A58" s="111"/>
+      <c r="A58" s="128"/>
       <c r="B58" s="18"/>
       <c r="C58" s="76"/>
       <c r="D58" s="18"/>
@@ -5500,7 +5575,7 @@
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A59" s="111">
+      <c r="A59" s="128">
         <v>46077</v>
       </c>
       <c r="B59" s="18"/>
@@ -5519,7 +5594,7 @@
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A60" s="111"/>
+      <c r="A60" s="128"/>
       <c r="B60" s="18"/>
       <c r="C60" s="76"/>
       <c r="D60" s="18"/>
@@ -5536,7 +5611,7 @@
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A61" s="111"/>
+      <c r="A61" s="128"/>
       <c r="B61" s="10"/>
       <c r="C61" s="78"/>
       <c r="D61" s="10"/>
@@ -5553,7 +5628,7 @@
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A62" s="111"/>
+      <c r="A62" s="128"/>
       <c r="B62" s="10"/>
       <c r="C62" s="78"/>
       <c r="D62" s="10"/>
@@ -5570,7 +5645,7 @@
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A63" s="111"/>
+      <c r="A63" s="128"/>
       <c r="B63" s="10"/>
       <c r="C63" s="78"/>
       <c r="D63" s="10"/>
@@ -5587,7 +5662,7 @@
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A64" s="111">
+      <c r="A64" s="128">
         <v>46078</v>
       </c>
       <c r="B64" s="10"/>
@@ -5606,7 +5681,7 @@
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A65" s="111"/>
+      <c r="A65" s="128"/>
       <c r="B65" s="10"/>
       <c r="C65" s="78"/>
       <c r="D65" s="10"/>
@@ -5623,7 +5698,7 @@
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A66" s="111">
+      <c r="A66" s="128">
         <v>46079</v>
       </c>
       <c r="B66" s="18"/>
@@ -5642,7 +5717,7 @@
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A67" s="111"/>
+      <c r="A67" s="128"/>
       <c r="B67" s="18"/>
       <c r="C67" s="76"/>
       <c r="D67" s="18"/>
@@ -5659,7 +5734,7 @@
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A68" s="111"/>
+      <c r="A68" s="128"/>
       <c r="B68" s="18"/>
       <c r="C68" s="76"/>
       <c r="D68" s="18"/>
@@ -5676,7 +5751,7 @@
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A69" s="111"/>
+      <c r="A69" s="128"/>
       <c r="B69" s="18"/>
       <c r="C69" s="76"/>
       <c r="D69" s="18"/>
@@ -5693,7 +5768,7 @@
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A70" s="111">
+      <c r="A70" s="128">
         <v>46080</v>
       </c>
       <c r="B70" s="18"/>
@@ -5712,7 +5787,7 @@
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A71" s="111"/>
+      <c r="A71" s="128"/>
       <c r="B71" s="18"/>
       <c r="C71" s="76"/>
       <c r="D71" s="18"/>
@@ -5729,7 +5804,7 @@
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A72" s="111"/>
+      <c r="A72" s="128"/>
       <c r="B72" s="18"/>
       <c r="C72" s="76"/>
       <c r="D72" s="18"/>
@@ -5746,7 +5821,7 @@
       </c>
     </row>
     <row r="73" spans="1:9" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A73" s="111">
+      <c r="A73" s="128">
         <v>46081</v>
       </c>
       <c r="B73" s="17" t="s">
@@ -5773,7 +5848,7 @@
       </c>
     </row>
     <row r="74" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="111"/>
+      <c r="A74" s="128"/>
       <c r="B74" s="18"/>
       <c r="C74" s="76"/>
       <c r="D74" s="18"/>
@@ -5792,7 +5867,7 @@
       </c>
     </row>
     <row r="75" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="111"/>
+      <c r="A75" s="128"/>
       <c r="B75" s="18"/>
       <c r="C75" s="76"/>
       <c r="D75" s="18"/>
@@ -5809,7 +5884,7 @@
       </c>
     </row>
     <row r="76" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="111"/>
+      <c r="A76" s="128"/>
       <c r="B76" s="18"/>
       <c r="C76" s="76"/>
       <c r="D76" s="18"/>
@@ -5826,7 +5901,7 @@
       </c>
     </row>
     <row r="77" spans="1:9" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A77" s="111"/>
+      <c r="A77" s="128"/>
       <c r="B77" s="18"/>
       <c r="C77" s="76"/>
       <c r="D77" s="18"/>
@@ -5841,12 +5916,12 @@
         <f t="shared" si="1"/>
         <v>2127.9400000000005</v>
       </c>
-      <c r="I77" s="107" t="s">
+      <c r="I77" s="124" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="112"/>
+      <c r="A78" s="129"/>
       <c r="B78" s="51"/>
       <c r="C78" s="79"/>
       <c r="D78" s="51"/>
@@ -5861,7 +5936,7 @@
         <f t="shared" si="1"/>
         <v>1427.9400000000005</v>
       </c>
-      <c r="I78" s="107"/>
+      <c r="I78" s="124"/>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="58"/>
@@ -6346,16 +6421,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="130" t="s">
         <v>178</v>
       </c>
-      <c r="B1" s="114"/>
-      <c r="C1" s="114"/>
-      <c r="D1" s="114"/>
-      <c r="E1" s="114"/>
-      <c r="F1" s="114"/>
-      <c r="G1" s="114"/>
-      <c r="H1" s="115"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="132"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="69"/>
@@ -6459,7 +6534,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="104">
+      <c r="A7" s="121">
         <v>46084</v>
       </c>
       <c r="B7" s="17"/>
@@ -6478,7 +6553,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="105"/>
+      <c r="A8" s="122"/>
       <c r="B8" s="17"/>
       <c r="C8" s="76"/>
       <c r="D8" s="17"/>
@@ -6495,7 +6570,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" s="15" customFormat="1" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A9" s="105"/>
+      <c r="A9" s="122"/>
       <c r="B9" s="17" t="s">
         <v>121</v>
       </c>
@@ -6520,7 +6595,7 @@
       </c>
     </row>
     <row r="10" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="106"/>
+      <c r="A10" s="123"/>
       <c r="B10" s="18"/>
       <c r="C10" s="76"/>
       <c r="D10" s="17"/>
@@ -6594,7 +6669,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" s="15" customFormat="1" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A14" s="104">
+      <c r="A14" s="121">
         <v>46088</v>
       </c>
       <c r="B14" s="17" t="s">
@@ -6621,7 +6696,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="105"/>
+      <c r="A15" s="122"/>
       <c r="B15" s="17"/>
       <c r="C15" s="76"/>
       <c r="D15" s="17"/>
@@ -6638,7 +6713,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="105"/>
+      <c r="A16" s="122"/>
       <c r="B16" s="17"/>
       <c r="C16" s="76"/>
       <c r="D16" s="17"/>
@@ -6655,7 +6730,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="105"/>
+      <c r="A17" s="122"/>
       <c r="B17" s="17"/>
       <c r="C17" s="76"/>
       <c r="D17" s="17"/>
@@ -6672,7 +6747,7 @@
       </c>
     </row>
     <row r="18" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="106"/>
+      <c r="A18" s="123"/>
       <c r="B18" s="17"/>
       <c r="C18" s="76"/>
       <c r="D18" s="17"/>
@@ -6708,7 +6783,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="104">
+      <c r="A20" s="121">
         <v>46092</v>
       </c>
       <c r="B20" s="17"/>
@@ -6727,7 +6802,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="105"/>
+      <c r="A21" s="122"/>
       <c r="B21" s="17"/>
       <c r="C21" s="76"/>
       <c r="D21" s="17"/>
@@ -6744,7 +6819,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="105"/>
+      <c r="A22" s="122"/>
       <c r="B22" s="17"/>
       <c r="C22" s="76"/>
       <c r="D22" s="17"/>
@@ -6761,7 +6836,7 @@
       </c>
     </row>
     <row r="23" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="106"/>
+      <c r="A23" s="123"/>
       <c r="B23" s="17"/>
       <c r="C23" s="76"/>
       <c r="D23" s="17"/>
@@ -6805,7 +6880,7 @@
       </c>
     </row>
     <row r="25" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="104">
+      <c r="A25" s="121">
         <v>46094</v>
       </c>
       <c r="B25" s="17"/>
@@ -6824,7 +6899,7 @@
       </c>
     </row>
     <row r="26" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="105"/>
+      <c r="A26" s="122"/>
       <c r="B26" s="17"/>
       <c r="C26" s="76"/>
       <c r="D26" s="17"/>
@@ -6841,7 +6916,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="105"/>
+      <c r="A27" s="122"/>
       <c r="B27" s="17"/>
       <c r="C27" s="76"/>
       <c r="D27" s="17"/>
@@ -6858,7 +6933,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="105"/>
+      <c r="A28" s="122"/>
       <c r="B28" s="17"/>
       <c r="C28" s="76"/>
       <c r="D28" s="17"/>
@@ -6875,7 +6950,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="105"/>
+      <c r="A29" s="122"/>
       <c r="B29" s="17"/>
       <c r="C29" s="76"/>
       <c r="D29" s="17"/>
@@ -6892,7 +6967,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="105"/>
+      <c r="A30" s="122"/>
       <c r="B30" s="18"/>
       <c r="C30" s="76"/>
       <c r="D30" s="17"/>
@@ -6909,7 +6984,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="105"/>
+      <c r="A31" s="122"/>
       <c r="B31" s="17"/>
       <c r="C31" s="76"/>
       <c r="D31" s="17"/>
@@ -6926,7 +7001,7 @@
       </c>
     </row>
     <row r="32" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="105"/>
+      <c r="A32" s="122"/>
       <c r="B32" s="17"/>
       <c r="C32" s="76"/>
       <c r="D32" s="17"/>
@@ -6943,7 +7018,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="105"/>
+      <c r="A33" s="122"/>
       <c r="B33" s="17"/>
       <c r="C33" s="76"/>
       <c r="D33" s="17"/>
@@ -6960,7 +7035,7 @@
       </c>
     </row>
     <row r="34" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="106"/>
+      <c r="A34" s="123"/>
       <c r="B34" s="17"/>
       <c r="C34" s="76"/>
       <c r="D34" s="17"/>
@@ -6977,7 +7052,7 @@
       </c>
     </row>
     <row r="35" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="104">
+      <c r="A35" s="121">
         <v>46095</v>
       </c>
       <c r="B35" s="17"/>
@@ -6996,7 +7071,7 @@
       </c>
     </row>
     <row r="36" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="105"/>
+      <c r="A36" s="122"/>
       <c r="B36" s="17"/>
       <c r="C36" s="76"/>
       <c r="D36" s="17"/>
@@ -7013,7 +7088,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="105"/>
+      <c r="A37" s="122"/>
       <c r="B37" s="17"/>
       <c r="C37" s="76"/>
       <c r="D37" s="17"/>
@@ -7030,7 +7105,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="106"/>
+      <c r="A38" s="123"/>
       <c r="B38" s="17"/>
       <c r="C38" s="76"/>
       <c r="D38" s="17"/>
@@ -7047,7 +7122,7 @@
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A39" s="104">
+      <c r="A39" s="121">
         <v>46097</v>
       </c>
       <c r="B39" s="25"/>
@@ -7066,7 +7141,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" s="105"/>
+      <c r="A40" s="122"/>
       <c r="B40" s="18"/>
       <c r="C40" s="76"/>
       <c r="D40" s="17"/>
@@ -7083,7 +7158,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" s="105"/>
+      <c r="A41" s="122"/>
       <c r="B41" s="25"/>
       <c r="C41" s="77"/>
       <c r="D41" s="11"/>
@@ -7100,7 +7175,7 @@
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A42" s="105"/>
+      <c r="A42" s="122"/>
       <c r="B42" s="25"/>
       <c r="C42" s="77"/>
       <c r="D42" s="11"/>
@@ -7117,7 +7192,7 @@
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" s="105"/>
+      <c r="A43" s="122"/>
       <c r="B43" s="25"/>
       <c r="C43" s="77"/>
       <c r="D43" s="11"/>
@@ -7134,7 +7209,7 @@
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A44" s="105"/>
+      <c r="A44" s="122"/>
       <c r="B44" s="17"/>
       <c r="C44" s="76"/>
       <c r="D44" s="17"/>
@@ -7151,7 +7226,7 @@
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A45" s="105"/>
+      <c r="A45" s="122"/>
       <c r="B45" s="17"/>
       <c r="C45" s="76"/>
       <c r="D45" s="17"/>
@@ -7168,7 +7243,7 @@
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A46" s="106"/>
+      <c r="A46" s="123"/>
       <c r="B46" s="17"/>
       <c r="C46" s="77"/>
       <c r="D46" s="11"/>
@@ -7185,7 +7260,7 @@
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A47" s="104">
+      <c r="A47" s="121">
         <v>46098</v>
       </c>
       <c r="B47" s="17"/>
@@ -7204,7 +7279,7 @@
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A48" s="105"/>
+      <c r="A48" s="122"/>
       <c r="B48" s="18"/>
       <c r="C48" s="76"/>
       <c r="D48" s="18"/>
@@ -7221,7 +7296,7 @@
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A49" s="105"/>
+      <c r="A49" s="122"/>
       <c r="B49" s="18"/>
       <c r="C49" s="76"/>
       <c r="D49" s="18"/>
@@ -7238,7 +7313,7 @@
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A50" s="105"/>
+      <c r="A50" s="122"/>
       <c r="B50" s="17"/>
       <c r="C50" s="76"/>
       <c r="D50" s="18"/>
@@ -7255,7 +7330,7 @@
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A51" s="105"/>
+      <c r="A51" s="122"/>
       <c r="B51" s="18"/>
       <c r="C51" s="76"/>
       <c r="D51" s="18"/>
@@ -7272,7 +7347,7 @@
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A52" s="106"/>
+      <c r="A52" s="123"/>
       <c r="B52" s="18"/>
       <c r="C52" s="76"/>
       <c r="D52" s="18"/>
@@ -7289,7 +7364,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A53" s="104">
+      <c r="A53" s="121">
         <v>46099</v>
       </c>
       <c r="B53" s="17" t="s">
@@ -7316,7 +7391,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A54" s="105"/>
+      <c r="A54" s="122"/>
       <c r="B54" s="18"/>
       <c r="C54" s="76"/>
       <c r="D54" s="18"/>
@@ -7333,7 +7408,7 @@
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A55" s="105"/>
+      <c r="A55" s="122"/>
       <c r="B55" s="17"/>
       <c r="C55" s="76"/>
       <c r="D55" s="17"/>
@@ -7350,7 +7425,7 @@
       </c>
     </row>
     <row r="56" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A56" s="106"/>
+      <c r="A56" s="123"/>
       <c r="B56" s="18" t="s">
         <v>229</v>
       </c>
@@ -7375,7 +7450,7 @@
       </c>
     </row>
     <row r="57" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A57" s="104">
+      <c r="A57" s="121">
         <v>46100</v>
       </c>
       <c r="B57" s="17" t="s">
@@ -7402,7 +7477,7 @@
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A58" s="106"/>
+      <c r="A58" s="123"/>
       <c r="B58" s="18"/>
       <c r="C58" s="76"/>
       <c r="D58" s="18"/>
@@ -7419,7 +7494,7 @@
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A59" s="104">
+      <c r="A59" s="121">
         <v>46101</v>
       </c>
       <c r="B59" s="18"/>
@@ -7438,7 +7513,7 @@
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A60" s="106"/>
+      <c r="A60" s="123"/>
       <c r="B60" s="18"/>
       <c r="C60" s="76"/>
       <c r="D60" s="18"/>
@@ -7455,7 +7530,7 @@
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A61" s="104">
+      <c r="A61" s="121">
         <v>46102</v>
       </c>
       <c r="B61" s="10"/>
@@ -7474,7 +7549,7 @@
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A62" s="105"/>
+      <c r="A62" s="122"/>
       <c r="B62" s="10"/>
       <c r="C62" s="78"/>
       <c r="D62" s="10"/>
@@ -7491,7 +7566,7 @@
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A63" s="106"/>
+      <c r="A63" s="123"/>
       <c r="B63" s="10"/>
       <c r="C63" s="78"/>
       <c r="D63" s="10"/>
@@ -7527,7 +7602,7 @@
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A65" s="104">
+      <c r="A65" s="121">
         <v>46104</v>
       </c>
       <c r="B65" s="10"/>
@@ -7546,7 +7621,7 @@
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A66" s="105"/>
+      <c r="A66" s="122"/>
       <c r="B66" s="18"/>
       <c r="C66" s="76"/>
       <c r="D66" s="18"/>
@@ -7563,7 +7638,7 @@
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A67" s="106"/>
+      <c r="A67" s="123"/>
       <c r="B67" s="18"/>
       <c r="C67" s="76"/>
       <c r="D67" s="18"/>
@@ -7580,7 +7655,7 @@
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A68" s="104">
+      <c r="A68" s="121">
         <v>46105</v>
       </c>
       <c r="B68" s="18"/>
@@ -7599,7 +7674,7 @@
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A69" s="105"/>
+      <c r="A69" s="122"/>
       <c r="B69" s="18"/>
       <c r="C69" s="76"/>
       <c r="D69" s="18"/>
@@ -7616,7 +7691,7 @@
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A70" s="106"/>
+      <c r="A70" s="123"/>
       <c r="B70" s="18"/>
       <c r="C70" s="76"/>
       <c r="D70" s="18"/>
@@ -7633,7 +7708,7 @@
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A71" s="104">
+      <c r="A71" s="121">
         <v>46106</v>
       </c>
       <c r="B71" s="18"/>
@@ -7652,7 +7727,7 @@
       </c>
     </row>
     <row r="72" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="105"/>
+      <c r="A72" s="122"/>
       <c r="B72" s="18"/>
       <c r="C72" s="76"/>
       <c r="D72" s="18"/>
@@ -7669,7 +7744,7 @@
       </c>
     </row>
     <row r="73" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="105"/>
+      <c r="A73" s="122"/>
       <c r="B73" s="17"/>
       <c r="C73" s="76"/>
       <c r="D73" s="17"/>
@@ -7686,7 +7761,7 @@
       </c>
     </row>
     <row r="74" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="105"/>
+      <c r="A74" s="122"/>
       <c r="B74" s="18"/>
       <c r="C74" s="76"/>
       <c r="D74" s="18"/>
@@ -7703,7 +7778,7 @@
       </c>
     </row>
     <row r="75" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="105"/>
+      <c r="A75" s="122"/>
       <c r="B75" s="18"/>
       <c r="C75" s="76"/>
       <c r="D75" s="18"/>
@@ -7720,7 +7795,7 @@
       </c>
     </row>
     <row r="76" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="105"/>
+      <c r="A76" s="122"/>
       <c r="B76" s="18"/>
       <c r="C76" s="76"/>
       <c r="D76" s="18"/>
@@ -7737,7 +7812,7 @@
       </c>
     </row>
     <row r="77" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="105"/>
+      <c r="A77" s="122"/>
       <c r="B77" s="87"/>
       <c r="C77" s="88"/>
       <c r="D77" s="87"/>
@@ -7754,12 +7829,12 @@
       </c>
     </row>
     <row r="78" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="116"/>
+      <c r="A78" s="133"/>
       <c r="B78" s="51"/>
       <c r="C78" s="79"/>
       <c r="D78" s="51"/>
       <c r="E78" s="52" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F78" s="75"/>
       <c r="G78" s="54">
@@ -7769,7 +7844,7 @@
         <f>H76+F78-G78</f>
         <v>219</v>
       </c>
-      <c r="I78" s="107" t="s">
+      <c r="I78" s="124" t="s">
         <v>9</v>
       </c>
     </row>
@@ -7791,7 +7866,7 @@
         <f>H78+F79-G79</f>
         <v>-781</v>
       </c>
-      <c r="I79" s="117"/>
+      <c r="I79" s="134"/>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="82">
@@ -7813,7 +7888,7 @@
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A81" s="104">
+      <c r="A81" s="121">
         <v>46111</v>
       </c>
       <c r="B81" s="18"/>
@@ -7832,7 +7907,7 @@
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A82" s="105"/>
+      <c r="A82" s="122"/>
       <c r="B82" s="18"/>
       <c r="C82" s="76"/>
       <c r="D82" s="18"/>
@@ -7849,7 +7924,7 @@
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A83" s="106"/>
+      <c r="A83" s="123"/>
       <c r="B83" s="18"/>
       <c r="C83" s="76"/>
       <c r="D83" s="18"/>
@@ -8296,6 +8371,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78EB2AAE-1BD7-400D-A761-4D5DA9FAB287}">
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FF92D050"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:T113"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -8323,42 +8399,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="125" t="s">
+      <c r="A1" s="141" t="s">
         <v>259</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="125"/>
-      <c r="D1" s="125"/>
-      <c r="E1" s="125"/>
-      <c r="F1" s="125"/>
-      <c r="G1" s="125"/>
-      <c r="H1" s="125"/>
-      <c r="J1" s="125" t="s">
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="J1" s="141" t="s">
         <v>259</v>
       </c>
-      <c r="K1" s="125"/>
-      <c r="L1" s="125"/>
-      <c r="M1" s="125"/>
-      <c r="N1" s="125"/>
-      <c r="O1" s="125"/>
-      <c r="P1" s="125"/>
-      <c r="Q1" s="125"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="141"/>
       <c r="R1" s="1"/>
     </row>
     <row r="2" spans="1:20" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="123" t="s">
+      <c r="A2" s="139" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="121" t="s">
+      <c r="B2" s="137" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="121" t="s">
+      <c r="C2" s="137" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="121" t="s">
+      <c r="D2" s="137" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="119" t="s">
+      <c r="E2" s="135" t="s">
         <v>6</v>
       </c>
       <c r="F2" s="62" t="s">
@@ -8371,77 +8447,77 @@
         <v>2</v>
       </c>
       <c r="J2" s="102" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="K2" s="100" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="L2" s="98" t="s">
+        <v>306</v>
+      </c>
+      <c r="M2" s="108" t="s">
+        <v>304</v>
+      </c>
+      <c r="N2" s="108" t="s">
+        <v>292</v>
+      </c>
+      <c r="O2" s="108" t="s">
+        <v>302</v>
+      </c>
+      <c r="P2" s="109" t="s">
+        <v>305</v>
+      </c>
+      <c r="Q2" s="107" t="s">
         <v>310</v>
       </c>
-      <c r="M2" s="132" t="s">
-        <v>308</v>
-      </c>
-      <c r="N2" s="132" t="s">
-        <v>296</v>
-      </c>
-      <c r="O2" s="132" t="s">
-        <v>306</v>
-      </c>
-      <c r="P2" s="133" t="s">
-        <v>309</v>
-      </c>
-      <c r="Q2" s="131" t="s">
-        <v>315</v>
-      </c>
       <c r="R2" s="1"/>
     </row>
     <row r="3" spans="1:20" s="22" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="124"/>
-      <c r="B3" s="122"/>
-      <c r="C3" s="122"/>
-      <c r="D3" s="122"/>
-      <c r="E3" s="120"/>
+      <c r="A3" s="140"/>
+      <c r="B3" s="138"/>
+      <c r="C3" s="138"/>
+      <c r="D3" s="138"/>
+      <c r="E3" s="136"/>
       <c r="F3" s="64">
         <f>SUM(F4:F268)</f>
-        <v>36071</v>
+        <v>41071</v>
       </c>
       <c r="G3" s="65">
         <f>SUM(G4:G268)</f>
-        <v>34778</v>
+        <v>36233</v>
       </c>
       <c r="H3" s="72">
         <f>+F3-G3</f>
-        <v>1293</v>
+        <v>4838</v>
       </c>
       <c r="J3" s="103">
         <f>SUM(J4:J268)</f>
-        <v>8470</v>
+        <v>9200</v>
       </c>
       <c r="K3" s="101">
         <f>SUM(K4:K268)</f>
-        <v>9028</v>
+        <v>10568</v>
       </c>
       <c r="L3" s="99">
         <f>SUM(L4:L268)</f>
-        <v>2746</v>
-      </c>
-      <c r="M3" s="138">
+        <v>2886</v>
+      </c>
+      <c r="M3" s="114">
         <f>SUM(M4:M268)</f>
-        <v>10628</v>
-      </c>
-      <c r="N3" s="129" t="s">
-        <v>307</v>
-      </c>
-      <c r="O3" s="128">
+        <v>12773</v>
+      </c>
+      <c r="N3" s="105" t="s">
+        <v>303</v>
+      </c>
+      <c r="O3" s="104">
         <f>SUM(O4:O268)</f>
-        <v>30000</v>
-      </c>
-      <c r="P3" s="128">
+        <v>38000</v>
+      </c>
+      <c r="P3" s="104">
         <f>+M3-O3</f>
-        <v>-19372</v>
-      </c>
-      <c r="Q3" s="130"/>
+        <v>-25227</v>
+      </c>
+      <c r="Q3" s="106"/>
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
@@ -8455,14 +8531,14 @@
       <c r="F4" s="66"/>
       <c r="G4" s="67"/>
       <c r="H4" s="73"/>
-      <c r="J4" s="102"/>
-      <c r="K4" s="100"/>
-      <c r="L4" s="98"/>
-      <c r="M4" s="139">
+      <c r="J4" s="78"/>
+      <c r="K4" s="78"/>
+      <c r="L4" s="78"/>
+      <c r="M4" s="105">
         <f>E4</f>
         <v>0</v>
       </c>
-      <c r="N4" s="129"/>
+      <c r="N4" s="105"/>
       <c r="O4" s="77">
         <v>0</v>
       </c>
@@ -8498,14 +8574,14 @@
         <f t="shared" ref="H5:H69" si="0">H4+F5-G5</f>
         <v>-2731</v>
       </c>
-      <c r="J5" s="102"/>
-      <c r="K5" s="100"/>
-      <c r="L5" s="98"/>
-      <c r="M5" s="139">
+      <c r="J5" s="78"/>
+      <c r="K5" s="78"/>
+      <c r="L5" s="78"/>
+      <c r="M5" s="105">
         <f>G5</f>
         <v>0</v>
       </c>
-      <c r="N5" s="129"/>
+      <c r="N5" s="105"/>
       <c r="O5" s="77">
         <v>0</v>
       </c>
@@ -8518,20 +8594,20 @@
       <c r="T5" s="1"/>
     </row>
     <row r="6" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="104">
+      <c r="A6" s="121">
         <v>46114</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C6" s="76" t="s">
         <v>25</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>264</v>
-      </c>
-      <c r="E6" s="134" t="s">
-        <v>331</v>
+        <v>262</v>
+      </c>
+      <c r="E6" s="110" t="s">
+        <v>316</v>
       </c>
       <c r="F6" s="13">
         <v>5000</v>
@@ -8543,16 +8619,16 @@
         <f t="shared" si="0"/>
         <v>-2581</v>
       </c>
-      <c r="J6" s="102"/>
+      <c r="J6" s="78"/>
       <c r="K6" s="100">
         <f>G6</f>
         <v>4850</v>
       </c>
-      <c r="L6" s="98"/>
-      <c r="M6" s="139">
-        <v>0</v>
-      </c>
-      <c r="N6" s="129"/>
+      <c r="L6" s="78"/>
+      <c r="M6" s="105">
+        <v>0</v>
+      </c>
+      <c r="N6" s="105"/>
       <c r="O6" s="77">
         <v>0</v>
       </c>
@@ -8565,18 +8641,18 @@
       <c r="T6" s="1"/>
     </row>
     <row r="7" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="105"/>
+      <c r="A7" s="122"/>
       <c r="B7" s="17" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C7" s="76" t="s">
         <v>25</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>264</v>
-      </c>
-      <c r="E7" s="134" t="s">
-        <v>329</v>
+        <v>262</v>
+      </c>
+      <c r="E7" s="110" t="s">
+        <v>314</v>
       </c>
       <c r="F7" s="24">
         <v>10000</v>
@@ -8588,16 +8664,16 @@
         <f t="shared" si="0"/>
         <v>6569</v>
       </c>
-      <c r="J7" s="102"/>
+      <c r="J7" s="78"/>
       <c r="K7" s="100">
         <f>G7</f>
         <v>850</v>
       </c>
-      <c r="L7" s="98"/>
-      <c r="M7" s="139">
-        <v>0</v>
-      </c>
-      <c r="N7" s="129"/>
+      <c r="L7" s="78"/>
+      <c r="M7" s="105">
+        <v>0</v>
+      </c>
+      <c r="N7" s="105"/>
       <c r="O7" s="77">
         <v>0</v>
       </c>
@@ -8610,18 +8686,18 @@
       <c r="T7" s="1"/>
     </row>
     <row r="8" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="105"/>
+      <c r="A8" s="122"/>
       <c r="B8" s="17" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C8" s="76" t="s">
         <v>25</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>264</v>
-      </c>
-      <c r="E8" s="134" t="s">
-        <v>330</v>
+        <v>262</v>
+      </c>
+      <c r="E8" s="110" t="s">
+        <v>315</v>
       </c>
       <c r="F8" s="24">
         <v>5000</v>
@@ -8633,16 +8709,16 @@
         <f t="shared" si="0"/>
         <v>11469</v>
       </c>
-      <c r="J8" s="102"/>
+      <c r="J8" s="78"/>
       <c r="K8" s="100">
         <f>G8</f>
         <v>100</v>
       </c>
-      <c r="L8" s="98"/>
-      <c r="M8" s="139">
-        <v>0</v>
-      </c>
-      <c r="N8" s="129"/>
+      <c r="L8" s="78"/>
+      <c r="M8" s="105">
+        <v>0</v>
+      </c>
+      <c r="N8" s="105"/>
       <c r="O8" s="77">
         <v>0</v>
       </c>
@@ -8655,11 +8731,11 @@
       <c r="T8" s="1"/>
     </row>
     <row r="9" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="105"/>
+      <c r="A9" s="122"/>
       <c r="B9" s="17"/>
       <c r="C9" s="76"/>
       <c r="D9" s="17"/>
-      <c r="E9" s="135" t="s">
+      <c r="E9" s="111" t="s">
         <v>260</v>
       </c>
       <c r="F9" s="24">
@@ -8672,18 +8748,18 @@
         <f t="shared" si="0"/>
         <v>8269</v>
       </c>
-      <c r="J9" s="126">
+      <c r="J9" s="102">
         <f>G9</f>
         <v>3200</v>
       </c>
-      <c r="K9" s="100">
-        <v>0</v>
-      </c>
-      <c r="L9" s="98"/>
-      <c r="M9" s="139">
-        <v>0</v>
-      </c>
-      <c r="N9" s="129"/>
+      <c r="K9" s="78">
+        <v>0</v>
+      </c>
+      <c r="L9" s="78"/>
+      <c r="M9" s="105">
+        <v>0</v>
+      </c>
+      <c r="N9" s="105"/>
       <c r="O9" s="77">
         <v>0</v>
       </c>
@@ -8696,12 +8772,12 @@
       <c r="T9" s="1"/>
     </row>
     <row r="10" spans="1:20" s="15" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A10" s="105"/>
+      <c r="A10" s="122"/>
       <c r="B10" s="18"/>
       <c r="C10" s="76"/>
       <c r="D10" s="17"/>
-      <c r="E10" s="134" t="s">
-        <v>328</v>
+      <c r="E10" s="110" t="s">
+        <v>313</v>
       </c>
       <c r="F10" s="24"/>
       <c r="G10" s="23">
@@ -8711,16 +8787,16 @@
         <f t="shared" si="0"/>
         <v>8019</v>
       </c>
-      <c r="J10" s="102"/>
+      <c r="J10" s="78"/>
       <c r="K10" s="100">
         <f>G10</f>
         <v>250</v>
       </c>
-      <c r="L10" s="98"/>
-      <c r="M10" s="139">
-        <v>0</v>
-      </c>
-      <c r="N10" s="129"/>
+      <c r="L10" s="78"/>
+      <c r="M10" s="105">
+        <v>0</v>
+      </c>
+      <c r="N10" s="105"/>
       <c r="O10" s="77">
         <v>0</v>
       </c>
@@ -8733,12 +8809,12 @@
       <c r="T10" s="1"/>
     </row>
     <row r="11" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="106"/>
+      <c r="A11" s="123"/>
       <c r="B11" s="17"/>
       <c r="C11" s="76"/>
       <c r="D11" s="17"/>
-      <c r="E11" s="137" t="s">
-        <v>261</v>
+      <c r="E11" s="113" t="s">
+        <v>319</v>
       </c>
       <c r="F11" s="24"/>
       <c r="G11" s="23">
@@ -8748,15 +8824,15 @@
         <f t="shared" si="0"/>
         <v>6544</v>
       </c>
-      <c r="J11" s="102"/>
-      <c r="K11" s="100"/>
-      <c r="L11" s="98"/>
-      <c r="M11" s="139">
+      <c r="J11" s="78"/>
+      <c r="K11" s="78"/>
+      <c r="L11" s="78"/>
+      <c r="M11" s="115">
         <f>G11</f>
         <v>1475</v>
       </c>
-      <c r="N11" s="129" t="s">
-        <v>297</v>
+      <c r="N11" s="105" t="s">
+        <v>293</v>
       </c>
       <c r="O11" s="77">
         <v>2000</v>
@@ -8770,14 +8846,14 @@
       <c r="T11" s="1"/>
     </row>
     <row r="12" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="104">
+      <c r="A12" s="121">
         <v>46115</v>
       </c>
       <c r="B12" s="17"/>
       <c r="C12" s="76"/>
       <c r="D12" s="17"/>
-      <c r="E12" s="137" t="s">
-        <v>262</v>
+      <c r="E12" s="110" t="s">
+        <v>323</v>
       </c>
       <c r="F12" s="24"/>
       <c r="G12" s="23">
@@ -8787,32 +8863,34 @@
         <f t="shared" si="0"/>
         <v>6274</v>
       </c>
-      <c r="J12" s="102"/>
-      <c r="K12" s="100"/>
-      <c r="L12" s="98"/>
-      <c r="M12" s="139">
-        <f t="shared" ref="M12:M13" si="2">G12</f>
+      <c r="J12" s="78"/>
+      <c r="K12" s="100">
+        <f>G12</f>
         <v>270</v>
       </c>
-      <c r="N12" s="129"/>
+      <c r="L12" s="78"/>
+      <c r="M12" s="105">
+        <v>0</v>
+      </c>
+      <c r="N12" s="105"/>
       <c r="O12" s="77">
         <v>0</v>
       </c>
       <c r="P12" s="77">
         <f t="shared" si="1"/>
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
     </row>
     <row r="13" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="106"/>
+      <c r="A13" s="123"/>
       <c r="B13" s="18"/>
       <c r="C13" s="76"/>
       <c r="D13" s="17"/>
-      <c r="E13" s="137" t="s">
-        <v>262</v>
+      <c r="E13" s="113" t="s">
+        <v>322</v>
       </c>
       <c r="F13" s="24"/>
       <c r="G13" s="23">
@@ -8822,34 +8900,36 @@
         <f t="shared" si="0"/>
         <v>5774</v>
       </c>
-      <c r="J13" s="102"/>
-      <c r="K13" s="100"/>
-      <c r="L13" s="98"/>
-      <c r="M13" s="139">
-        <f t="shared" si="2"/>
+      <c r="J13" s="78"/>
+      <c r="K13" s="100">
+        <f>G13</f>
         <v>500</v>
       </c>
-      <c r="N13" s="129"/>
+      <c r="L13" s="78"/>
+      <c r="M13" s="105">
+        <v>0</v>
+      </c>
+      <c r="N13" s="105"/>
       <c r="O13" s="77">
         <v>0</v>
       </c>
       <c r="P13" s="77">
         <f t="shared" si="1"/>
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
       <c r="T13" s="1"/>
     </row>
     <row r="14" spans="1:20" s="15" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A14" s="104">
+      <c r="A14" s="121">
         <v>46116</v>
       </c>
       <c r="B14" s="17"/>
       <c r="C14" s="76"/>
       <c r="D14" s="17"/>
-      <c r="E14" s="134" t="s">
-        <v>327</v>
+      <c r="E14" s="110" t="s">
+        <v>312</v>
       </c>
       <c r="F14" s="24">
         <v>0</v>
@@ -8861,16 +8941,16 @@
         <f t="shared" si="0"/>
         <v>5704</v>
       </c>
-      <c r="J14" s="102"/>
+      <c r="J14" s="78"/>
       <c r="K14" s="100">
         <f>G14</f>
         <v>70</v>
       </c>
-      <c r="L14" s="98"/>
-      <c r="M14" s="139">
-        <v>0</v>
-      </c>
-      <c r="N14" s="129"/>
+      <c r="L14" s="78"/>
+      <c r="M14" s="105">
+        <v>0</v>
+      </c>
+      <c r="N14" s="105"/>
       <c r="O14" s="77">
         <v>0</v>
       </c>
@@ -8886,12 +8966,12 @@
       <c r="T14" s="1"/>
     </row>
     <row r="15" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="105"/>
+      <c r="A15" s="122"/>
       <c r="B15" s="17"/>
       <c r="C15" s="76"/>
       <c r="D15" s="17"/>
-      <c r="E15" s="137" t="s">
-        <v>266</v>
+      <c r="E15" s="113" t="s">
+        <v>264</v>
       </c>
       <c r="F15" s="24"/>
       <c r="G15" s="23">
@@ -8901,15 +8981,15 @@
         <f t="shared" si="0"/>
         <v>5304</v>
       </c>
-      <c r="J15" s="102"/>
-      <c r="K15" s="100"/>
-      <c r="L15" s="98"/>
-      <c r="M15" s="139">
+      <c r="J15" s="78"/>
+      <c r="K15" s="78"/>
+      <c r="L15" s="78"/>
+      <c r="M15" s="115">
         <f>G15</f>
         <v>400</v>
       </c>
-      <c r="N15" s="129" t="s">
-        <v>298</v>
+      <c r="N15" s="105" t="s">
+        <v>294</v>
       </c>
       <c r="O15" s="77">
         <v>2000</v>
@@ -8923,29 +9003,31 @@
       <c r="T15" s="1"/>
     </row>
     <row r="16" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="105"/>
+      <c r="A16" s="122"/>
       <c r="B16" s="17"/>
       <c r="C16" s="76"/>
       <c r="D16" s="17"/>
-      <c r="E16" s="140" t="s">
-        <v>326</v>
+      <c r="E16" s="116" t="s">
+        <v>320</v>
       </c>
       <c r="F16" s="24"/>
-      <c r="G16" s="142">
+      <c r="G16" s="23">
         <v>111</v>
       </c>
       <c r="H16" s="47">
         <f t="shared" si="0"/>
         <v>5193</v>
       </c>
-      <c r="J16" s="102"/>
-      <c r="K16" s="100"/>
-      <c r="L16" s="98"/>
-      <c r="M16" s="139">
-        <f t="shared" ref="M16:M19" si="3">G16</f>
+      <c r="J16" s="78"/>
+      <c r="K16" s="78"/>
+      <c r="L16" s="78"/>
+      <c r="M16" s="115">
+        <f t="shared" ref="M16:M19" si="2">G16</f>
         <v>111</v>
       </c>
-      <c r="N16" s="129"/>
+      <c r="N16" s="105" t="s">
+        <v>321</v>
+      </c>
       <c r="O16" s="77">
         <v>0</v>
       </c>
@@ -8958,29 +9040,31 @@
       <c r="T16" s="1"/>
     </row>
     <row r="17" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="105"/>
+      <c r="A17" s="122"/>
       <c r="B17" s="17"/>
       <c r="C17" s="76"/>
       <c r="D17" s="17"/>
-      <c r="E17" s="141" t="s">
-        <v>317</v>
+      <c r="E17" s="117" t="s">
+        <v>337</v>
       </c>
       <c r="F17" s="24"/>
-      <c r="G17" s="142">
+      <c r="G17" s="23">
         <v>70</v>
       </c>
       <c r="H17" s="47">
         <f t="shared" si="0"/>
         <v>5123</v>
       </c>
-      <c r="J17" s="102"/>
-      <c r="K17" s="100"/>
-      <c r="L17" s="98"/>
-      <c r="M17" s="139">
-        <f t="shared" si="3"/>
+      <c r="J17" s="78"/>
+      <c r="K17" s="78"/>
+      <c r="L17" s="78"/>
+      <c r="M17" s="115">
+        <f t="shared" si="2"/>
         <v>70</v>
       </c>
-      <c r="N17" s="129"/>
+      <c r="N17" s="105" t="s">
+        <v>338</v>
+      </c>
       <c r="O17" s="77">
         <v>0</v>
       </c>
@@ -8993,84 +9077,88 @@
       <c r="T17" s="1"/>
     </row>
     <row r="18" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="106"/>
+      <c r="A18" s="123"/>
       <c r="B18" s="17"/>
       <c r="C18" s="76"/>
       <c r="D18" s="17"/>
-      <c r="E18" s="141" t="s">
-        <v>316</v>
+      <c r="E18" s="110" t="s">
+        <v>339</v>
       </c>
       <c r="F18" s="24"/>
-      <c r="G18" s="142">
+      <c r="G18" s="23">
         <v>450</v>
       </c>
       <c r="H18" s="47">
         <f t="shared" si="0"/>
         <v>4673</v>
       </c>
-      <c r="J18" s="102"/>
-      <c r="K18" s="100"/>
-      <c r="L18" s="98"/>
-      <c r="M18" s="139">
-        <f t="shared" si="3"/>
+      <c r="J18" s="78"/>
+      <c r="K18" s="100">
+        <f>G18</f>
         <v>450</v>
       </c>
-      <c r="N18" s="129"/>
+      <c r="L18" s="78"/>
+      <c r="M18" s="105">
+        <v>0</v>
+      </c>
+      <c r="N18" s="105"/>
       <c r="O18" s="77">
         <v>0</v>
       </c>
       <c r="P18" s="77">
         <f t="shared" si="1"/>
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
       <c r="T18" s="1"/>
     </row>
     <row r="19" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="104">
+      <c r="A19" s="121">
         <v>46118</v>
       </c>
       <c r="B19" s="17"/>
       <c r="C19" s="76"/>
       <c r="D19" s="17"/>
-      <c r="E19" s="140" t="s">
-        <v>324</v>
+      <c r="E19" s="116" t="s">
+        <v>333</v>
       </c>
       <c r="F19" s="24"/>
-      <c r="G19" s="142">
+      <c r="G19" s="23">
         <v>210</v>
       </c>
       <c r="H19" s="47">
         <f t="shared" si="0"/>
         <v>4463</v>
       </c>
-      <c r="J19" s="102"/>
-      <c r="K19" s="100"/>
-      <c r="L19" s="98"/>
-      <c r="M19" s="139">
-        <f t="shared" si="3"/>
+      <c r="J19" s="78"/>
+      <c r="K19" s="78"/>
+      <c r="L19" s="78"/>
+      <c r="M19" s="115">
+        <f t="shared" si="2"/>
         <v>210</v>
       </c>
-      <c r="N19" s="129"/>
+      <c r="N19" s="105" t="s">
+        <v>334</v>
+      </c>
       <c r="O19" s="77">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="P19" s="77">
         <f t="shared" si="1"/>
-        <v>210</v>
+        <v>-1790</v>
       </c>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
     </row>
     <row r="20" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="105"/>
+      <c r="A20" s="122"/>
       <c r="B20" s="17"/>
       <c r="C20" s="76"/>
       <c r="D20" s="17"/>
-      <c r="E20" s="137" t="s">
-        <v>267</v>
+      <c r="E20" s="113" t="s">
+        <v>265</v>
       </c>
       <c r="F20" s="24"/>
       <c r="G20" s="23">
@@ -9080,15 +9168,15 @@
         <f t="shared" si="0"/>
         <v>4283</v>
       </c>
-      <c r="J20" s="102"/>
-      <c r="K20" s="100"/>
-      <c r="L20" s="98"/>
-      <c r="M20" s="139">
-        <f t="shared" ref="M20:M25" si="4">G20</f>
+      <c r="J20" s="78"/>
+      <c r="K20" s="78"/>
+      <c r="L20" s="78"/>
+      <c r="M20" s="115">
+        <f t="shared" ref="M20:M25" si="3">G20</f>
         <v>180</v>
       </c>
-      <c r="N20" s="129" t="s">
-        <v>299</v>
+      <c r="N20" s="105" t="s">
+        <v>295</v>
       </c>
       <c r="O20" s="77">
         <v>2000</v>
@@ -9102,47 +9190,49 @@
       <c r="T20" s="1"/>
     </row>
     <row r="21" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="105"/>
+      <c r="A21" s="122"/>
       <c r="B21" s="17"/>
       <c r="C21" s="76"/>
       <c r="D21" s="17"/>
-      <c r="E21" s="137" t="s">
-        <v>318</v>
+      <c r="E21" s="110" t="s">
+        <v>324</v>
       </c>
       <c r="F21" s="24"/>
-      <c r="G21" s="142">
+      <c r="G21" s="23">
         <v>320</v>
       </c>
       <c r="H21" s="47">
         <f t="shared" si="0"/>
         <v>3963</v>
       </c>
-      <c r="J21" s="102"/>
-      <c r="K21" s="100"/>
-      <c r="L21" s="98"/>
-      <c r="M21" s="139">
-        <f t="shared" si="4"/>
+      <c r="J21" s="78"/>
+      <c r="K21" s="100">
+        <f>G21</f>
         <v>320</v>
       </c>
-      <c r="N21" s="129"/>
+      <c r="L21" s="78"/>
+      <c r="M21" s="105">
+        <v>0</v>
+      </c>
+      <c r="N21" s="105"/>
       <c r="O21" s="77">
         <v>0</v>
       </c>
       <c r="P21" s="77">
         <f t="shared" si="1"/>
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
       <c r="T21" s="1"/>
     </row>
     <row r="22" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="105"/>
+      <c r="A22" s="122"/>
       <c r="B22" s="17"/>
       <c r="C22" s="76"/>
       <c r="D22" s="17"/>
-      <c r="E22" s="137" t="s">
-        <v>268</v>
+      <c r="E22" s="113" t="s">
+        <v>266</v>
       </c>
       <c r="F22" s="24"/>
       <c r="G22" s="23">
@@ -9152,15 +9242,15 @@
         <f t="shared" si="0"/>
         <v>3683</v>
       </c>
-      <c r="J22" s="102"/>
-      <c r="K22" s="100"/>
-      <c r="L22" s="98"/>
-      <c r="M22" s="139">
-        <f t="shared" si="4"/>
+      <c r="J22" s="78"/>
+      <c r="K22" s="78"/>
+      <c r="L22" s="78"/>
+      <c r="M22" s="115">
+        <f t="shared" si="3"/>
         <v>280</v>
       </c>
-      <c r="N22" s="129" t="s">
-        <v>298</v>
+      <c r="N22" s="105" t="s">
+        <v>294</v>
       </c>
       <c r="O22" s="77">
         <v>2000</v>
@@ -9174,12 +9264,12 @@
       <c r="T22" s="1"/>
     </row>
     <row r="23" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="106"/>
+      <c r="A23" s="123"/>
       <c r="B23" s="17"/>
       <c r="C23" s="76"/>
       <c r="D23" s="17"/>
-      <c r="E23" s="134" t="s">
-        <v>311</v>
+      <c r="E23" s="110" t="s">
+        <v>336</v>
       </c>
       <c r="F23" s="24"/>
       <c r="G23" s="23">
@@ -9189,16 +9279,16 @@
         <f t="shared" si="0"/>
         <v>1913</v>
       </c>
-      <c r="J23" s="102"/>
+      <c r="J23" s="78"/>
       <c r="K23" s="100">
         <f>G23</f>
         <v>1770</v>
       </c>
-      <c r="L23" s="98"/>
-      <c r="M23" s="139">
-        <v>0</v>
-      </c>
-      <c r="N23" s="129"/>
+      <c r="L23" s="78"/>
+      <c r="M23" s="105">
+        <v>0</v>
+      </c>
+      <c r="N23" s="105"/>
       <c r="O23" s="77">
         <v>0</v>
       </c>
@@ -9211,33 +9301,35 @@
       <c r="T23" s="1"/>
     </row>
     <row r="24" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="104">
+      <c r="A24" s="121">
         <v>46119</v>
       </c>
       <c r="B24" s="17"/>
       <c r="C24" s="76"/>
       <c r="D24" s="17"/>
-      <c r="E24" s="140" t="s">
+      <c r="E24" s="116" t="s">
         <v>325</v>
       </c>
       <c r="F24" s="24">
         <v>0</v>
       </c>
-      <c r="G24" s="142">
+      <c r="G24" s="23">
         <v>400</v>
       </c>
       <c r="H24" s="47">
         <f t="shared" si="0"/>
         <v>1513</v>
       </c>
-      <c r="J24" s="102"/>
-      <c r="K24" s="100"/>
-      <c r="L24" s="98"/>
-      <c r="M24" s="139">
-        <f t="shared" si="4"/>
+      <c r="J24" s="78"/>
+      <c r="K24" s="78"/>
+      <c r="L24" s="78"/>
+      <c r="M24" s="115">
+        <f t="shared" si="3"/>
         <v>400</v>
       </c>
-      <c r="N24" s="129"/>
+      <c r="N24" s="105" t="s">
+        <v>328</v>
+      </c>
       <c r="O24" s="77">
         <v>0</v>
       </c>
@@ -9250,29 +9342,31 @@
       <c r="T24" s="1"/>
     </row>
     <row r="25" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="105"/>
+      <c r="A25" s="122"/>
       <c r="B25" s="17"/>
       <c r="C25" s="76"/>
       <c r="D25" s="17"/>
-      <c r="E25" s="140" t="s">
-        <v>323</v>
+      <c r="E25" s="116" t="s">
+        <v>335</v>
       </c>
       <c r="F25" s="24"/>
-      <c r="G25" s="142">
+      <c r="G25" s="23">
         <v>72</v>
       </c>
       <c r="H25" s="47">
         <f t="shared" si="0"/>
         <v>1441</v>
       </c>
-      <c r="J25" s="102"/>
-      <c r="K25" s="100"/>
-      <c r="L25" s="98"/>
-      <c r="M25" s="139">
-        <f t="shared" si="4"/>
+      <c r="J25" s="78"/>
+      <c r="K25" s="78"/>
+      <c r="L25" s="78"/>
+      <c r="M25" s="115">
+        <f t="shared" si="3"/>
         <v>72</v>
       </c>
-      <c r="N25" s="129"/>
+      <c r="N25" s="105" t="s">
+        <v>328</v>
+      </c>
       <c r="O25" s="77">
         <v>0</v>
       </c>
@@ -9285,12 +9379,12 @@
       <c r="T25" s="1"/>
     </row>
     <row r="26" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="105"/>
+      <c r="A26" s="122"/>
       <c r="B26" s="17"/>
       <c r="C26" s="76"/>
       <c r="D26" s="17"/>
-      <c r="E26" s="135" t="s">
-        <v>269</v>
+      <c r="E26" s="111" t="s">
+        <v>267</v>
       </c>
       <c r="F26" s="24"/>
       <c r="G26" s="23">
@@ -9300,16 +9394,16 @@
         <f t="shared" si="0"/>
         <v>941</v>
       </c>
-      <c r="J26" s="126">
+      <c r="J26" s="102">
         <f>G26</f>
         <v>500</v>
       </c>
-      <c r="K26" s="100"/>
-      <c r="L26" s="98"/>
-      <c r="M26" s="139">
-        <v>0</v>
-      </c>
-      <c r="N26" s="129"/>
+      <c r="K26" s="78"/>
+      <c r="L26" s="78"/>
+      <c r="M26" s="105">
+        <v>0</v>
+      </c>
+      <c r="N26" s="105"/>
       <c r="O26" s="77">
         <v>0</v>
       </c>
@@ -9322,12 +9416,12 @@
       <c r="T26" s="1"/>
     </row>
     <row r="27" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="105"/>
+      <c r="A27" s="122"/>
       <c r="B27" s="17"/>
       <c r="C27" s="76"/>
       <c r="D27" s="17"/>
-      <c r="E27" s="137" t="s">
-        <v>270</v>
+      <c r="E27" s="113" t="s">
+        <v>326</v>
       </c>
       <c r="F27" s="24"/>
       <c r="G27" s="23">
@@ -9337,15 +9431,15 @@
         <f t="shared" si="0"/>
         <v>761</v>
       </c>
-      <c r="J27" s="102"/>
-      <c r="K27" s="100"/>
-      <c r="L27" s="98"/>
-      <c r="M27" s="139">
+      <c r="J27" s="78"/>
+      <c r="K27" s="78"/>
+      <c r="L27" s="78"/>
+      <c r="M27" s="115">
         <f>G27</f>
         <v>180</v>
       </c>
-      <c r="N27" s="129" t="s">
-        <v>300</v>
+      <c r="N27" s="105" t="s">
+        <v>296</v>
       </c>
       <c r="O27" s="77">
         <v>2000</v>
@@ -9359,12 +9453,12 @@
       <c r="T27" s="1"/>
     </row>
     <row r="28" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="105"/>
+      <c r="A28" s="122"/>
       <c r="B28" s="17"/>
       <c r="C28" s="76"/>
       <c r="D28" s="17"/>
-      <c r="E28" s="134" t="s">
-        <v>271</v>
+      <c r="E28" s="110" t="s">
+        <v>268</v>
       </c>
       <c r="F28" s="24"/>
       <c r="G28" s="23">
@@ -9374,16 +9468,16 @@
         <f t="shared" si="0"/>
         <v>-377</v>
       </c>
-      <c r="J28" s="102"/>
+      <c r="J28" s="78"/>
       <c r="K28" s="100">
         <f>G28</f>
         <v>1138</v>
       </c>
-      <c r="L28" s="98"/>
-      <c r="M28" s="139">
-        <v>0</v>
-      </c>
-      <c r="N28" s="129"/>
+      <c r="L28" s="78"/>
+      <c r="M28" s="105">
+        <v>0</v>
+      </c>
+      <c r="N28" s="105"/>
       <c r="O28" s="77">
         <v>0</v>
       </c>
@@ -9396,12 +9490,12 @@
       <c r="T28" s="1"/>
     </row>
     <row r="29" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="106"/>
+      <c r="A29" s="123"/>
       <c r="B29" s="17"/>
       <c r="C29" s="76"/>
       <c r="D29" s="17"/>
-      <c r="E29" s="137" t="s">
-        <v>272</v>
+      <c r="E29" s="113" t="s">
+        <v>269</v>
       </c>
       <c r="F29" s="24"/>
       <c r="G29" s="23">
@@ -9411,15 +9505,15 @@
         <f t="shared" si="0"/>
         <v>-677</v>
       </c>
-      <c r="J29" s="102"/>
-      <c r="K29" s="100"/>
-      <c r="L29" s="98"/>
-      <c r="M29" s="139">
+      <c r="J29" s="78"/>
+      <c r="K29" s="78"/>
+      <c r="L29" s="78"/>
+      <c r="M29" s="115">
         <f>G29</f>
         <v>300</v>
       </c>
-      <c r="N29" s="129" t="s">
-        <v>298</v>
+      <c r="N29" s="105" t="s">
+        <v>294</v>
       </c>
       <c r="O29" s="77">
         <v>2000</v>
@@ -9433,33 +9527,33 @@
       <c r="T29" s="1"/>
     </row>
     <row r="30" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="104">
+      <c r="A30" s="121">
         <v>46120</v>
       </c>
       <c r="B30" s="18"/>
       <c r="C30" s="76"/>
       <c r="D30" s="17"/>
-      <c r="E30" s="136" t="s">
-        <v>273</v>
+      <c r="E30" s="112" t="s">
+        <v>270</v>
       </c>
       <c r="F30" s="24"/>
-      <c r="G30" s="143">
+      <c r="G30" s="23">
         <v>197</v>
       </c>
       <c r="H30" s="47">
         <f t="shared" si="0"/>
         <v>-874</v>
       </c>
-      <c r="J30" s="102"/>
-      <c r="K30" s="100"/>
-      <c r="L30" s="127">
+      <c r="J30" s="78"/>
+      <c r="K30" s="78"/>
+      <c r="L30" s="98">
         <f>G30</f>
         <v>197</v>
       </c>
-      <c r="M30" s="139">
-        <v>0</v>
-      </c>
-      <c r="N30" s="129"/>
+      <c r="M30" s="105">
+        <v>0</v>
+      </c>
+      <c r="N30" s="105"/>
       <c r="O30" s="77">
         <v>0</v>
       </c>
@@ -9472,12 +9566,12 @@
       <c r="T30" s="1"/>
     </row>
     <row r="31" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="105"/>
+      <c r="A31" s="122"/>
       <c r="B31" s="17"/>
       <c r="C31" s="76"/>
       <c r="D31" s="17"/>
-      <c r="E31" s="137" t="s">
-        <v>274</v>
+      <c r="E31" s="113" t="s">
+        <v>271</v>
       </c>
       <c r="F31" s="24"/>
       <c r="G31" s="23">
@@ -9487,15 +9581,15 @@
         <f t="shared" si="0"/>
         <v>-1424</v>
       </c>
-      <c r="J31" s="102"/>
-      <c r="K31" s="100"/>
-      <c r="L31" s="98"/>
-      <c r="M31" s="139">
+      <c r="J31" s="78"/>
+      <c r="K31" s="78"/>
+      <c r="L31" s="78"/>
+      <c r="M31" s="115">
         <f>G31</f>
         <v>550</v>
       </c>
-      <c r="N31" s="129" t="s">
-        <v>298</v>
+      <c r="N31" s="105" t="s">
+        <v>294</v>
       </c>
       <c r="O31" s="77">
         <v>2000</v>
@@ -9509,12 +9603,12 @@
       <c r="T31" s="1"/>
     </row>
     <row r="32" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="105"/>
+      <c r="A32" s="122"/>
       <c r="B32" s="17"/>
       <c r="C32" s="76"/>
       <c r="D32" s="17"/>
-      <c r="E32" s="137" t="s">
-        <v>275</v>
+      <c r="E32" s="113" t="s">
+        <v>272</v>
       </c>
       <c r="F32" s="24"/>
       <c r="G32" s="23">
@@ -9524,15 +9618,15 @@
         <f t="shared" si="0"/>
         <v>-1574</v>
       </c>
-      <c r="J32" s="102"/>
-      <c r="K32" s="100"/>
-      <c r="L32" s="98"/>
-      <c r="M32" s="139">
+      <c r="J32" s="78"/>
+      <c r="K32" s="78"/>
+      <c r="L32" s="78"/>
+      <c r="M32" s="115">
         <f>G32</f>
         <v>150</v>
       </c>
-      <c r="N32" s="129" t="s">
-        <v>301</v>
+      <c r="N32" s="105" t="s">
+        <v>297</v>
       </c>
       <c r="O32" s="77">
         <v>2000</v>
@@ -9546,48 +9640,51 @@
       <c r="T32" s="1"/>
     </row>
     <row r="33" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="106"/>
+      <c r="A33" s="123"/>
       <c r="B33" s="17"/>
       <c r="C33" s="76"/>
       <c r="D33" s="17"/>
-      <c r="E33" s="137" t="s">
-        <v>321</v>
+      <c r="E33" s="113" t="s">
+        <v>327</v>
       </c>
       <c r="F33" s="24"/>
-      <c r="G33" s="142">
+      <c r="G33" s="23">
         <v>290</v>
       </c>
       <c r="H33" s="47">
         <f t="shared" si="0"/>
         <v>-1864</v>
       </c>
-      <c r="J33" s="102"/>
-      <c r="K33" s="100"/>
-      <c r="L33" s="98"/>
-      <c r="M33" s="139">
-        <v>0</v>
-      </c>
-      <c r="N33" s="129"/>
+      <c r="J33" s="78"/>
+      <c r="K33" s="78"/>
+      <c r="L33" s="78"/>
+      <c r="M33" s="115">
+        <f>G33</f>
+        <v>290</v>
+      </c>
+      <c r="N33" s="105" t="s">
+        <v>298</v>
+      </c>
       <c r="O33" s="77">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="P33" s="77">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-1710</v>
       </c>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
       <c r="T33" s="1"/>
     </row>
     <row r="34" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="104">
+      <c r="A34" s="121">
         <v>46121</v>
       </c>
       <c r="B34" s="17"/>
       <c r="C34" s="76"/>
       <c r="D34" s="17"/>
-      <c r="E34" s="144" t="s">
-        <v>277</v>
+      <c r="E34" s="119" t="s">
+        <v>274</v>
       </c>
       <c r="F34" s="24"/>
       <c r="G34" s="23">
@@ -9597,16 +9694,16 @@
         <f t="shared" si="0"/>
         <v>-2088</v>
       </c>
-      <c r="J34" s="102"/>
-      <c r="K34" s="100"/>
-      <c r="L34" s="127">
+      <c r="J34" s="78"/>
+      <c r="K34" s="78"/>
+      <c r="L34" s="98">
         <f>G34</f>
         <v>224</v>
       </c>
-      <c r="M34" s="139">
-        <v>0</v>
-      </c>
-      <c r="N34" s="129"/>
+      <c r="M34" s="105">
+        <v>0</v>
+      </c>
+      <c r="N34" s="105"/>
       <c r="O34" s="77">
         <v>0</v>
       </c>
@@ -9619,12 +9716,12 @@
       <c r="T34" s="1"/>
     </row>
     <row r="35" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="106"/>
+      <c r="A35" s="123"/>
       <c r="B35" s="17"/>
       <c r="C35" s="76"/>
       <c r="D35" s="17"/>
-      <c r="E35" s="137" t="s">
-        <v>322</v>
+      <c r="E35" s="113" t="s">
+        <v>332</v>
       </c>
       <c r="F35" s="24"/>
       <c r="G35" s="23">
@@ -9634,13 +9731,13 @@
         <f t="shared" si="0"/>
         <v>-2348</v>
       </c>
-      <c r="J35" s="102"/>
-      <c r="K35" s="100"/>
-      <c r="L35" s="98"/>
-      <c r="M35" s="139">
-        <v>0</v>
-      </c>
-      <c r="N35" s="129"/>
+      <c r="J35" s="78"/>
+      <c r="K35" s="78"/>
+      <c r="L35" s="78"/>
+      <c r="M35" s="105">
+        <v>0</v>
+      </c>
+      <c r="N35" s="105"/>
       <c r="O35" s="77">
         <v>0</v>
       </c>
@@ -9657,16 +9754,16 @@
         <v>46122</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C36" s="76" t="s">
         <v>25</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>264</v>
-      </c>
-      <c r="E36" s="144" t="s">
-        <v>276</v>
+        <v>262</v>
+      </c>
+      <c r="E36" s="119" t="s">
+        <v>273</v>
       </c>
       <c r="F36" s="24">
         <v>5000</v>
@@ -9678,16 +9775,16 @@
         <f t="shared" si="0"/>
         <v>2460</v>
       </c>
-      <c r="J36" s="102"/>
-      <c r="K36" s="100"/>
-      <c r="L36" s="127">
+      <c r="J36" s="78"/>
+      <c r="K36" s="78"/>
+      <c r="L36" s="98">
         <f>G36</f>
         <v>192</v>
       </c>
-      <c r="M36" s="139">
-        <v>0</v>
-      </c>
-      <c r="N36" s="129"/>
+      <c r="M36" s="105">
+        <v>0</v>
+      </c>
+      <c r="N36" s="105"/>
       <c r="O36" s="77">
         <v>0</v>
       </c>
@@ -9700,33 +9797,33 @@
       <c r="T36" s="1"/>
     </row>
     <row r="37" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="104">
+      <c r="A37" s="121">
         <v>46123</v>
       </c>
       <c r="B37" s="17"/>
       <c r="C37" s="76"/>
       <c r="D37" s="17"/>
-      <c r="E37" s="144" t="s">
-        <v>273</v>
+      <c r="E37" s="119" t="s">
+        <v>270</v>
       </c>
       <c r="F37" s="24"/>
-      <c r="G37" s="143">
+      <c r="G37" s="23">
         <v>704</v>
       </c>
       <c r="H37" s="47">
         <f t="shared" si="0"/>
         <v>1756</v>
       </c>
-      <c r="J37" s="102"/>
-      <c r="K37" s="100"/>
-      <c r="L37" s="127">
+      <c r="J37" s="78"/>
+      <c r="K37" s="78"/>
+      <c r="L37" s="98">
         <f>G37</f>
         <v>704</v>
       </c>
-      <c r="M37" s="139">
-        <v>0</v>
-      </c>
-      <c r="N37" s="129"/>
+      <c r="M37" s="105">
+        <v>0</v>
+      </c>
+      <c r="N37" s="105"/>
       <c r="O37" s="77">
         <v>0</v>
       </c>
@@ -9739,12 +9836,12 @@
       <c r="T37" s="1"/>
     </row>
     <row r="38" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="105"/>
+      <c r="A38" s="122"/>
       <c r="B38" s="17"/>
       <c r="C38" s="76"/>
       <c r="D38" s="17"/>
-      <c r="E38" s="137" t="s">
-        <v>278</v>
+      <c r="E38" s="113" t="s">
+        <v>275</v>
       </c>
       <c r="F38" s="24"/>
       <c r="G38" s="23">
@@ -9754,15 +9851,15 @@
         <f t="shared" si="0"/>
         <v>1406</v>
       </c>
-      <c r="J38" s="102"/>
-      <c r="K38" s="100"/>
-      <c r="L38" s="98"/>
-      <c r="M38" s="139">
+      <c r="J38" s="78"/>
+      <c r="K38" s="78"/>
+      <c r="L38" s="78"/>
+      <c r="M38" s="115">
         <f>G38</f>
         <v>350</v>
       </c>
-      <c r="N38" s="129" t="s">
-        <v>302</v>
+      <c r="N38" s="105" t="s">
+        <v>298</v>
       </c>
       <c r="O38" s="77">
         <v>2000</v>
@@ -9776,29 +9873,31 @@
       <c r="T38" s="1"/>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A39" s="106"/>
+      <c r="A39" s="123"/>
       <c r="B39" s="25"/>
       <c r="C39" s="77"/>
       <c r="D39" s="11"/>
-      <c r="E39" s="140" t="s">
-        <v>332</v>
+      <c r="E39" s="116" t="s">
+        <v>329</v>
       </c>
       <c r="F39" s="24"/>
-      <c r="G39" s="142">
+      <c r="G39" s="23">
         <v>400</v>
       </c>
       <c r="H39" s="47">
         <f t="shared" si="0"/>
         <v>1006</v>
       </c>
-      <c r="J39" s="102"/>
-      <c r="K39" s="100"/>
-      <c r="L39" s="98"/>
-      <c r="M39" s="139">
+      <c r="J39" s="78"/>
+      <c r="K39" s="78"/>
+      <c r="L39" s="78"/>
+      <c r="M39" s="115">
         <f>G39</f>
         <v>400</v>
       </c>
-      <c r="N39" s="129"/>
+      <c r="N39" s="105" t="s">
+        <v>301</v>
+      </c>
       <c r="O39" s="77">
         <v>0</v>
       </c>
@@ -9815,8 +9914,8 @@
       <c r="B40" s="18"/>
       <c r="C40" s="76"/>
       <c r="D40" s="17"/>
-      <c r="E40" s="137" t="s">
-        <v>319</v>
+      <c r="E40" s="113" t="s">
+        <v>330</v>
       </c>
       <c r="F40" s="24"/>
       <c r="G40" s="23">
@@ -9826,13 +9925,15 @@
         <f t="shared" si="0"/>
         <v>876</v>
       </c>
-      <c r="J40" s="102"/>
-      <c r="K40" s="100"/>
-      <c r="L40" s="98"/>
-      <c r="M40" s="139">
-        <v>0</v>
-      </c>
-      <c r="N40" s="129"/>
+      <c r="J40" s="78"/>
+      <c r="K40" s="78"/>
+      <c r="L40" s="78"/>
+      <c r="M40" s="105">
+        <v>0</v>
+      </c>
+      <c r="N40" s="105" t="s">
+        <v>301</v>
+      </c>
       <c r="O40" s="77">
         <v>0</v>
       </c>
@@ -9849,27 +9950,27 @@
       <c r="B41" s="25"/>
       <c r="C41" s="77"/>
       <c r="D41" s="11"/>
-      <c r="E41" s="93" t="s">
-        <v>273</v>
+      <c r="E41" s="119" t="s">
+        <v>270</v>
       </c>
       <c r="F41" s="24"/>
-      <c r="G41" s="143">
+      <c r="G41" s="23">
         <v>167</v>
       </c>
       <c r="H41" s="47">
         <f t="shared" si="0"/>
         <v>709</v>
       </c>
-      <c r="J41" s="102"/>
-      <c r="K41" s="100"/>
-      <c r="L41" s="127">
+      <c r="J41" s="78"/>
+      <c r="K41" s="78"/>
+      <c r="L41" s="98">
         <f>G41</f>
         <v>167</v>
       </c>
-      <c r="M41" s="139">
-        <v>0</v>
-      </c>
-      <c r="N41" s="129"/>
+      <c r="M41" s="105">
+        <v>0</v>
+      </c>
+      <c r="N41" s="105"/>
       <c r="O41" s="77">
         <v>0</v>
       </c>
@@ -9880,20 +9981,20 @@
       <c r="R41" s="1"/>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A42" s="104">
+      <c r="A42" s="121">
         <v>46126</v>
       </c>
       <c r="B42" s="25" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C42" s="77" t="s">
         <v>25</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>264</v>
-      </c>
-      <c r="E42" s="137" t="s">
-        <v>279</v>
+        <v>262</v>
+      </c>
+      <c r="E42" s="113" t="s">
+        <v>276</v>
       </c>
       <c r="F42" s="24">
         <v>10000</v>
@@ -9905,15 +10006,15 @@
         <f t="shared" si="0"/>
         <v>10389</v>
       </c>
-      <c r="J42" s="102"/>
-      <c r="K42" s="100"/>
-      <c r="L42" s="98"/>
-      <c r="M42" s="139">
+      <c r="J42" s="78"/>
+      <c r="K42" s="78"/>
+      <c r="L42" s="78"/>
+      <c r="M42" s="115">
         <f>G42</f>
         <v>320</v>
       </c>
-      <c r="N42" s="129" t="s">
-        <v>303</v>
+      <c r="N42" s="105" t="s">
+        <v>299</v>
       </c>
       <c r="O42" s="77">
         <v>2000</v>
@@ -9925,12 +10026,12 @@
       <c r="R42" s="1"/>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A43" s="105"/>
+      <c r="A43" s="122"/>
       <c r="B43" s="25"/>
       <c r="C43" s="77"/>
       <c r="D43" s="11"/>
-      <c r="E43" s="137" t="s">
-        <v>280</v>
+      <c r="E43" s="113" t="s">
+        <v>331</v>
       </c>
       <c r="F43" s="24"/>
       <c r="G43" s="23">
@@ -9940,29 +10041,32 @@
         <f t="shared" si="0"/>
         <v>8309</v>
       </c>
-      <c r="J43" s="102"/>
-      <c r="K43" s="100"/>
-      <c r="L43" s="98"/>
-      <c r="M43" s="139">
-        <v>0</v>
-      </c>
-      <c r="N43" s="129"/>
+      <c r="J43" s="78"/>
+      <c r="K43" s="78"/>
+      <c r="L43" s="78"/>
+      <c r="M43" s="115">
+        <f>G43</f>
+        <v>2080</v>
+      </c>
+      <c r="N43" s="105" t="s">
+        <v>277</v>
+      </c>
       <c r="O43" s="77">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="P43" s="77">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="R43" s="1"/>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A44" s="105"/>
+      <c r="A44" s="122"/>
       <c r="B44" s="17"/>
       <c r="C44" s="76"/>
       <c r="D44" s="17"/>
-      <c r="E44" s="137" t="s">
-        <v>281</v>
+      <c r="E44" s="113" t="s">
+        <v>278</v>
       </c>
       <c r="F44" s="24"/>
       <c r="G44" s="23">
@@ -9972,15 +10076,15 @@
         <f t="shared" si="0"/>
         <v>7919</v>
       </c>
-      <c r="J44" s="102"/>
-      <c r="K44" s="100"/>
-      <c r="L44" s="98"/>
-      <c r="M44" s="139">
-        <f t="shared" ref="M44:M46" si="5">G44</f>
+      <c r="J44" s="78"/>
+      <c r="K44" s="78"/>
+      <c r="L44" s="78"/>
+      <c r="M44" s="115">
+        <f t="shared" ref="M44:M46" si="4">G44</f>
         <v>390</v>
       </c>
-      <c r="N44" s="129" t="s">
-        <v>304</v>
+      <c r="N44" s="105" t="s">
+        <v>300</v>
       </c>
       <c r="O44" s="77">
         <v>2000</v>
@@ -9992,12 +10096,12 @@
       <c r="R44" s="1"/>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A45" s="105"/>
+      <c r="A45" s="122"/>
       <c r="B45" s="17"/>
       <c r="C45" s="76"/>
       <c r="D45" s="17"/>
-      <c r="E45" s="137" t="s">
-        <v>282</v>
+      <c r="E45" s="113" t="s">
+        <v>279</v>
       </c>
       <c r="F45" s="24"/>
       <c r="G45" s="23">
@@ -10007,15 +10111,15 @@
         <f t="shared" si="0"/>
         <v>7219</v>
       </c>
-      <c r="J45" s="102"/>
-      <c r="K45" s="100"/>
-      <c r="L45" s="98"/>
-      <c r="M45" s="139">
-        <f t="shared" si="5"/>
+      <c r="J45" s="78"/>
+      <c r="K45" s="78"/>
+      <c r="L45" s="78"/>
+      <c r="M45" s="115">
+        <f t="shared" si="4"/>
         <v>700</v>
       </c>
-      <c r="N45" s="129" t="s">
-        <v>298</v>
+      <c r="N45" s="105" t="s">
+        <v>294</v>
       </c>
       <c r="O45" s="77">
         <v>2000</v>
@@ -10027,12 +10131,12 @@
       <c r="R45" s="1"/>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A46" s="105"/>
+      <c r="A46" s="122"/>
       <c r="B46" s="17"/>
       <c r="C46" s="77"/>
       <c r="D46" s="11"/>
-      <c r="E46" s="137" t="s">
-        <v>274</v>
+      <c r="E46" s="113" t="s">
+        <v>271</v>
       </c>
       <c r="F46" s="24"/>
       <c r="G46" s="23">
@@ -10042,15 +10146,15 @@
         <f t="shared" si="0"/>
         <v>6319</v>
       </c>
-      <c r="J46" s="102"/>
-      <c r="K46" s="100"/>
-      <c r="L46" s="98"/>
-      <c r="M46" s="139">
-        <f t="shared" si="5"/>
+      <c r="J46" s="78"/>
+      <c r="K46" s="78"/>
+      <c r="L46" s="78"/>
+      <c r="M46" s="115">
+        <f t="shared" si="4"/>
         <v>900</v>
       </c>
-      <c r="N46" s="129" t="s">
-        <v>298</v>
+      <c r="N46" s="105" t="s">
+        <v>294</v>
       </c>
       <c r="O46" s="77">
         <v>2000</v>
@@ -10062,12 +10166,14 @@
       <c r="R46" s="1"/>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A47" s="105"/>
+      <c r="A47" s="122"/>
       <c r="B47" s="17"/>
       <c r="C47" s="77"/>
-      <c r="D47" s="11"/>
-      <c r="E47" s="118" t="s">
-        <v>283</v>
+      <c r="D47" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E47" s="110" t="s">
+        <v>280</v>
       </c>
       <c r="F47" s="24"/>
       <c r="G47" s="23">
@@ -10077,13 +10183,16 @@
         <f t="shared" si="0"/>
         <v>5589</v>
       </c>
-      <c r="J47" s="102"/>
-      <c r="K47" s="100"/>
-      <c r="L47" s="98"/>
-      <c r="M47" s="139">
-        <v>0</v>
-      </c>
-      <c r="N47" s="129"/>
+      <c r="J47" s="102">
+        <f>G47</f>
+        <v>730</v>
+      </c>
+      <c r="K47" s="78"/>
+      <c r="L47" s="78"/>
+      <c r="M47" s="105">
+        <v>0</v>
+      </c>
+      <c r="N47" s="105"/>
       <c r="O47" s="77">
         <v>0</v>
       </c>
@@ -10094,18 +10203,18 @@
       <c r="R47" s="1"/>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A48" s="105"/>
+      <c r="A48" s="122"/>
       <c r="B48" s="89" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C48" s="90" t="s">
         <v>7</v>
       </c>
       <c r="D48" s="57" t="s">
-        <v>287</v>
-      </c>
-      <c r="E48" s="135" t="s">
-        <v>293</v>
+        <v>283</v>
+      </c>
+      <c r="E48" s="111" t="s">
+        <v>289</v>
       </c>
       <c r="F48" s="91">
         <v>1000</v>
@@ -10117,16 +10226,16 @@
         <f t="shared" si="0"/>
         <v>5869</v>
       </c>
-      <c r="J48" s="126">
+      <c r="J48" s="102">
         <f>G48</f>
         <v>720</v>
       </c>
-      <c r="K48" s="100"/>
-      <c r="L48" s="98"/>
-      <c r="M48" s="139">
-        <v>0</v>
-      </c>
-      <c r="N48" s="129"/>
+      <c r="K48" s="78"/>
+      <c r="L48" s="78"/>
+      <c r="M48" s="105">
+        <v>0</v>
+      </c>
+      <c r="N48" s="105"/>
       <c r="O48" s="77">
         <v>0</v>
       </c>
@@ -10137,28 +10246,28 @@
       <c r="R48" s="1"/>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A49" s="106"/>
+      <c r="A49" s="123"/>
       <c r="B49" s="18"/>
       <c r="C49" s="76"/>
       <c r="D49" s="18"/>
-      <c r="E49" s="118" t="s">
-        <v>284</v>
+      <c r="E49" s="93" t="s">
+        <v>340</v>
       </c>
       <c r="F49" s="24"/>
-      <c r="G49" s="142">
+      <c r="G49" s="118">
         <v>124</v>
       </c>
       <c r="H49" s="47">
         <f t="shared" si="0"/>
         <v>5745</v>
       </c>
-      <c r="J49" s="102"/>
-      <c r="K49" s="100"/>
-      <c r="L49" s="98"/>
-      <c r="M49" s="139">
-        <v>0</v>
-      </c>
-      <c r="N49" s="129"/>
+      <c r="J49" s="78"/>
+      <c r="K49" s="78"/>
+      <c r="L49" s="78"/>
+      <c r="M49" s="105">
+        <v>0</v>
+      </c>
+      <c r="N49" s="105"/>
       <c r="O49" s="77">
         <v>0</v>
       </c>
@@ -10175,8 +10284,8 @@
       <c r="B50" s="18"/>
       <c r="C50" s="76"/>
       <c r="D50" s="18"/>
-      <c r="E50" s="144" t="s">
-        <v>320</v>
+      <c r="E50" s="119" t="s">
+        <v>311</v>
       </c>
       <c r="F50" s="24"/>
       <c r="G50" s="23">
@@ -10186,16 +10295,16 @@
         <f t="shared" si="0"/>
         <v>4745</v>
       </c>
-      <c r="J50" s="102"/>
-      <c r="K50" s="100"/>
-      <c r="L50" s="127">
-        <f>G50</f>
+      <c r="J50" s="78"/>
+      <c r="K50" s="78"/>
+      <c r="L50" s="98">
+        <f t="shared" ref="L50:L51" si="5">G50</f>
         <v>1000</v>
       </c>
-      <c r="M50" s="139">
-        <v>0</v>
-      </c>
-      <c r="N50" s="129"/>
+      <c r="M50" s="105">
+        <v>0</v>
+      </c>
+      <c r="N50" s="105"/>
       <c r="O50" s="77">
         <v>0</v>
       </c>
@@ -10206,14 +10315,14 @@
       <c r="R50" s="1"/>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A51" s="104">
+      <c r="A51" s="121">
         <v>46128</v>
       </c>
       <c r="B51" s="17"/>
       <c r="C51" s="76"/>
       <c r="D51" s="18"/>
-      <c r="E51" s="144" t="s">
-        <v>333</v>
+      <c r="E51" s="119" t="s">
+        <v>317</v>
       </c>
       <c r="F51" s="24"/>
       <c r="G51" s="23">
@@ -10223,16 +10332,16 @@
         <f t="shared" si="0"/>
         <v>4577</v>
       </c>
-      <c r="J51" s="102"/>
-      <c r="K51" s="100"/>
-      <c r="L51" s="127">
-        <f>G51</f>
+      <c r="J51" s="78"/>
+      <c r="K51" s="78"/>
+      <c r="L51" s="98">
+        <f t="shared" si="5"/>
         <v>168</v>
       </c>
-      <c r="M51" s="139">
-        <v>0</v>
-      </c>
-      <c r="N51" s="129"/>
+      <c r="M51" s="105">
+        <v>0</v>
+      </c>
+      <c r="N51" s="105"/>
       <c r="O51" s="77">
         <v>0</v>
       </c>
@@ -10243,12 +10352,12 @@
       <c r="R51" s="1"/>
     </row>
     <row r="52" spans="1:18" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A52" s="105"/>
+      <c r="A52" s="122"/>
       <c r="B52" s="18"/>
       <c r="C52" s="76"/>
       <c r="D52" s="18"/>
-      <c r="E52" s="135" t="s">
-        <v>285</v>
+      <c r="E52" s="111" t="s">
+        <v>281</v>
       </c>
       <c r="F52" s="24"/>
       <c r="G52" s="23">
@@ -10258,16 +10367,16 @@
         <f t="shared" si="0"/>
         <v>2477</v>
       </c>
-      <c r="J52" s="126">
+      <c r="J52" s="102">
         <f>G52</f>
         <v>2100</v>
       </c>
-      <c r="K52" s="100"/>
-      <c r="L52" s="98"/>
-      <c r="M52" s="139">
-        <v>0</v>
-      </c>
-      <c r="N52" s="129"/>
+      <c r="K52" s="78"/>
+      <c r="L52" s="78"/>
+      <c r="M52" s="105">
+        <v>0</v>
+      </c>
+      <c r="N52" s="105"/>
       <c r="O52" s="77">
         <v>0</v>
       </c>
@@ -10278,12 +10387,12 @@
       <c r="R52" s="1"/>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A53" s="105"/>
+      <c r="A53" s="122"/>
       <c r="B53" s="18"/>
       <c r="C53" s="76"/>
       <c r="D53" s="18"/>
-      <c r="E53" s="144" t="s">
-        <v>294</v>
+      <c r="E53" s="119" t="s">
+        <v>290</v>
       </c>
       <c r="F53" s="24"/>
       <c r="G53" s="32">
@@ -10293,16 +10402,16 @@
         <f t="shared" si="0"/>
         <v>2447</v>
       </c>
-      <c r="J53" s="102"/>
-      <c r="K53" s="100"/>
-      <c r="L53" s="127">
+      <c r="J53" s="78"/>
+      <c r="K53" s="78"/>
+      <c r="L53" s="98">
         <f>G53</f>
         <v>30</v>
       </c>
-      <c r="M53" s="139">
-        <v>0</v>
-      </c>
-      <c r="N53" s="129"/>
+      <c r="M53" s="105">
+        <v>0</v>
+      </c>
+      <c r="N53" s="105"/>
       <c r="O53" s="77">
         <v>0</v>
       </c>
@@ -10313,12 +10422,12 @@
       <c r="R53" s="1"/>
     </row>
     <row r="54" spans="1:18" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A54" s="105"/>
+      <c r="A54" s="122"/>
       <c r="B54" s="17"/>
       <c r="C54" s="76"/>
       <c r="D54" s="17"/>
       <c r="E54" s="94" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F54" s="31">
         <v>2802</v>
@@ -10330,13 +10439,13 @@
         <f t="shared" si="0"/>
         <v>5249</v>
       </c>
-      <c r="J54" s="102"/>
-      <c r="K54" s="100"/>
-      <c r="L54" s="98"/>
-      <c r="M54" s="139">
-        <v>0</v>
-      </c>
-      <c r="N54" s="129"/>
+      <c r="J54" s="78"/>
+      <c r="K54" s="78"/>
+      <c r="L54" s="78"/>
+      <c r="M54" s="105">
+        <v>0</v>
+      </c>
+      <c r="N54" s="105"/>
       <c r="O54" s="77">
         <v>0</v>
       </c>
@@ -10347,14 +10456,14 @@
       <c r="R54" s="1"/>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A55" s="104">
+      <c r="A55" s="121">
         <v>46130</v>
       </c>
       <c r="B55" s="18"/>
       <c r="C55" s="76"/>
       <c r="D55" s="18"/>
-      <c r="E55" s="137" t="s">
-        <v>289</v>
+      <c r="E55" s="113" t="s">
+        <v>285</v>
       </c>
       <c r="F55" s="24"/>
       <c r="G55" s="23">
@@ -10364,15 +10473,15 @@
         <f t="shared" si="0"/>
         <v>4049</v>
       </c>
-      <c r="J55" s="102"/>
-      <c r="K55" s="100"/>
-      <c r="L55" s="98"/>
-      <c r="M55" s="139">
+      <c r="J55" s="78"/>
+      <c r="K55" s="78"/>
+      <c r="L55" s="78"/>
+      <c r="M55" s="115">
         <f t="shared" ref="M55:M56" si="6">G55</f>
         <v>1200</v>
       </c>
-      <c r="N55" s="129" t="s">
-        <v>305</v>
+      <c r="N55" s="105" t="s">
+        <v>301</v>
       </c>
       <c r="O55" s="77">
         <v>2000</v>
@@ -10384,12 +10493,12 @@
       <c r="R55" s="1"/>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A56" s="105"/>
+      <c r="A56" s="122"/>
       <c r="B56" s="17"/>
       <c r="C56" s="76"/>
       <c r="D56" s="17"/>
-      <c r="E56" s="137" t="s">
-        <v>290</v>
+      <c r="E56" s="113" t="s">
+        <v>286</v>
       </c>
       <c r="F56" s="24"/>
       <c r="G56" s="23">
@@ -10399,15 +10508,15 @@
         <f t="shared" si="0"/>
         <v>3599</v>
       </c>
-      <c r="J56" s="102"/>
-      <c r="K56" s="100"/>
-      <c r="L56" s="98"/>
-      <c r="M56" s="139">
+      <c r="J56" s="78"/>
+      <c r="K56" s="78"/>
+      <c r="L56" s="78"/>
+      <c r="M56" s="115">
         <f t="shared" si="6"/>
         <v>450</v>
       </c>
-      <c r="N56" s="129" t="s">
-        <v>305</v>
+      <c r="N56" s="105" t="s">
+        <v>301</v>
       </c>
       <c r="O56" s="77">
         <v>2000</v>
@@ -10419,30 +10528,32 @@
       <c r="R56" s="1"/>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A57" s="105"/>
+      <c r="A57" s="122"/>
       <c r="B57" s="18"/>
       <c r="C57" s="76"/>
-      <c r="D57" s="17"/>
-      <c r="E57" s="118" t="s">
-        <v>291</v>
+      <c r="D57" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E57" s="93" t="s">
+        <v>287</v>
       </c>
       <c r="F57" s="24">
         <v>0</v>
       </c>
-      <c r="G57" s="142">
+      <c r="G57" s="120">
         <v>104</v>
       </c>
       <c r="H57" s="47">
         <f t="shared" si="0"/>
         <v>3495</v>
       </c>
-      <c r="J57" s="102"/>
-      <c r="K57" s="100"/>
-      <c r="L57" s="98"/>
-      <c r="M57" s="139">
-        <v>0</v>
-      </c>
-      <c r="N57" s="129"/>
+      <c r="J57" s="78"/>
+      <c r="K57" s="78"/>
+      <c r="L57" s="78"/>
+      <c r="M57" s="105">
+        <v>0</v>
+      </c>
+      <c r="N57" s="105"/>
       <c r="O57" s="77">
         <v>0</v>
       </c>
@@ -10453,12 +10564,12 @@
       <c r="R57" s="1"/>
     </row>
     <row r="58" spans="1:18" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A58" s="105"/>
+      <c r="A58" s="122"/>
       <c r="B58" s="17"/>
       <c r="C58" s="76"/>
       <c r="D58" s="17"/>
-      <c r="E58" s="135" t="s">
-        <v>292</v>
+      <c r="E58" s="111" t="s">
+        <v>288</v>
       </c>
       <c r="F58" s="24">
         <v>0</v>
@@ -10470,16 +10581,16 @@
         <f t="shared" si="0"/>
         <v>1545</v>
       </c>
-      <c r="J58" s="126">
+      <c r="J58" s="102">
         <f>G58</f>
         <v>1950</v>
       </c>
-      <c r="K58" s="100"/>
-      <c r="L58" s="98"/>
-      <c r="M58" s="139">
-        <v>0</v>
-      </c>
-      <c r="N58" s="129"/>
+      <c r="K58" s="78"/>
+      <c r="L58" s="78"/>
+      <c r="M58" s="105">
+        <v>0</v>
+      </c>
+      <c r="N58" s="105"/>
       <c r="O58" s="77">
         <v>0</v>
       </c>
@@ -10490,12 +10601,14 @@
       <c r="R58" s="1"/>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A59" s="84"/>
+      <c r="A59" s="84">
+        <v>46131</v>
+      </c>
       <c r="B59" s="18"/>
       <c r="C59" s="76"/>
       <c r="D59" s="18"/>
-      <c r="E59" s="144" t="s">
-        <v>314</v>
+      <c r="E59" s="119" t="s">
+        <v>309</v>
       </c>
       <c r="F59" s="24"/>
       <c r="G59" s="23">
@@ -10505,16 +10618,16 @@
         <f t="shared" si="0"/>
         <v>1481</v>
       </c>
-      <c r="J59" s="102"/>
-      <c r="K59" s="100"/>
-      <c r="L59" s="127">
+      <c r="J59" s="78"/>
+      <c r="K59" s="78"/>
+      <c r="L59" s="98">
         <f>G59</f>
         <v>64</v>
       </c>
-      <c r="M59" s="139">
-        <v>0</v>
-      </c>
-      <c r="N59" s="129"/>
+      <c r="M59" s="105">
+        <v>0</v>
+      </c>
+      <c r="N59" s="105"/>
       <c r="O59" s="77">
         <v>0</v>
       </c>
@@ -10525,28 +10638,38 @@
       <c r="R59" s="1"/>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A60" s="83"/>
-      <c r="B60" s="18"/>
-      <c r="C60" s="76"/>
-      <c r="D60" s="18"/>
-      <c r="E60" s="94" t="s">
-        <v>295</v>
-      </c>
-      <c r="F60" s="24"/>
+      <c r="A60" s="121">
+        <v>46132</v>
+      </c>
+      <c r="B60" s="25" t="s">
+        <v>261</v>
+      </c>
+      <c r="C60" s="77" t="s">
+        <v>25</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="E60" s="119" t="s">
+        <v>318</v>
+      </c>
+      <c r="F60" s="24">
+        <v>5000</v>
+      </c>
       <c r="G60" s="23">
-        <v>188</v>
+        <v>32</v>
       </c>
       <c r="H60" s="47">
         <f t="shared" si="0"/>
-        <v>1293</v>
-      </c>
-      <c r="J60" s="102"/>
-      <c r="K60" s="100"/>
-      <c r="L60" s="98"/>
-      <c r="M60" s="139">
-        <v>0</v>
-      </c>
-      <c r="N60" s="129"/>
+        <v>6449</v>
+      </c>
+      <c r="J60" s="78"/>
+      <c r="K60" s="78"/>
+      <c r="L60" s="78"/>
+      <c r="M60" s="105">
+        <v>0</v>
+      </c>
+      <c r="N60" s="105"/>
       <c r="O60" s="77">
         <v>0</v>
       </c>
@@ -10557,120 +10680,136 @@
       <c r="R60" s="1"/>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A61" s="84"/>
+      <c r="A61" s="122"/>
       <c r="B61" s="18"/>
       <c r="C61" s="76"/>
       <c r="D61" s="18"/>
-      <c r="E61" s="93"/>
+      <c r="E61" s="113" t="s">
+        <v>347</v>
+      </c>
       <c r="F61" s="24"/>
       <c r="G61" s="23">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="H61" s="47">
         <f t="shared" si="0"/>
-        <v>1293</v>
-      </c>
-      <c r="J61" s="102"/>
-      <c r="K61" s="100"/>
-      <c r="L61" s="98"/>
-      <c r="M61" s="139">
-        <f>E61</f>
-        <v>0</v>
-      </c>
-      <c r="N61" s="129"/>
+        <v>6297</v>
+      </c>
+      <c r="J61" s="78"/>
+      <c r="K61" s="78"/>
+      <c r="L61" s="78"/>
+      <c r="M61" s="115">
+        <f t="shared" ref="M61" si="7">G61</f>
+        <v>152</v>
+      </c>
+      <c r="N61" s="105" t="s">
+        <v>343</v>
+      </c>
       <c r="O61" s="77">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="P61" s="77">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-1848</v>
       </c>
       <c r="R61" s="1"/>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A62" s="83"/>
+      <c r="A62" s="122"/>
       <c r="B62" s="10"/>
       <c r="C62" s="78"/>
       <c r="D62" s="10"/>
-      <c r="E62" s="93"/>
+      <c r="E62" s="113" t="s">
+        <v>345</v>
+      </c>
       <c r="F62" s="24"/>
       <c r="G62" s="23">
-        <v>0</v>
+        <v>447</v>
       </c>
       <c r="H62" s="47">
         <f t="shared" si="0"/>
-        <v>1293</v>
-      </c>
-      <c r="J62" s="102"/>
-      <c r="K62" s="100"/>
-      <c r="L62" s="98"/>
-      <c r="M62" s="139">
-        <f>E62</f>
-        <v>0</v>
-      </c>
-      <c r="N62" s="129"/>
+        <v>5850</v>
+      </c>
+      <c r="J62" s="78"/>
+      <c r="K62" s="78"/>
+      <c r="L62" s="78"/>
+      <c r="M62" s="115">
+        <f t="shared" ref="M62:M67" si="8">G62</f>
+        <v>447</v>
+      </c>
+      <c r="N62" s="105" t="s">
+        <v>344</v>
+      </c>
       <c r="O62" s="77">
         <v>0</v>
       </c>
       <c r="P62" s="77">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>447</v>
       </c>
       <c r="R62" s="1"/>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A63" s="85"/>
+      <c r="A63" s="122"/>
       <c r="B63" s="10"/>
       <c r="C63" s="78"/>
       <c r="D63" s="10"/>
-      <c r="E63" s="92"/>
+      <c r="E63" s="113" t="s">
+        <v>346</v>
+      </c>
       <c r="F63" s="24"/>
       <c r="G63" s="23">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="H63" s="47">
         <f t="shared" si="0"/>
-        <v>1293</v>
-      </c>
-      <c r="J63" s="102"/>
-      <c r="K63" s="100"/>
-      <c r="L63" s="98"/>
-      <c r="M63" s="139">
-        <f>E63</f>
-        <v>0</v>
-      </c>
-      <c r="N63" s="129"/>
+        <v>5776</v>
+      </c>
+      <c r="J63" s="78"/>
+      <c r="K63" s="78"/>
+      <c r="L63" s="78"/>
+      <c r="M63" s="115">
+        <f t="shared" si="8"/>
+        <v>74</v>
+      </c>
+      <c r="N63" s="105"/>
       <c r="O63" s="77">
         <v>0</v>
       </c>
       <c r="P63" s="77">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="R63" s="1"/>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A64" s="84"/>
+      <c r="A64" s="122"/>
       <c r="B64" s="10"/>
       <c r="C64" s="78"/>
       <c r="D64" s="10"/>
-      <c r="E64" s="92"/>
+      <c r="E64" s="94" t="s">
+        <v>341</v>
+      </c>
       <c r="F64" s="24"/>
       <c r="G64" s="23">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="H64" s="47">
         <f t="shared" si="0"/>
-        <v>1293</v>
-      </c>
-      <c r="J64" s="102"/>
-      <c r="K64" s="100"/>
-      <c r="L64" s="98"/>
-      <c r="M64" s="139">
-        <f>E64</f>
-        <v>0</v>
-      </c>
-      <c r="N64" s="129"/>
+        <v>5636</v>
+      </c>
+      <c r="J64" s="78"/>
+      <c r="K64" s="78"/>
+      <c r="L64" s="98">
+        <f>G64</f>
+        <v>140</v>
+      </c>
+      <c r="M64" s="105">
+        <v>0</v>
+      </c>
+      <c r="N64" s="105" t="s">
+        <v>342</v>
+      </c>
       <c r="O64" s="77">
         <v>0</v>
       </c>
@@ -10681,120 +10820,137 @@
       <c r="R64" s="1"/>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A65" s="82"/>
+      <c r="A65" s="122"/>
       <c r="B65" s="10"/>
       <c r="C65" s="78"/>
       <c r="D65" s="10"/>
-      <c r="E65" s="92"/>
+      <c r="E65" s="113" t="s">
+        <v>348</v>
+      </c>
       <c r="F65" s="24"/>
       <c r="G65" s="23">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="H65" s="47">
         <f t="shared" si="0"/>
-        <v>1293</v>
-      </c>
-      <c r="J65" s="102"/>
-      <c r="K65" s="100"/>
-      <c r="L65" s="98"/>
-      <c r="M65" s="139">
-        <f>E65</f>
-        <v>0</v>
-      </c>
-      <c r="N65" s="129"/>
+        <v>5296</v>
+      </c>
+      <c r="J65" s="78"/>
+      <c r="K65" s="78"/>
+      <c r="L65" s="78"/>
+      <c r="M65" s="115">
+        <f t="shared" si="8"/>
+        <v>340</v>
+      </c>
+      <c r="N65" s="105" t="s">
+        <v>294</v>
+      </c>
       <c r="O65" s="77">
         <v>0</v>
       </c>
       <c r="P65" s="77">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="R65" s="1"/>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A66" s="83"/>
+      <c r="A66" s="122"/>
       <c r="B66" s="10"/>
       <c r="C66" s="78"/>
       <c r="D66" s="10"/>
-      <c r="E66" s="92"/>
+      <c r="E66" s="113" t="s">
+        <v>353</v>
+      </c>
       <c r="F66" s="24"/>
       <c r="G66" s="23">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="H66" s="47">
         <f t="shared" si="0"/>
-        <v>1293</v>
-      </c>
-      <c r="J66" s="102"/>
-      <c r="K66" s="100"/>
-      <c r="L66" s="98"/>
-      <c r="M66" s="139">
-        <f>E66</f>
-        <v>0</v>
-      </c>
-      <c r="N66" s="129"/>
+        <v>5139</v>
+      </c>
+      <c r="J66" s="78"/>
+      <c r="K66" s="78"/>
+      <c r="L66" s="78"/>
+      <c r="M66" s="115">
+        <f t="shared" si="8"/>
+        <v>157</v>
+      </c>
+      <c r="N66" s="105" t="s">
+        <v>350</v>
+      </c>
       <c r="O66" s="77">
         <v>0</v>
       </c>
       <c r="P66" s="77">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="R66" s="1"/>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A67" s="85"/>
+      <c r="A67" s="84">
+        <v>46133</v>
+      </c>
       <c r="B67" s="18"/>
       <c r="C67" s="76"/>
       <c r="D67" s="18"/>
-      <c r="E67" s="92"/>
+      <c r="E67" s="113" t="s">
+        <v>349</v>
+      </c>
       <c r="F67" s="24"/>
       <c r="G67" s="23">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="H67" s="47">
         <f t="shared" si="0"/>
-        <v>1293</v>
-      </c>
-      <c r="J67" s="102"/>
-      <c r="K67" s="100"/>
-      <c r="L67" s="98"/>
-      <c r="M67" s="139">
-        <f>E67</f>
-        <v>0</v>
-      </c>
-      <c r="N67" s="129"/>
+        <v>4994</v>
+      </c>
+      <c r="J67" s="78"/>
+      <c r="K67" s="78"/>
+      <c r="L67" s="78"/>
+      <c r="M67" s="115">
+        <f t="shared" si="8"/>
+        <v>145</v>
+      </c>
+      <c r="N67" s="105" t="s">
+        <v>342</v>
+      </c>
       <c r="O67" s="77">
         <v>0</v>
       </c>
       <c r="P67" s="77">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="R67" s="1"/>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:18" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A68" s="84"/>
       <c r="B68" s="18"/>
       <c r="C68" s="76"/>
       <c r="D68" s="18"/>
-      <c r="E68" s="93"/>
-      <c r="F68" s="24"/>
+      <c r="E68" s="143" t="s">
+        <v>352</v>
+      </c>
+      <c r="F68" s="142"/>
       <c r="G68" s="23">
         <v>0</v>
       </c>
       <c r="H68" s="47">
         <f t="shared" si="0"/>
-        <v>1293</v>
-      </c>
-      <c r="J68" s="102"/>
-      <c r="K68" s="100"/>
-      <c r="L68" s="98"/>
-      <c r="M68" s="139">
-        <f>E68</f>
-        <v>0</v>
-      </c>
-      <c r="N68" s="129"/>
+        <v>4994</v>
+      </c>
+      <c r="J68" s="78"/>
+      <c r="K68" s="78"/>
+      <c r="L68" s="78"/>
+      <c r="M68" s="105">
+        <v>0</v>
+      </c>
+      <c r="N68" s="78" t="s">
+        <v>351</v>
+      </c>
       <c r="O68" s="77">
         <v>0</v>
       </c>
@@ -10809,28 +10965,29 @@
       <c r="B69" s="18"/>
       <c r="C69" s="76"/>
       <c r="D69" s="18"/>
-      <c r="E69" s="92"/>
+      <c r="E69" s="94" t="s">
+        <v>291</v>
+      </c>
       <c r="F69" s="24"/>
       <c r="G69" s="23">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="H69" s="47">
         <f t="shared" si="0"/>
-        <v>1293</v>
-      </c>
-      <c r="J69" s="102"/>
-      <c r="K69" s="100"/>
-      <c r="L69" s="98"/>
-      <c r="M69" s="139">
-        <f t="shared" ref="M69:M78" si="7">E69</f>
-        <v>0</v>
-      </c>
-      <c r="N69" s="129"/>
+        <v>4838</v>
+      </c>
+      <c r="J69" s="78"/>
+      <c r="K69" s="78"/>
+      <c r="L69" s="78"/>
+      <c r="M69" s="105">
+        <v>0</v>
+      </c>
+      <c r="N69" s="105"/>
       <c r="O69" s="77">
         <v>0</v>
       </c>
       <c r="P69" s="77">
-        <f t="shared" ref="P69:P112" si="8">+M69-O69</f>
+        <f t="shared" ref="P69:P112" si="9">+M69-O69</f>
         <v>0</v>
       </c>
       <c r="R69" s="1"/>
@@ -10846,22 +11003,22 @@
         <v>0</v>
       </c>
       <c r="H70" s="47">
-        <f t="shared" ref="H70:H112" si="9">H69+F70-G70</f>
-        <v>1293</v>
-      </c>
-      <c r="J70" s="102"/>
-      <c r="K70" s="100"/>
-      <c r="L70" s="98"/>
-      <c r="M70" s="139">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="N70" s="129"/>
+        <f t="shared" ref="H70:H112" si="10">H69+F70-G70</f>
+        <v>4838</v>
+      </c>
+      <c r="J70" s="78"/>
+      <c r="K70" s="78"/>
+      <c r="L70" s="78"/>
+      <c r="M70" s="105">
+        <f t="shared" ref="M66:M72" si="11">E70</f>
+        <v>0</v>
+      </c>
+      <c r="N70" s="105"/>
       <c r="O70" s="77">
         <v>0</v>
       </c>
       <c r="P70" s="77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R70" s="1"/>
@@ -10877,22 +11034,22 @@
         <v>0</v>
       </c>
       <c r="H71" s="47">
+        <f t="shared" si="10"/>
+        <v>4838</v>
+      </c>
+      <c r="J71" s="78"/>
+      <c r="K71" s="78"/>
+      <c r="L71" s="78"/>
+      <c r="M71" s="105">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="N71" s="105"/>
+      <c r="O71" s="77">
+        <v>0</v>
+      </c>
+      <c r="P71" s="77">
         <f t="shared" si="9"/>
-        <v>1293</v>
-      </c>
-      <c r="J71" s="102"/>
-      <c r="K71" s="100"/>
-      <c r="L71" s="98"/>
-      <c r="M71" s="139">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="N71" s="129"/>
-      <c r="O71" s="77">
-        <v>0</v>
-      </c>
-      <c r="P71" s="77">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R71" s="1"/>
@@ -10908,22 +11065,24 @@
         <v>0</v>
       </c>
       <c r="H72" s="47">
+        <f t="shared" si="10"/>
+        <v>4838</v>
+      </c>
+      <c r="J72" s="78"/>
+      <c r="K72" s="78"/>
+      <c r="L72" s="78"/>
+      <c r="M72" s="105">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="N72" s="105" t="s">
+        <v>342</v>
+      </c>
+      <c r="O72" s="77">
+        <v>0</v>
+      </c>
+      <c r="P72" s="77">
         <f t="shared" si="9"/>
-        <v>1293</v>
-      </c>
-      <c r="J72" s="102"/>
-      <c r="K72" s="100"/>
-      <c r="L72" s="98"/>
-      <c r="M72" s="139">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="N72" s="129"/>
-      <c r="O72" s="77">
-        <v>0</v>
-      </c>
-      <c r="P72" s="77">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R72" s="1"/>
@@ -10939,22 +11098,22 @@
         <v>0</v>
       </c>
       <c r="H73" s="47">
+        <f t="shared" si="10"/>
+        <v>4838</v>
+      </c>
+      <c r="J73" s="78"/>
+      <c r="K73" s="78"/>
+      <c r="L73" s="78"/>
+      <c r="M73" s="105">
+        <f t="shared" ref="M73:M78" si="12">E73</f>
+        <v>0</v>
+      </c>
+      <c r="N73" s="105"/>
+      <c r="O73" s="77">
+        <v>0</v>
+      </c>
+      <c r="P73" s="77">
         <f t="shared" si="9"/>
-        <v>1293</v>
-      </c>
-      <c r="J73" s="102"/>
-      <c r="K73" s="100"/>
-      <c r="L73" s="98"/>
-      <c r="M73" s="139">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="N73" s="129"/>
-      <c r="O73" s="77">
-        <v>0</v>
-      </c>
-      <c r="P73" s="77">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R73" s="1"/>
@@ -10970,22 +11129,22 @@
         <v>0</v>
       </c>
       <c r="H74" s="47">
+        <f t="shared" si="10"/>
+        <v>4838</v>
+      </c>
+      <c r="J74" s="78"/>
+      <c r="K74" s="78"/>
+      <c r="L74" s="78"/>
+      <c r="M74" s="105">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="N74" s="105"/>
+      <c r="O74" s="77">
+        <v>0</v>
+      </c>
+      <c r="P74" s="77">
         <f t="shared" si="9"/>
-        <v>1293</v>
-      </c>
-      <c r="J74" s="102"/>
-      <c r="K74" s="100"/>
-      <c r="L74" s="98"/>
-      <c r="M74" s="139">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="N74" s="129"/>
-      <c r="O74" s="77">
-        <v>0</v>
-      </c>
-      <c r="P74" s="77">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R74" s="1"/>
@@ -11001,22 +11160,22 @@
         <v>0</v>
       </c>
       <c r="H75" s="47">
+        <f t="shared" si="10"/>
+        <v>4838</v>
+      </c>
+      <c r="J75" s="78"/>
+      <c r="K75" s="78"/>
+      <c r="L75" s="78"/>
+      <c r="M75" s="105">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="N75" s="105"/>
+      <c r="O75" s="77">
+        <v>0</v>
+      </c>
+      <c r="P75" s="77">
         <f t="shared" si="9"/>
-        <v>1293</v>
-      </c>
-      <c r="J75" s="102"/>
-      <c r="K75" s="100"/>
-      <c r="L75" s="98"/>
-      <c r="M75" s="139">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="N75" s="129"/>
-      <c r="O75" s="77">
-        <v>0</v>
-      </c>
-      <c r="P75" s="77">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R75" s="1"/>
@@ -11032,22 +11191,22 @@
         <v>0</v>
       </c>
       <c r="H76" s="47">
+        <f t="shared" si="10"/>
+        <v>4838</v>
+      </c>
+      <c r="J76" s="78"/>
+      <c r="K76" s="78"/>
+      <c r="L76" s="78"/>
+      <c r="M76" s="105">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="N76" s="105"/>
+      <c r="O76" s="77">
+        <v>0</v>
+      </c>
+      <c r="P76" s="77">
         <f t="shared" si="9"/>
-        <v>1293</v>
-      </c>
-      <c r="J76" s="102"/>
-      <c r="K76" s="100"/>
-      <c r="L76" s="98"/>
-      <c r="M76" s="139">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="N76" s="129"/>
-      <c r="O76" s="77">
-        <v>0</v>
-      </c>
-      <c r="P76" s="77">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R76" s="1"/>
@@ -11063,22 +11222,22 @@
         <v>0</v>
       </c>
       <c r="H77" s="47">
+        <f t="shared" si="10"/>
+        <v>4838</v>
+      </c>
+      <c r="J77" s="78"/>
+      <c r="K77" s="78"/>
+      <c r="L77" s="78"/>
+      <c r="M77" s="105">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="N77" s="105"/>
+      <c r="O77" s="77">
+        <v>0</v>
+      </c>
+      <c r="P77" s="77">
         <f t="shared" si="9"/>
-        <v>1293</v>
-      </c>
-      <c r="J77" s="102"/>
-      <c r="K77" s="100"/>
-      <c r="L77" s="98"/>
-      <c r="M77" s="139">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="N77" s="129"/>
-      <c r="O77" s="77">
-        <v>0</v>
-      </c>
-      <c r="P77" s="77">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R77" s="1"/>
@@ -11094,25 +11253,25 @@
         <v>0</v>
       </c>
       <c r="H78" s="55">
+        <f t="shared" si="10"/>
+        <v>4838</v>
+      </c>
+      <c r="I78" s="124" t="s">
+        <v>9</v>
+      </c>
+      <c r="J78" s="78"/>
+      <c r="K78" s="78"/>
+      <c r="L78" s="78"/>
+      <c r="M78" s="105">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="N78" s="105"/>
+      <c r="O78" s="77">
+        <v>0</v>
+      </c>
+      <c r="P78" s="77">
         <f t="shared" si="9"/>
-        <v>1293</v>
-      </c>
-      <c r="I78" s="107" t="s">
-        <v>9</v>
-      </c>
-      <c r="J78" s="102"/>
-      <c r="K78" s="100"/>
-      <c r="L78" s="98"/>
-      <c r="M78" s="139">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="N78" s="129"/>
-      <c r="O78" s="77">
-        <v>0</v>
-      </c>
-      <c r="P78" s="77">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R78" s="1"/>
@@ -11128,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="H79" s="60">
-        <f t="shared" si="9"/>
-        <v>1293</v>
-      </c>
-      <c r="I79" s="117"/>
+        <f t="shared" si="10"/>
+        <v>4838</v>
+      </c>
+      <c r="I79" s="134"/>
       <c r="J79" s="96"/>
       <c r="K79" s="96"/>
       <c r="L79" s="96"/>
@@ -11143,7 +11302,7 @@
         <v>0</v>
       </c>
       <c r="P79" s="77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R79" s="1"/>
@@ -11159,8 +11318,8 @@
         <v>0</v>
       </c>
       <c r="H80" s="24">
-        <f t="shared" si="9"/>
-        <v>1293</v>
+        <f t="shared" si="10"/>
+        <v>4838</v>
       </c>
       <c r="J80" s="92"/>
       <c r="K80" s="92"/>
@@ -11173,7 +11332,7 @@
         <v>0</v>
       </c>
       <c r="P80" s="77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R80" s="1"/>
@@ -11189,8 +11348,8 @@
         <v>0</v>
       </c>
       <c r="H81" s="24">
-        <f t="shared" si="9"/>
-        <v>1293</v>
+        <f t="shared" si="10"/>
+        <v>4838</v>
       </c>
       <c r="J81" s="92"/>
       <c r="K81" s="92"/>
@@ -11203,7 +11362,7 @@
         <v>0</v>
       </c>
       <c r="P81" s="77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R81" s="1"/>
@@ -11219,8 +11378,8 @@
         <v>0</v>
       </c>
       <c r="H82" s="24">
-        <f t="shared" si="9"/>
-        <v>1293</v>
+        <f t="shared" si="10"/>
+        <v>4838</v>
       </c>
       <c r="J82" s="92"/>
       <c r="K82" s="92"/>
@@ -11233,7 +11392,7 @@
         <v>0</v>
       </c>
       <c r="P82" s="77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R82" s="1"/>
@@ -11249,8 +11408,8 @@
         <v>0</v>
       </c>
       <c r="H83" s="24">
-        <f t="shared" si="9"/>
-        <v>1293</v>
+        <f t="shared" si="10"/>
+        <v>4838</v>
       </c>
       <c r="J83" s="92"/>
       <c r="K83" s="92"/>
@@ -11263,7 +11422,7 @@
         <v>0</v>
       </c>
       <c r="P83" s="77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R83" s="1"/>
@@ -11279,8 +11438,8 @@
         <v>0</v>
       </c>
       <c r="H84" s="24">
-        <f t="shared" si="9"/>
-        <v>1293</v>
+        <f t="shared" si="10"/>
+        <v>4838</v>
       </c>
       <c r="J84" s="92"/>
       <c r="K84" s="92"/>
@@ -11293,7 +11452,7 @@
         <v>0</v>
       </c>
       <c r="P84" s="77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R84" s="1"/>
@@ -11309,8 +11468,8 @@
         <v>0</v>
       </c>
       <c r="H85" s="24">
-        <f t="shared" si="9"/>
-        <v>1293</v>
+        <f t="shared" si="10"/>
+        <v>4838</v>
       </c>
       <c r="J85" s="92"/>
       <c r="K85" s="92"/>
@@ -11323,7 +11482,7 @@
         <v>0</v>
       </c>
       <c r="P85" s="77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R85" s="1"/>
@@ -11339,8 +11498,8 @@
         <v>0</v>
       </c>
       <c r="H86" s="24">
-        <f t="shared" si="9"/>
-        <v>1293</v>
+        <f t="shared" si="10"/>
+        <v>4838</v>
       </c>
       <c r="J86" s="92"/>
       <c r="K86" s="92"/>
@@ -11353,7 +11512,7 @@
         <v>0</v>
       </c>
       <c r="P86" s="77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R86" s="1"/>
@@ -11369,8 +11528,8 @@
         <v>0</v>
       </c>
       <c r="H87" s="24">
-        <f t="shared" si="9"/>
-        <v>1293</v>
+        <f t="shared" si="10"/>
+        <v>4838</v>
       </c>
       <c r="J87" s="92"/>
       <c r="K87" s="92"/>
@@ -11383,7 +11542,7 @@
         <v>0</v>
       </c>
       <c r="P87" s="77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R87" s="1"/>
@@ -11399,8 +11558,8 @@
         <v>0</v>
       </c>
       <c r="H88" s="24">
-        <f t="shared" si="9"/>
-        <v>1293</v>
+        <f t="shared" si="10"/>
+        <v>4838</v>
       </c>
       <c r="J88" s="92"/>
       <c r="K88" s="92"/>
@@ -11413,7 +11572,7 @@
         <v>0</v>
       </c>
       <c r="P88" s="77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R88" s="1"/>
@@ -11429,8 +11588,8 @@
         <v>0</v>
       </c>
       <c r="H89" s="24">
-        <f t="shared" si="9"/>
-        <v>1293</v>
+        <f t="shared" si="10"/>
+        <v>4838</v>
       </c>
       <c r="J89" s="92"/>
       <c r="K89" s="92"/>
@@ -11443,7 +11602,7 @@
         <v>0</v>
       </c>
       <c r="P89" s="77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R89" s="1"/>
@@ -11459,8 +11618,8 @@
         <v>0</v>
       </c>
       <c r="H90" s="24">
-        <f t="shared" si="9"/>
-        <v>1293</v>
+        <f t="shared" si="10"/>
+        <v>4838</v>
       </c>
       <c r="J90" s="92"/>
       <c r="K90" s="92"/>
@@ -11473,7 +11632,7 @@
         <v>0</v>
       </c>
       <c r="P90" s="77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R90" s="1"/>
@@ -11487,8 +11646,8 @@
       <c r="F91" s="24"/>
       <c r="G91" s="23"/>
       <c r="H91" s="24">
-        <f t="shared" si="9"/>
-        <v>1293</v>
+        <f t="shared" si="10"/>
+        <v>4838</v>
       </c>
       <c r="J91" s="92"/>
       <c r="K91" s="92"/>
@@ -11501,7 +11660,7 @@
         <v>0</v>
       </c>
       <c r="P91" s="77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R91" s="1"/>
@@ -11515,8 +11674,8 @@
       <c r="F92" s="24"/>
       <c r="G92" s="23"/>
       <c r="H92" s="24">
-        <f t="shared" si="9"/>
-        <v>1293</v>
+        <f t="shared" si="10"/>
+        <v>4838</v>
       </c>
       <c r="J92" s="92"/>
       <c r="K92" s="92"/>
@@ -11529,7 +11688,7 @@
         <v>0</v>
       </c>
       <c r="P92" s="77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R92" s="1"/>
@@ -11543,8 +11702,8 @@
       <c r="F93" s="24"/>
       <c r="G93" s="23"/>
       <c r="H93" s="24">
-        <f t="shared" si="9"/>
-        <v>1293</v>
+        <f t="shared" si="10"/>
+        <v>4838</v>
       </c>
       <c r="J93" s="92"/>
       <c r="K93" s="92"/>
@@ -11557,7 +11716,7 @@
         <v>0</v>
       </c>
       <c r="P93" s="77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R93" s="1"/>
@@ -11571,8 +11730,8 @@
       <c r="F94" s="24"/>
       <c r="G94" s="23"/>
       <c r="H94" s="24">
-        <f t="shared" si="9"/>
-        <v>1293</v>
+        <f t="shared" si="10"/>
+        <v>4838</v>
       </c>
       <c r="J94" s="92"/>
       <c r="K94" s="92"/>
@@ -11585,7 +11744,7 @@
         <v>0</v>
       </c>
       <c r="P94" s="77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R94" s="1"/>
@@ -11599,8 +11758,8 @@
       <c r="F95" s="24"/>
       <c r="G95" s="23"/>
       <c r="H95" s="24">
-        <f t="shared" si="9"/>
-        <v>1293</v>
+        <f t="shared" si="10"/>
+        <v>4838</v>
       </c>
       <c r="J95" s="92"/>
       <c r="K95" s="92"/>
@@ -11613,7 +11772,7 @@
         <v>0</v>
       </c>
       <c r="P95" s="77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R95" s="1"/>
@@ -11627,8 +11786,8 @@
       <c r="F96" s="24"/>
       <c r="G96" s="23"/>
       <c r="H96" s="24">
-        <f t="shared" si="9"/>
-        <v>1293</v>
+        <f t="shared" si="10"/>
+        <v>4838</v>
       </c>
       <c r="J96" s="92"/>
       <c r="K96" s="92"/>
@@ -11641,7 +11800,7 @@
         <v>0</v>
       </c>
       <c r="P96" s="77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R96" s="1"/>
@@ -11655,8 +11814,8 @@
       <c r="F97" s="24"/>
       <c r="G97" s="23"/>
       <c r="H97" s="24">
-        <f t="shared" si="9"/>
-        <v>1293</v>
+        <f t="shared" si="10"/>
+        <v>4838</v>
       </c>
       <c r="J97" s="92"/>
       <c r="K97" s="92"/>
@@ -11669,7 +11828,7 @@
         <v>0</v>
       </c>
       <c r="P97" s="77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R97" s="1"/>
@@ -11683,8 +11842,8 @@
       <c r="F98" s="24"/>
       <c r="G98" s="23"/>
       <c r="H98" s="24">
-        <f t="shared" si="9"/>
-        <v>1293</v>
+        <f t="shared" si="10"/>
+        <v>4838</v>
       </c>
       <c r="J98" s="92"/>
       <c r="K98" s="92"/>
@@ -11697,7 +11856,7 @@
         <v>0</v>
       </c>
       <c r="P98" s="77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R98" s="1"/>
@@ -11711,8 +11870,8 @@
       <c r="F99" s="24"/>
       <c r="G99" s="23"/>
       <c r="H99" s="24">
-        <f t="shared" si="9"/>
-        <v>1293</v>
+        <f t="shared" si="10"/>
+        <v>4838</v>
       </c>
       <c r="J99" s="92"/>
       <c r="K99" s="92"/>
@@ -11725,7 +11884,7 @@
         <v>0</v>
       </c>
       <c r="P99" s="77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R99" s="1"/>
@@ -11739,8 +11898,8 @@
       <c r="F100" s="24"/>
       <c r="G100" s="23"/>
       <c r="H100" s="24">
-        <f t="shared" si="9"/>
-        <v>1293</v>
+        <f t="shared" si="10"/>
+        <v>4838</v>
       </c>
       <c r="J100" s="92"/>
       <c r="K100" s="92"/>
@@ -11753,7 +11912,7 @@
         <v>0</v>
       </c>
       <c r="P100" s="77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R100" s="1"/>
@@ -11767,8 +11926,8 @@
       <c r="F101" s="24"/>
       <c r="G101" s="23"/>
       <c r="H101" s="24">
-        <f t="shared" si="9"/>
-        <v>1293</v>
+        <f t="shared" si="10"/>
+        <v>4838</v>
       </c>
       <c r="J101" s="92"/>
       <c r="K101" s="92"/>
@@ -11781,7 +11940,7 @@
         <v>0</v>
       </c>
       <c r="P101" s="77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R101" s="1"/>
@@ -11795,8 +11954,8 @@
       <c r="F102" s="24"/>
       <c r="G102" s="23"/>
       <c r="H102" s="24">
-        <f t="shared" si="9"/>
-        <v>1293</v>
+        <f t="shared" si="10"/>
+        <v>4838</v>
       </c>
       <c r="J102" s="92"/>
       <c r="K102" s="92"/>
@@ -11809,7 +11968,7 @@
         <v>0</v>
       </c>
       <c r="P102" s="77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R102" s="1"/>
@@ -11823,8 +11982,8 @@
       <c r="F103" s="24"/>
       <c r="G103" s="23"/>
       <c r="H103" s="24">
-        <f t="shared" si="9"/>
-        <v>1293</v>
+        <f t="shared" si="10"/>
+        <v>4838</v>
       </c>
       <c r="J103" s="92"/>
       <c r="K103" s="92"/>
@@ -11837,7 +11996,7 @@
         <v>0</v>
       </c>
       <c r="P103" s="77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R103" s="1"/>
@@ -11851,8 +12010,8 @@
       <c r="F104" s="24"/>
       <c r="G104" s="23"/>
       <c r="H104" s="24">
-        <f t="shared" si="9"/>
-        <v>1293</v>
+        <f t="shared" si="10"/>
+        <v>4838</v>
       </c>
       <c r="J104" s="92"/>
       <c r="K104" s="92"/>
@@ -11865,7 +12024,7 @@
         <v>0</v>
       </c>
       <c r="P104" s="77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R104" s="1"/>
@@ -11879,8 +12038,8 @@
       <c r="F105" s="24"/>
       <c r="G105" s="23"/>
       <c r="H105" s="24">
-        <f t="shared" si="9"/>
-        <v>1293</v>
+        <f t="shared" si="10"/>
+        <v>4838</v>
       </c>
       <c r="J105" s="92"/>
       <c r="K105" s="92"/>
@@ -11893,7 +12052,7 @@
         <v>0</v>
       </c>
       <c r="P105" s="77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R105" s="1"/>
@@ -11907,8 +12066,8 @@
       <c r="F106" s="24"/>
       <c r="G106" s="23"/>
       <c r="H106" s="24">
-        <f t="shared" si="9"/>
-        <v>1293</v>
+        <f t="shared" si="10"/>
+        <v>4838</v>
       </c>
       <c r="J106" s="92"/>
       <c r="K106" s="92"/>
@@ -11921,7 +12080,7 @@
         <v>0</v>
       </c>
       <c r="P106" s="77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R106" s="1"/>
@@ -11935,8 +12094,8 @@
       <c r="F107" s="24"/>
       <c r="G107" s="23"/>
       <c r="H107" s="24">
-        <f t="shared" si="9"/>
-        <v>1293</v>
+        <f t="shared" si="10"/>
+        <v>4838</v>
       </c>
       <c r="J107" s="92"/>
       <c r="K107" s="92"/>
@@ -11949,7 +12108,7 @@
         <v>0</v>
       </c>
       <c r="P107" s="77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R107" s="1"/>
@@ -11963,8 +12122,8 @@
       <c r="F108" s="24"/>
       <c r="G108" s="23"/>
       <c r="H108" s="24">
-        <f t="shared" si="9"/>
-        <v>1293</v>
+        <f t="shared" si="10"/>
+        <v>4838</v>
       </c>
       <c r="J108" s="92"/>
       <c r="K108" s="92"/>
@@ -11977,7 +12136,7 @@
         <v>0</v>
       </c>
       <c r="P108" s="77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R108" s="1"/>
@@ -11991,8 +12150,8 @@
       <c r="F109" s="24"/>
       <c r="G109" s="23"/>
       <c r="H109" s="24">
-        <f t="shared" si="9"/>
-        <v>1293</v>
+        <f t="shared" si="10"/>
+        <v>4838</v>
       </c>
       <c r="J109" s="92"/>
       <c r="K109" s="92"/>
@@ -12005,7 +12164,7 @@
         <v>0</v>
       </c>
       <c r="P109" s="77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R109" s="1"/>
@@ -12019,8 +12178,8 @@
       <c r="F110" s="24"/>
       <c r="G110" s="23"/>
       <c r="H110" s="24">
-        <f t="shared" si="9"/>
-        <v>1293</v>
+        <f t="shared" si="10"/>
+        <v>4838</v>
       </c>
       <c r="J110" s="92"/>
       <c r="K110" s="92"/>
@@ -12033,7 +12192,7 @@
         <v>0</v>
       </c>
       <c r="P110" s="77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R110" s="1"/>
@@ -12047,8 +12206,8 @@
       <c r="F111" s="24"/>
       <c r="G111" s="23"/>
       <c r="H111" s="24">
-        <f t="shared" si="9"/>
-        <v>1293</v>
+        <f t="shared" si="10"/>
+        <v>4838</v>
       </c>
       <c r="J111" s="92"/>
       <c r="K111" s="92"/>
@@ -12061,7 +12220,7 @@
         <v>0</v>
       </c>
       <c r="P111" s="77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R111" s="1"/>
@@ -12075,8 +12234,8 @@
       <c r="F112" s="24"/>
       <c r="G112" s="23"/>
       <c r="H112" s="24">
-        <f t="shared" si="9"/>
-        <v>1293</v>
+        <f t="shared" si="10"/>
+        <v>4838</v>
       </c>
       <c r="J112" s="92"/>
       <c r="K112" s="92"/>
@@ -12089,7 +12248,7 @@
         <v>0</v>
       </c>
       <c r="P112" s="77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R112" s="1"/>
@@ -12098,9 +12257,7 @@
       <c r="R113" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A2:A3"/>
+  <mergeCells count="20">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="J1:Q1"/>
     <mergeCell ref="I78:I79"/>
@@ -12115,13 +12272,16 @@
     <mergeCell ref="A42:A49"/>
     <mergeCell ref="A51:A54"/>
     <mergeCell ref="A55:A58"/>
+    <mergeCell ref="A60:A66"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="C2:C3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A2:A3"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="58" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="35" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="8" max="77" man="1"/>
   </colBreaks>

--- a/Site Cash Details/Englabs Site Cash.xlsx
+++ b/Site Cash Details/Englabs Site Cash.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B9DF200-438F-42E2-98B3-A3348C1B876C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD67A8DC-718D-4E47-9B92-EF40A1374971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14,8 +14,8 @@
     <sheet name="April_2026" sheetId="17" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">April_2026!$C$2:$P$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">April_2026!$A$1:$Q$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">April_2026!$N$1:$N$113</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">April_2026!$A$1:$Q$89</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">FEB_2026!$A$1:$H$78</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">JAN_2026!$A$1:$H$111</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">MARCH_2026!$A$1:$H$91</definedName>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="376">
   <si>
     <t>Cr.</t>
   </si>
@@ -1142,13 +1142,79 @@
     <t>C4851</t>
   </si>
   <si>
-    <t>Drone Survey</t>
-  </si>
-  <si>
     <t>Porter From Ambala to Englabs by Indrive (Drone Survey Invoice)</t>
   </si>
   <si>
     <t>Porter From Industrial area phase to Englabs C4851</t>
+  </si>
+  <si>
+    <t>DONE</t>
+  </si>
+  <si>
+    <t>Porter FromChannai Airport to Henkel C5008</t>
+  </si>
+  <si>
+    <t>Porter From Englabs to Menthosa C5133</t>
+  </si>
+  <si>
+    <t>C5133</t>
+  </si>
+  <si>
+    <t>C5144</t>
+  </si>
+  <si>
+    <t>Porter From Noida to gurugram C5144</t>
+  </si>
+  <si>
+    <t>Porter From Excel Faridabad C5138</t>
+  </si>
+  <si>
+    <t>C5138</t>
+  </si>
+  <si>
+    <t>Zepto UPI</t>
+  </si>
+  <si>
+    <t>Porter From Faridabad to HC Robotics C5138</t>
+  </si>
+  <si>
+    <t>Porter From Cadqua to Orient C…........</t>
+  </si>
+  <si>
+    <t>Porter From Cadqua to Henjel C5154</t>
+  </si>
+  <si>
+    <t>C5154</t>
+  </si>
+  <si>
+    <t>Porter From Englabs to Aebocode C4922</t>
+  </si>
+  <si>
+    <t>C4922</t>
+  </si>
+  <si>
+    <t>Porter From Delhi to Chandigarh C4922 &amp; 4967</t>
+  </si>
+  <si>
+    <t>C4922 &amp;4967</t>
+  </si>
+  <si>
+    <t>Saha Drone Survey</t>
+  </si>
+  <si>
+    <t>Labat Asia Vist Shubham ,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zepto Wallet </t>
+  </si>
+  <si>
+    <t>as per New Projects Visit</t>
+  </si>
+  <si>
+    <t>Purchased to Handtowel For Washrrom 2nos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kabadi </t>
   </si>
 </sst>
 </file>
@@ -1720,7 +1786,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="144">
+  <cellXfs count="140">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1944,16 +2010,7 @@
     <xf numFmtId="168" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="168" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1979,9 +2036,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2054,6 +2108,15 @@
     <xf numFmtId="167" fontId="4" fillId="13" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="168" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2063,8 +2126,11 @@
     <xf numFmtId="168" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2075,11 +2141,11 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2090,10 +2156,7 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="7" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2113,15 +2176,6 @@
     </xf>
     <xf numFmtId="165" fontId="4" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="7" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2538,7 +2592,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="121">
+      <c r="A6" s="120">
         <v>46024</v>
       </c>
       <c r="B6" s="17"/>
@@ -2557,7 +2611,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="123"/>
+      <c r="A7" s="122"/>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
@@ -2574,7 +2628,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="121">
+      <c r="A8" s="120">
         <v>46025</v>
       </c>
       <c r="B8" s="17"/>
@@ -2593,7 +2647,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="123"/>
+      <c r="A9" s="122"/>
       <c r="B9" s="17"/>
       <c r="C9" s="17"/>
       <c r="D9" s="17"/>
@@ -2637,7 +2691,7 @@
       </c>
     </row>
     <row r="11" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="121">
+      <c r="A11" s="120">
         <v>46028</v>
       </c>
       <c r="B11" s="17"/>
@@ -2658,7 +2712,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="123"/>
+      <c r="A12" s="122"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
       <c r="D12" s="17"/>
@@ -2675,7 +2729,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="121">
+      <c r="A13" s="120">
         <v>46029</v>
       </c>
       <c r="B13" s="18" t="s">
@@ -2702,7 +2756,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="122"/>
+      <c r="A14" s="121"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17"/>
       <c r="D14" s="17"/>
@@ -2719,7 +2773,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="123"/>
+      <c r="A15" s="122"/>
       <c r="B15" s="17"/>
       <c r="C15" s="17"/>
       <c r="D15" s="17"/>
@@ -2736,7 +2790,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="121">
+      <c r="A16" s="120">
         <v>46030</v>
       </c>
       <c r="B16" s="17"/>
@@ -2755,7 +2809,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="122"/>
+      <c r="A17" s="121"/>
       <c r="B17" s="17"/>
       <c r="C17" s="17"/>
       <c r="D17" s="17"/>
@@ -2772,7 +2826,7 @@
       </c>
     </row>
     <row r="18" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="122"/>
+      <c r="A18" s="121"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17"/>
       <c r="D18" s="17"/>
@@ -2789,7 +2843,7 @@
       </c>
     </row>
     <row r="19" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="122"/>
+      <c r="A19" s="121"/>
       <c r="B19" s="17"/>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
@@ -2806,7 +2860,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="122"/>
+      <c r="A20" s="121"/>
       <c r="B20" s="17"/>
       <c r="C20" s="17"/>
       <c r="D20" s="17"/>
@@ -2823,7 +2877,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="122"/>
+      <c r="A21" s="121"/>
       <c r="B21" s="17"/>
       <c r="C21" s="17"/>
       <c r="D21" s="17"/>
@@ -2840,7 +2894,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="123"/>
+      <c r="A22" s="122"/>
       <c r="B22" s="17"/>
       <c r="C22" s="17"/>
       <c r="D22" s="17"/>
@@ -2857,7 +2911,7 @@
       </c>
     </row>
     <row r="23" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="121">
+      <c r="A23" s="120">
         <v>46031</v>
       </c>
       <c r="B23" s="17"/>
@@ -2878,7 +2932,7 @@
       </c>
     </row>
     <row r="24" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="122"/>
+      <c r="A24" s="121"/>
       <c r="B24" s="18" t="s">
         <v>59</v>
       </c>
@@ -2903,7 +2957,7 @@
       </c>
     </row>
     <row r="25" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="123"/>
+      <c r="A25" s="122"/>
       <c r="B25" s="17"/>
       <c r="C25" s="17"/>
       <c r="D25" s="17"/>
@@ -2920,7 +2974,7 @@
       </c>
     </row>
     <row r="26" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="121">
+      <c r="A26" s="120">
         <v>46032</v>
       </c>
       <c r="B26" s="17"/>
@@ -2939,7 +2993,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="123"/>
+      <c r="A27" s="122"/>
       <c r="B27" s="17"/>
       <c r="C27" s="17"/>
       <c r="D27" s="17"/>
@@ -2975,7 +3029,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="121">
+      <c r="A29" s="120">
         <v>46035</v>
       </c>
       <c r="B29" s="17"/>
@@ -2994,7 +3048,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="122"/>
+      <c r="A30" s="121"/>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
@@ -3011,7 +3065,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="122"/>
+      <c r="A31" s="121"/>
       <c r="B31" s="18" t="s">
         <v>59</v>
       </c>
@@ -3036,7 +3090,7 @@
       </c>
     </row>
     <row r="32" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="122"/>
+      <c r="A32" s="121"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
@@ -3053,7 +3107,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="122"/>
+      <c r="A33" s="121"/>
       <c r="B33" s="17"/>
       <c r="C33" s="17"/>
       <c r="D33" s="17"/>
@@ -3070,7 +3124,7 @@
       </c>
     </row>
     <row r="34" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="122"/>
+      <c r="A34" s="121"/>
       <c r="B34" s="17"/>
       <c r="C34" s="17"/>
       <c r="D34" s="17"/>
@@ -3087,7 +3141,7 @@
       </c>
     </row>
     <row r="35" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="122"/>
+      <c r="A35" s="121"/>
       <c r="B35" s="17"/>
       <c r="C35" s="17"/>
       <c r="D35" s="17"/>
@@ -3104,7 +3158,7 @@
       </c>
     </row>
     <row r="36" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="122"/>
+      <c r="A36" s="121"/>
       <c r="B36" s="17"/>
       <c r="C36" s="17"/>
       <c r="D36" s="17"/>
@@ -3121,7 +3175,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="122"/>
+      <c r="A37" s="121"/>
       <c r="B37" s="17"/>
       <c r="C37" s="17"/>
       <c r="D37" s="17"/>
@@ -3138,7 +3192,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="122"/>
+      <c r="A38" s="121"/>
       <c r="B38" s="17"/>
       <c r="C38" s="17"/>
       <c r="D38" s="17"/>
@@ -3155,7 +3209,7 @@
       </c>
     </row>
     <row r="39" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="121">
+      <c r="A39" s="120">
         <v>46036</v>
       </c>
       <c r="B39" s="17"/>
@@ -3174,7 +3228,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" s="122"/>
+      <c r="A40" s="121"/>
       <c r="B40" s="25"/>
       <c r="C40" s="11"/>
       <c r="D40" s="11"/>
@@ -3191,7 +3245,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" s="122"/>
+      <c r="A41" s="121"/>
       <c r="B41" s="18"/>
       <c r="C41" s="17"/>
       <c r="D41" s="17"/>
@@ -3210,7 +3264,7 @@
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A42" s="122"/>
+      <c r="A42" s="121"/>
       <c r="B42" s="25"/>
       <c r="C42" s="11"/>
       <c r="D42" s="11"/>
@@ -3227,7 +3281,7 @@
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" s="122"/>
+      <c r="A43" s="121"/>
       <c r="B43" s="25"/>
       <c r="C43" s="11"/>
       <c r="D43" s="11"/>
@@ -3244,7 +3298,7 @@
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A44" s="122"/>
+      <c r="A44" s="121"/>
       <c r="B44" s="25"/>
       <c r="C44" s="11"/>
       <c r="D44" s="11"/>
@@ -3263,7 +3317,7 @@
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A45" s="122"/>
+      <c r="A45" s="121"/>
       <c r="B45" s="18"/>
       <c r="C45" s="18"/>
       <c r="D45" s="18"/>
@@ -3280,7 +3334,7 @@
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A46" s="122"/>
+      <c r="A46" s="121"/>
       <c r="B46" s="17"/>
       <c r="C46" s="11"/>
       <c r="D46" s="11"/>
@@ -3299,7 +3353,7 @@
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A47" s="123"/>
+      <c r="A47" s="122"/>
       <c r="B47" s="17"/>
       <c r="C47" s="11"/>
       <c r="D47" s="11"/>
@@ -3318,7 +3372,7 @@
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A48" s="121">
+      <c r="A48" s="120">
         <v>46037</v>
       </c>
       <c r="B48" s="18"/>
@@ -3339,7 +3393,7 @@
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A49" s="122"/>
+      <c r="A49" s="121"/>
       <c r="B49" s="18"/>
       <c r="C49" s="18"/>
       <c r="D49" s="18"/>
@@ -3358,7 +3412,7 @@
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A50" s="122"/>
+      <c r="A50" s="121"/>
       <c r="B50" s="17"/>
       <c r="C50" s="18"/>
       <c r="D50" s="18"/>
@@ -3377,7 +3431,7 @@
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A51" s="123"/>
+      <c r="A51" s="122"/>
       <c r="B51" s="18"/>
       <c r="C51" s="18"/>
       <c r="D51" s="18"/>
@@ -3394,7 +3448,7 @@
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A52" s="121">
+      <c r="A52" s="120">
         <v>46038</v>
       </c>
       <c r="B52" s="18" t="s">
@@ -3421,7 +3475,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A53" s="122"/>
+      <c r="A53" s="121"/>
       <c r="B53" s="18"/>
       <c r="C53" s="18"/>
       <c r="D53" s="18"/>
@@ -3438,7 +3492,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A54" s="123"/>
+      <c r="A54" s="122"/>
       <c r="B54" s="18"/>
       <c r="C54" s="18"/>
       <c r="D54" s="18"/>
@@ -3476,7 +3530,7 @@
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A56" s="121">
+      <c r="A56" s="120">
         <v>46040</v>
       </c>
       <c r="B56" s="18"/>
@@ -3495,7 +3549,7 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A57" s="123"/>
+      <c r="A57" s="122"/>
       <c r="B57" s="18"/>
       <c r="C57" s="18"/>
       <c r="D57" s="18"/>
@@ -3531,7 +3585,7 @@
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A59" s="121">
+      <c r="A59" s="120">
         <v>46042</v>
       </c>
       <c r="B59" s="18"/>
@@ -3552,7 +3606,7 @@
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A60" s="122"/>
+      <c r="A60" s="121"/>
       <c r="B60" s="18"/>
       <c r="C60" s="18"/>
       <c r="D60" s="18"/>
@@ -3571,7 +3625,7 @@
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A61" s="122"/>
+      <c r="A61" s="121"/>
       <c r="B61" s="10"/>
       <c r="C61" s="10"/>
       <c r="D61" s="10"/>
@@ -3590,7 +3644,7 @@
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A62" s="122"/>
+      <c r="A62" s="121"/>
       <c r="B62" s="10"/>
       <c r="C62" s="10"/>
       <c r="D62" s="10"/>
@@ -3609,7 +3663,7 @@
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A63" s="122"/>
+      <c r="A63" s="121"/>
       <c r="B63" s="10"/>
       <c r="C63" s="10"/>
       <c r="D63" s="10"/>
@@ -3626,7 +3680,7 @@
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A64" s="122"/>
+      <c r="A64" s="121"/>
       <c r="B64" s="10" t="s">
         <v>72</v>
       </c>
@@ -3651,7 +3705,7 @@
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A65" s="122"/>
+      <c r="A65" s="121"/>
       <c r="B65" s="10"/>
       <c r="C65" s="10"/>
       <c r="D65" s="10"/>
@@ -3668,7 +3722,7 @@
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A66" s="123"/>
+      <c r="A66" s="122"/>
       <c r="B66" s="18"/>
       <c r="C66" s="18"/>
       <c r="D66" s="18"/>
@@ -3687,7 +3741,7 @@
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A67" s="121">
+      <c r="A67" s="120">
         <v>46043</v>
       </c>
       <c r="B67" s="18" t="s">
@@ -3714,7 +3768,7 @@
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A68" s="122"/>
+      <c r="A68" s="121"/>
       <c r="B68" s="18"/>
       <c r="C68" s="18"/>
       <c r="D68" s="18"/>
@@ -3733,7 +3787,7 @@
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A69" s="122"/>
+      <c r="A69" s="121"/>
       <c r="B69" s="18"/>
       <c r="C69" s="18"/>
       <c r="D69" s="18"/>
@@ -3750,7 +3804,7 @@
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A70" s="122"/>
+      <c r="A70" s="121"/>
       <c r="B70" s="18"/>
       <c r="C70" s="18"/>
       <c r="D70" s="18"/>
@@ -3767,7 +3821,7 @@
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A71" s="123"/>
+      <c r="A71" s="122"/>
       <c r="B71" s="18"/>
       <c r="C71" s="18"/>
       <c r="D71" s="18"/>
@@ -3784,7 +3838,7 @@
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A72" s="121">
+      <c r="A72" s="120">
         <v>46044</v>
       </c>
       <c r="B72" s="18"/>
@@ -3803,7 +3857,7 @@
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A73" s="122"/>
+      <c r="A73" s="121"/>
       <c r="B73" s="18"/>
       <c r="C73" s="18"/>
       <c r="D73" s="18"/>
@@ -3820,7 +3874,7 @@
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A74" s="122"/>
+      <c r="A74" s="121"/>
       <c r="B74" s="18"/>
       <c r="C74" s="18"/>
       <c r="D74" s="18"/>
@@ -3837,7 +3891,7 @@
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A75" s="122"/>
+      <c r="A75" s="121"/>
       <c r="B75" s="18"/>
       <c r="C75" s="18"/>
       <c r="D75" s="18"/>
@@ -3854,7 +3908,7 @@
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A76" s="123"/>
+      <c r="A76" s="122"/>
       <c r="B76" s="18"/>
       <c r="C76" s="18"/>
       <c r="D76" s="18"/>
@@ -3871,7 +3925,7 @@
       </c>
     </row>
     <row r="77" spans="1:9" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A77" s="121">
+      <c r="A77" s="120">
         <v>46045</v>
       </c>
       <c r="B77" s="18"/>
@@ -3888,12 +3942,12 @@
         <f t="shared" si="0"/>
         <v>2439</v>
       </c>
-      <c r="I77" s="124" t="s">
+      <c r="I77" s="119" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A78" s="122"/>
+      <c r="A78" s="121"/>
       <c r="B78" s="18"/>
       <c r="C78" s="18"/>
       <c r="D78" s="18"/>
@@ -3910,10 +3964,10 @@
         <f t="shared" si="0"/>
         <v>2314</v>
       </c>
-      <c r="I78" s="124"/>
+      <c r="I78" s="119"/>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A79" s="122"/>
+      <c r="A79" s="121"/>
       <c r="B79" s="18"/>
       <c r="C79" s="18"/>
       <c r="D79" s="18"/>
@@ -3932,7 +3986,7 @@
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A80" s="123"/>
+      <c r="A80" s="122"/>
       <c r="B80" s="18"/>
       <c r="C80" s="18"/>
       <c r="D80" s="18"/>
@@ -3949,7 +4003,7 @@
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A81" s="121">
+      <c r="A81" s="120">
         <v>46046</v>
       </c>
       <c r="B81" s="18" t="s">
@@ -3976,7 +4030,7 @@
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A82" s="122"/>
+      <c r="A82" s="121"/>
       <c r="B82" s="18"/>
       <c r="C82" s="18"/>
       <c r="D82" s="18"/>
@@ -3993,7 +4047,7 @@
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A83" s="122"/>
+      <c r="A83" s="121"/>
       <c r="B83" s="18"/>
       <c r="C83" s="18"/>
       <c r="D83" s="18"/>
@@ -4010,7 +4064,7 @@
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A84" s="123"/>
+      <c r="A84" s="122"/>
       <c r="B84" s="18"/>
       <c r="C84" s="18"/>
       <c r="D84" s="18"/>
@@ -4027,7 +4081,7 @@
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A85" s="121">
+      <c r="A85" s="120">
         <v>46049</v>
       </c>
       <c r="B85" s="18"/>
@@ -4046,7 +4100,7 @@
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A86" s="122"/>
+      <c r="A86" s="121"/>
       <c r="B86" s="18"/>
       <c r="C86" s="18"/>
       <c r="D86" s="18"/>
@@ -4063,7 +4117,7 @@
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A87" s="123"/>
+      <c r="A87" s="122"/>
       <c r="B87" s="18"/>
       <c r="C87" s="18"/>
       <c r="D87" s="18"/>
@@ -4080,7 +4134,7 @@
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A88" s="121">
+      <c r="A88" s="120">
         <v>46050</v>
       </c>
       <c r="B88" s="18" t="s">
@@ -4107,7 +4161,7 @@
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A89" s="122"/>
+      <c r="A89" s="121"/>
       <c r="B89" s="18"/>
       <c r="C89" s="18"/>
       <c r="D89" s="18"/>
@@ -4124,7 +4178,7 @@
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A90" s="122"/>
+      <c r="A90" s="121"/>
       <c r="B90" s="18"/>
       <c r="C90" s="18"/>
       <c r="D90" s="18"/>
@@ -4141,7 +4195,7 @@
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A91" s="122"/>
+      <c r="A91" s="121"/>
       <c r="B91" s="18"/>
       <c r="C91" s="18"/>
       <c r="D91" s="18"/>
@@ -4160,7 +4214,7 @@
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A92" s="123"/>
+      <c r="A92" s="122"/>
       <c r="B92" s="18"/>
       <c r="C92" s="18"/>
       <c r="D92" s="18"/>
@@ -4177,7 +4231,7 @@
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A93" s="121">
+      <c r="A93" s="120">
         <v>46051</v>
       </c>
       <c r="B93" s="18"/>
@@ -4196,7 +4250,7 @@
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A94" s="122"/>
+      <c r="A94" s="121"/>
       <c r="B94" s="18"/>
       <c r="C94" s="18"/>
       <c r="D94" s="18"/>
@@ -4213,7 +4267,7 @@
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A95" s="123"/>
+      <c r="A95" s="122"/>
       <c r="B95" s="18"/>
       <c r="C95" s="18"/>
       <c r="D95" s="18"/>
@@ -4463,6 +4517,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A72:A76"/>
+    <mergeCell ref="A77:A80"/>
+    <mergeCell ref="A81:A84"/>
+    <mergeCell ref="A85:A87"/>
+    <mergeCell ref="A93:A95"/>
     <mergeCell ref="I77:I78"/>
     <mergeCell ref="A88:A92"/>
     <mergeCell ref="A6:A7"/>
@@ -4479,11 +4538,6 @@
     <mergeCell ref="A56:A57"/>
     <mergeCell ref="A59:A66"/>
     <mergeCell ref="A67:A71"/>
-    <mergeCell ref="A72:A76"/>
-    <mergeCell ref="A77:A80"/>
-    <mergeCell ref="A81:A84"/>
-    <mergeCell ref="A85:A87"/>
-    <mergeCell ref="A93:A95"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="68" fitToHeight="0" orientation="landscape" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
@@ -4606,7 +4660,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="128">
+      <c r="A6" s="123">
         <v>46055</v>
       </c>
       <c r="B6" s="17"/>
@@ -4627,7 +4681,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="128"/>
+      <c r="A7" s="123"/>
       <c r="B7" s="17"/>
       <c r="C7" s="76"/>
       <c r="D7" s="17"/>
@@ -4644,7 +4698,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="128"/>
+      <c r="A8" s="123"/>
       <c r="B8" s="17"/>
       <c r="C8" s="76"/>
       <c r="D8" s="17"/>
@@ -4661,7 +4715,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="128"/>
+      <c r="A9" s="123"/>
       <c r="B9" s="17"/>
       <c r="C9" s="76"/>
       <c r="D9" s="17"/>
@@ -4678,7 +4732,7 @@
       </c>
     </row>
     <row r="10" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="128">
+      <c r="A10" s="123">
         <v>46056</v>
       </c>
       <c r="B10" s="18"/>
@@ -4697,7 +4751,7 @@
       </c>
     </row>
     <row r="11" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="128"/>
+      <c r="A11" s="123"/>
       <c r="B11" s="17"/>
       <c r="C11" s="76"/>
       <c r="D11" s="17"/>
@@ -4714,7 +4768,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="128"/>
+      <c r="A12" s="123"/>
       <c r="B12" s="17"/>
       <c r="C12" s="76"/>
       <c r="D12" s="17"/>
@@ -4731,7 +4785,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="128"/>
+      <c r="A13" s="123"/>
       <c r="B13" s="18"/>
       <c r="C13" s="76"/>
       <c r="D13" s="17"/>
@@ -4748,7 +4802,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="128"/>
+      <c r="A14" s="123"/>
       <c r="B14" s="17"/>
       <c r="C14" s="76"/>
       <c r="D14" s="17"/>
@@ -4765,7 +4819,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="128">
+      <c r="A15" s="123">
         <v>46057</v>
       </c>
       <c r="B15" s="17"/>
@@ -4784,7 +4838,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="128"/>
+      <c r="A16" s="123"/>
       <c r="B16" s="17"/>
       <c r="C16" s="76"/>
       <c r="D16" s="17"/>
@@ -4801,7 +4855,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="128">
+      <c r="A17" s="123">
         <v>46058</v>
       </c>
       <c r="B17" s="17"/>
@@ -4820,7 +4874,7 @@
       </c>
     </row>
     <row r="18" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="128"/>
+      <c r="A18" s="123"/>
       <c r="B18" s="17"/>
       <c r="C18" s="76"/>
       <c r="D18" s="17"/>
@@ -4837,7 +4891,7 @@
       </c>
     </row>
     <row r="19" spans="1:8" s="15" customFormat="1" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A19" s="128">
+      <c r="A19" s="123">
         <v>46060</v>
       </c>
       <c r="B19" s="17" t="s">
@@ -4864,7 +4918,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" s="15" customFormat="1" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A20" s="128"/>
+      <c r="A20" s="123"/>
       <c r="B20" s="17" t="s">
         <v>121</v>
       </c>
@@ -4889,7 +4943,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="128"/>
+      <c r="A21" s="123"/>
       <c r="B21" s="17"/>
       <c r="C21" s="76"/>
       <c r="D21" s="17"/>
@@ -4906,7 +4960,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="128"/>
+      <c r="A22" s="123"/>
       <c r="B22" s="17"/>
       <c r="C22" s="76"/>
       <c r="D22" s="17"/>
@@ -4923,7 +4977,7 @@
       </c>
     </row>
     <row r="23" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="128"/>
+      <c r="A23" s="123"/>
       <c r="B23" s="17"/>
       <c r="C23" s="76"/>
       <c r="D23" s="17"/>
@@ -4940,7 +4994,7 @@
       </c>
     </row>
     <row r="24" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="128"/>
+      <c r="A24" s="123"/>
       <c r="B24" s="18"/>
       <c r="C24" s="76"/>
       <c r="D24" s="17"/>
@@ -4957,7 +5011,7 @@
       </c>
     </row>
     <row r="25" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="128"/>
+      <c r="A25" s="123"/>
       <c r="B25" s="17"/>
       <c r="C25" s="76"/>
       <c r="D25" s="17"/>
@@ -4974,7 +5028,7 @@
       </c>
     </row>
     <row r="26" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="128"/>
+      <c r="A26" s="123"/>
       <c r="B26" s="17"/>
       <c r="C26" s="76"/>
       <c r="D26" s="17"/>
@@ -4991,7 +5045,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="128">
+      <c r="A27" s="123">
         <v>46062</v>
       </c>
       <c r="B27" s="17"/>
@@ -5010,7 +5064,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="128"/>
+      <c r="A28" s="123"/>
       <c r="B28" s="17"/>
       <c r="C28" s="76"/>
       <c r="D28" s="17"/>
@@ -5027,7 +5081,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="128"/>
+      <c r="A29" s="123"/>
       <c r="B29" s="17"/>
       <c r="C29" s="76"/>
       <c r="D29" s="17"/>
@@ -5044,7 +5098,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="128">
+      <c r="A30" s="123">
         <v>46063</v>
       </c>
       <c r="B30" s="18"/>
@@ -5063,7 +5117,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="128"/>
+      <c r="A31" s="123"/>
       <c r="B31" s="17"/>
       <c r="C31" s="76"/>
       <c r="D31" s="17"/>
@@ -5080,7 +5134,7 @@
       </c>
     </row>
     <row r="32" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="128"/>
+      <c r="A32" s="123"/>
       <c r="B32" s="17"/>
       <c r="C32" s="76"/>
       <c r="D32" s="17"/>
@@ -5097,7 +5151,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="128"/>
+      <c r="A33" s="123"/>
       <c r="B33" s="17"/>
       <c r="C33" s="76"/>
       <c r="D33" s="17"/>
@@ -5114,7 +5168,7 @@
       </c>
     </row>
     <row r="34" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="128">
+      <c r="A34" s="123">
         <v>46064</v>
       </c>
       <c r="B34" s="17"/>
@@ -5133,7 +5187,7 @@
       </c>
     </row>
     <row r="35" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="128"/>
+      <c r="A35" s="123"/>
       <c r="B35" s="17"/>
       <c r="C35" s="76"/>
       <c r="D35" s="17"/>
@@ -5150,7 +5204,7 @@
       </c>
     </row>
     <row r="36" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="128"/>
+      <c r="A36" s="123"/>
       <c r="B36" s="17"/>
       <c r="C36" s="76"/>
       <c r="D36" s="17"/>
@@ -5167,7 +5221,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="128"/>
+      <c r="A37" s="123"/>
       <c r="B37" s="17"/>
       <c r="C37" s="76"/>
       <c r="D37" s="17"/>
@@ -5184,7 +5238,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="128">
+      <c r="A38" s="123">
         <v>46065</v>
       </c>
       <c r="B38" s="17"/>
@@ -5203,7 +5257,7 @@
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A39" s="128"/>
+      <c r="A39" s="123"/>
       <c r="B39" s="25"/>
       <c r="C39" s="77"/>
       <c r="D39" s="11"/>
@@ -5220,7 +5274,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" s="128"/>
+      <c r="A40" s="123"/>
       <c r="B40" s="18"/>
       <c r="C40" s="76"/>
       <c r="D40" s="17"/>
@@ -5256,7 +5310,7 @@
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A42" s="128">
+      <c r="A42" s="123">
         <v>46067</v>
       </c>
       <c r="B42" s="25"/>
@@ -5275,7 +5329,7 @@
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" s="128"/>
+      <c r="A43" s="123"/>
       <c r="B43" s="25"/>
       <c r="C43" s="77"/>
       <c r="D43" s="11"/>
@@ -5292,7 +5346,7 @@
       </c>
     </row>
     <row r="44" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A44" s="128"/>
+      <c r="A44" s="123"/>
       <c r="B44" s="17" t="s">
         <v>120</v>
       </c>
@@ -5338,7 +5392,7 @@
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A46" s="128">
+      <c r="A46" s="123">
         <v>46071</v>
       </c>
       <c r="B46" s="17"/>
@@ -5357,7 +5411,7 @@
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A47" s="128"/>
+      <c r="A47" s="123"/>
       <c r="B47" s="17"/>
       <c r="C47" s="77"/>
       <c r="D47" s="11"/>
@@ -5374,7 +5428,7 @@
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A48" s="128">
+      <c r="A48" s="123">
         <v>46072</v>
       </c>
       <c r="B48" s="18"/>
@@ -5393,7 +5447,7 @@
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A49" s="128"/>
+      <c r="A49" s="123"/>
       <c r="B49" s="18"/>
       <c r="C49" s="76"/>
       <c r="D49" s="18"/>
@@ -5410,7 +5464,7 @@
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A50" s="128"/>
+      <c r="A50" s="123"/>
       <c r="B50" s="17"/>
       <c r="C50" s="76"/>
       <c r="D50" s="18"/>
@@ -5427,7 +5481,7 @@
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A51" s="128"/>
+      <c r="A51" s="123"/>
       <c r="B51" s="18"/>
       <c r="C51" s="76"/>
       <c r="D51" s="18"/>
@@ -5444,7 +5498,7 @@
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A52" s="128">
+      <c r="A52" s="123">
         <v>46073</v>
       </c>
       <c r="B52" s="18"/>
@@ -5463,7 +5517,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A53" s="128"/>
+      <c r="A53" s="123"/>
       <c r="B53" s="18"/>
       <c r="C53" s="76"/>
       <c r="D53" s="18"/>
@@ -5480,7 +5534,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A54" s="128"/>
+      <c r="A54" s="123"/>
       <c r="B54" s="18"/>
       <c r="C54" s="76"/>
       <c r="D54" s="18"/>
@@ -5497,7 +5551,7 @@
       </c>
     </row>
     <row r="55" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A55" s="128">
+      <c r="A55" s="123">
         <v>46076</v>
       </c>
       <c r="B55" s="17" t="s">
@@ -5524,7 +5578,7 @@
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A56" s="128"/>
+      <c r="A56" s="123"/>
       <c r="B56" s="18"/>
       <c r="C56" s="76"/>
       <c r="D56" s="18"/>
@@ -5541,7 +5595,7 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A57" s="128"/>
+      <c r="A57" s="123"/>
       <c r="B57" s="18"/>
       <c r="C57" s="76"/>
       <c r="D57" s="18"/>
@@ -5558,7 +5612,7 @@
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A58" s="128"/>
+      <c r="A58" s="123"/>
       <c r="B58" s="18"/>
       <c r="C58" s="76"/>
       <c r="D58" s="18"/>
@@ -5575,7 +5629,7 @@
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A59" s="128">
+      <c r="A59" s="123">
         <v>46077</v>
       </c>
       <c r="B59" s="18"/>
@@ -5594,7 +5648,7 @@
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A60" s="128"/>
+      <c r="A60" s="123"/>
       <c r="B60" s="18"/>
       <c r="C60" s="76"/>
       <c r="D60" s="18"/>
@@ -5611,7 +5665,7 @@
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A61" s="128"/>
+      <c r="A61" s="123"/>
       <c r="B61" s="10"/>
       <c r="C61" s="78"/>
       <c r="D61" s="10"/>
@@ -5628,7 +5682,7 @@
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A62" s="128"/>
+      <c r="A62" s="123"/>
       <c r="B62" s="10"/>
       <c r="C62" s="78"/>
       <c r="D62" s="10"/>
@@ -5645,7 +5699,7 @@
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A63" s="128"/>
+      <c r="A63" s="123"/>
       <c r="B63" s="10"/>
       <c r="C63" s="78"/>
       <c r="D63" s="10"/>
@@ -5662,7 +5716,7 @@
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A64" s="128">
+      <c r="A64" s="123">
         <v>46078</v>
       </c>
       <c r="B64" s="10"/>
@@ -5681,7 +5735,7 @@
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A65" s="128"/>
+      <c r="A65" s="123"/>
       <c r="B65" s="10"/>
       <c r="C65" s="78"/>
       <c r="D65" s="10"/>
@@ -5698,7 +5752,7 @@
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A66" s="128">
+      <c r="A66" s="123">
         <v>46079</v>
       </c>
       <c r="B66" s="18"/>
@@ -5717,7 +5771,7 @@
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A67" s="128"/>
+      <c r="A67" s="123"/>
       <c r="B67" s="18"/>
       <c r="C67" s="76"/>
       <c r="D67" s="18"/>
@@ -5734,7 +5788,7 @@
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A68" s="128"/>
+      <c r="A68" s="123"/>
       <c r="B68" s="18"/>
       <c r="C68" s="76"/>
       <c r="D68" s="18"/>
@@ -5751,7 +5805,7 @@
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A69" s="128"/>
+      <c r="A69" s="123"/>
       <c r="B69" s="18"/>
       <c r="C69" s="76"/>
       <c r="D69" s="18"/>
@@ -5768,7 +5822,7 @@
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A70" s="128">
+      <c r="A70" s="123">
         <v>46080</v>
       </c>
       <c r="B70" s="18"/>
@@ -5787,7 +5841,7 @@
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A71" s="128"/>
+      <c r="A71" s="123"/>
       <c r="B71" s="18"/>
       <c r="C71" s="76"/>
       <c r="D71" s="18"/>
@@ -5804,7 +5858,7 @@
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A72" s="128"/>
+      <c r="A72" s="123"/>
       <c r="B72" s="18"/>
       <c r="C72" s="76"/>
       <c r="D72" s="18"/>
@@ -5821,7 +5875,7 @@
       </c>
     </row>
     <row r="73" spans="1:9" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A73" s="128">
+      <c r="A73" s="123">
         <v>46081</v>
       </c>
       <c r="B73" s="17" t="s">
@@ -5848,7 +5902,7 @@
       </c>
     </row>
     <row r="74" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="128"/>
+      <c r="A74" s="123"/>
       <c r="B74" s="18"/>
       <c r="C74" s="76"/>
       <c r="D74" s="18"/>
@@ -5867,7 +5921,7 @@
       </c>
     </row>
     <row r="75" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="128"/>
+      <c r="A75" s="123"/>
       <c r="B75" s="18"/>
       <c r="C75" s="76"/>
       <c r="D75" s="18"/>
@@ -5884,7 +5938,7 @@
       </c>
     </row>
     <row r="76" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="128"/>
+      <c r="A76" s="123"/>
       <c r="B76" s="18"/>
       <c r="C76" s="76"/>
       <c r="D76" s="18"/>
@@ -5901,7 +5955,7 @@
       </c>
     </row>
     <row r="77" spans="1:9" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A77" s="128"/>
+      <c r="A77" s="123"/>
       <c r="B77" s="18"/>
       <c r="C77" s="76"/>
       <c r="D77" s="18"/>
@@ -5916,12 +5970,12 @@
         <f t="shared" si="1"/>
         <v>2127.9400000000005</v>
       </c>
-      <c r="I77" s="124" t="s">
+      <c r="I77" s="119" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="129"/>
+      <c r="A78" s="124"/>
       <c r="B78" s="51"/>
       <c r="C78" s="79"/>
       <c r="D78" s="51"/>
@@ -5936,7 +5990,7 @@
         <f t="shared" si="1"/>
         <v>1427.9400000000005</v>
       </c>
-      <c r="I78" s="124"/>
+      <c r="I78" s="119"/>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="58"/>
@@ -6369,11 +6423,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A66:A69"/>
-    <mergeCell ref="A70:A72"/>
-    <mergeCell ref="A59:A63"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="A73:A78"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="I77:I78"/>
     <mergeCell ref="A6:A9"/>
@@ -6390,6 +6439,11 @@
     <mergeCell ref="A48:A51"/>
     <mergeCell ref="A52:A54"/>
     <mergeCell ref="A55:A58"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="A70:A72"/>
+    <mergeCell ref="A59:A63"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="A73:A78"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="63" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -6534,7 +6588,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="121">
+      <c r="A7" s="120">
         <v>46084</v>
       </c>
       <c r="B7" s="17"/>
@@ -6553,7 +6607,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="122"/>
+      <c r="A8" s="121"/>
       <c r="B8" s="17"/>
       <c r="C8" s="76"/>
       <c r="D8" s="17"/>
@@ -6570,7 +6624,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" s="15" customFormat="1" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A9" s="122"/>
+      <c r="A9" s="121"/>
       <c r="B9" s="17" t="s">
         <v>121</v>
       </c>
@@ -6595,7 +6649,7 @@
       </c>
     </row>
     <row r="10" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="123"/>
+      <c r="A10" s="122"/>
       <c r="B10" s="18"/>
       <c r="C10" s="76"/>
       <c r="D10" s="17"/>
@@ -6669,7 +6723,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" s="15" customFormat="1" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A14" s="121">
+      <c r="A14" s="120">
         <v>46088</v>
       </c>
       <c r="B14" s="17" t="s">
@@ -6696,7 +6750,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="122"/>
+      <c r="A15" s="121"/>
       <c r="B15" s="17"/>
       <c r="C15" s="76"/>
       <c r="D15" s="17"/>
@@ -6713,7 +6767,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="122"/>
+      <c r="A16" s="121"/>
       <c r="B16" s="17"/>
       <c r="C16" s="76"/>
       <c r="D16" s="17"/>
@@ -6730,7 +6784,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="122"/>
+      <c r="A17" s="121"/>
       <c r="B17" s="17"/>
       <c r="C17" s="76"/>
       <c r="D17" s="17"/>
@@ -6747,7 +6801,7 @@
       </c>
     </row>
     <row r="18" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="123"/>
+      <c r="A18" s="122"/>
       <c r="B18" s="17"/>
       <c r="C18" s="76"/>
       <c r="D18" s="17"/>
@@ -6783,7 +6837,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="121">
+      <c r="A20" s="120">
         <v>46092</v>
       </c>
       <c r="B20" s="17"/>
@@ -6802,7 +6856,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="122"/>
+      <c r="A21" s="121"/>
       <c r="B21" s="17"/>
       <c r="C21" s="76"/>
       <c r="D21" s="17"/>
@@ -6819,7 +6873,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="122"/>
+      <c r="A22" s="121"/>
       <c r="B22" s="17"/>
       <c r="C22" s="76"/>
       <c r="D22" s="17"/>
@@ -6836,7 +6890,7 @@
       </c>
     </row>
     <row r="23" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="123"/>
+      <c r="A23" s="122"/>
       <c r="B23" s="17"/>
       <c r="C23" s="76"/>
       <c r="D23" s="17"/>
@@ -6880,7 +6934,7 @@
       </c>
     </row>
     <row r="25" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="121">
+      <c r="A25" s="120">
         <v>46094</v>
       </c>
       <c r="B25" s="17"/>
@@ -6899,7 +6953,7 @@
       </c>
     </row>
     <row r="26" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="122"/>
+      <c r="A26" s="121"/>
       <c r="B26" s="17"/>
       <c r="C26" s="76"/>
       <c r="D26" s="17"/>
@@ -6916,7 +6970,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="122"/>
+      <c r="A27" s="121"/>
       <c r="B27" s="17"/>
       <c r="C27" s="76"/>
       <c r="D27" s="17"/>
@@ -6933,7 +6987,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="122"/>
+      <c r="A28" s="121"/>
       <c r="B28" s="17"/>
       <c r="C28" s="76"/>
       <c r="D28" s="17"/>
@@ -6950,7 +7004,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="122"/>
+      <c r="A29" s="121"/>
       <c r="B29" s="17"/>
       <c r="C29" s="76"/>
       <c r="D29" s="17"/>
@@ -6967,7 +7021,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="122"/>
+      <c r="A30" s="121"/>
       <c r="B30" s="18"/>
       <c r="C30" s="76"/>
       <c r="D30" s="17"/>
@@ -6984,7 +7038,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="122"/>
+      <c r="A31" s="121"/>
       <c r="B31" s="17"/>
       <c r="C31" s="76"/>
       <c r="D31" s="17"/>
@@ -7001,7 +7055,7 @@
       </c>
     </row>
     <row r="32" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="122"/>
+      <c r="A32" s="121"/>
       <c r="B32" s="17"/>
       <c r="C32" s="76"/>
       <c r="D32" s="17"/>
@@ -7018,7 +7072,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="122"/>
+      <c r="A33" s="121"/>
       <c r="B33" s="17"/>
       <c r="C33" s="76"/>
       <c r="D33" s="17"/>
@@ -7035,7 +7089,7 @@
       </c>
     </row>
     <row r="34" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="123"/>
+      <c r="A34" s="122"/>
       <c r="B34" s="17"/>
       <c r="C34" s="76"/>
       <c r="D34" s="17"/>
@@ -7052,7 +7106,7 @@
       </c>
     </row>
     <row r="35" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="121">
+      <c r="A35" s="120">
         <v>46095</v>
       </c>
       <c r="B35" s="17"/>
@@ -7071,7 +7125,7 @@
       </c>
     </row>
     <row r="36" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="122"/>
+      <c r="A36" s="121"/>
       <c r="B36" s="17"/>
       <c r="C36" s="76"/>
       <c r="D36" s="17"/>
@@ -7088,7 +7142,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="122"/>
+      <c r="A37" s="121"/>
       <c r="B37" s="17"/>
       <c r="C37" s="76"/>
       <c r="D37" s="17"/>
@@ -7105,7 +7159,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="123"/>
+      <c r="A38" s="122"/>
       <c r="B38" s="17"/>
       <c r="C38" s="76"/>
       <c r="D38" s="17"/>
@@ -7122,7 +7176,7 @@
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A39" s="121">
+      <c r="A39" s="120">
         <v>46097</v>
       </c>
       <c r="B39" s="25"/>
@@ -7141,7 +7195,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" s="122"/>
+      <c r="A40" s="121"/>
       <c r="B40" s="18"/>
       <c r="C40" s="76"/>
       <c r="D40" s="17"/>
@@ -7158,7 +7212,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" s="122"/>
+      <c r="A41" s="121"/>
       <c r="B41" s="25"/>
       <c r="C41" s="77"/>
       <c r="D41" s="11"/>
@@ -7175,7 +7229,7 @@
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A42" s="122"/>
+      <c r="A42" s="121"/>
       <c r="B42" s="25"/>
       <c r="C42" s="77"/>
       <c r="D42" s="11"/>
@@ -7192,7 +7246,7 @@
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" s="122"/>
+      <c r="A43" s="121"/>
       <c r="B43" s="25"/>
       <c r="C43" s="77"/>
       <c r="D43" s="11"/>
@@ -7209,7 +7263,7 @@
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A44" s="122"/>
+      <c r="A44" s="121"/>
       <c r="B44" s="17"/>
       <c r="C44" s="76"/>
       <c r="D44" s="17"/>
@@ -7226,7 +7280,7 @@
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A45" s="122"/>
+      <c r="A45" s="121"/>
       <c r="B45" s="17"/>
       <c r="C45" s="76"/>
       <c r="D45" s="17"/>
@@ -7243,7 +7297,7 @@
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A46" s="123"/>
+      <c r="A46" s="122"/>
       <c r="B46" s="17"/>
       <c r="C46" s="77"/>
       <c r="D46" s="11"/>
@@ -7260,7 +7314,7 @@
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A47" s="121">
+      <c r="A47" s="120">
         <v>46098</v>
       </c>
       <c r="B47" s="17"/>
@@ -7279,7 +7333,7 @@
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A48" s="122"/>
+      <c r="A48" s="121"/>
       <c r="B48" s="18"/>
       <c r="C48" s="76"/>
       <c r="D48" s="18"/>
@@ -7296,7 +7350,7 @@
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A49" s="122"/>
+      <c r="A49" s="121"/>
       <c r="B49" s="18"/>
       <c r="C49" s="76"/>
       <c r="D49" s="18"/>
@@ -7313,7 +7367,7 @@
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A50" s="122"/>
+      <c r="A50" s="121"/>
       <c r="B50" s="17"/>
       <c r="C50" s="76"/>
       <c r="D50" s="18"/>
@@ -7330,7 +7384,7 @@
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A51" s="122"/>
+      <c r="A51" s="121"/>
       <c r="B51" s="18"/>
       <c r="C51" s="76"/>
       <c r="D51" s="18"/>
@@ -7347,7 +7401,7 @@
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A52" s="123"/>
+      <c r="A52" s="122"/>
       <c r="B52" s="18"/>
       <c r="C52" s="76"/>
       <c r="D52" s="18"/>
@@ -7364,7 +7418,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A53" s="121">
+      <c r="A53" s="120">
         <v>46099</v>
       </c>
       <c r="B53" s="17" t="s">
@@ -7391,7 +7445,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A54" s="122"/>
+      <c r="A54" s="121"/>
       <c r="B54" s="18"/>
       <c r="C54" s="76"/>
       <c r="D54" s="18"/>
@@ -7408,7 +7462,7 @@
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A55" s="122"/>
+      <c r="A55" s="121"/>
       <c r="B55" s="17"/>
       <c r="C55" s="76"/>
       <c r="D55" s="17"/>
@@ -7425,7 +7479,7 @@
       </c>
     </row>
     <row r="56" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A56" s="123"/>
+      <c r="A56" s="122"/>
       <c r="B56" s="18" t="s">
         <v>229</v>
       </c>
@@ -7450,7 +7504,7 @@
       </c>
     </row>
     <row r="57" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A57" s="121">
+      <c r="A57" s="120">
         <v>46100</v>
       </c>
       <c r="B57" s="17" t="s">
@@ -7477,7 +7531,7 @@
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A58" s="123"/>
+      <c r="A58" s="122"/>
       <c r="B58" s="18"/>
       <c r="C58" s="76"/>
       <c r="D58" s="18"/>
@@ -7494,7 +7548,7 @@
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A59" s="121">
+      <c r="A59" s="120">
         <v>46101</v>
       </c>
       <c r="B59" s="18"/>
@@ -7513,7 +7567,7 @@
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A60" s="123"/>
+      <c r="A60" s="122"/>
       <c r="B60" s="18"/>
       <c r="C60" s="76"/>
       <c r="D60" s="18"/>
@@ -7530,7 +7584,7 @@
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A61" s="121">
+      <c r="A61" s="120">
         <v>46102</v>
       </c>
       <c r="B61" s="10"/>
@@ -7549,7 +7603,7 @@
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A62" s="122"/>
+      <c r="A62" s="121"/>
       <c r="B62" s="10"/>
       <c r="C62" s="78"/>
       <c r="D62" s="10"/>
@@ -7566,7 +7620,7 @@
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A63" s="123"/>
+      <c r="A63" s="122"/>
       <c r="B63" s="10"/>
       <c r="C63" s="78"/>
       <c r="D63" s="10"/>
@@ -7602,7 +7656,7 @@
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A65" s="121">
+      <c r="A65" s="120">
         <v>46104</v>
       </c>
       <c r="B65" s="10"/>
@@ -7621,7 +7675,7 @@
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A66" s="122"/>
+      <c r="A66" s="121"/>
       <c r="B66" s="18"/>
       <c r="C66" s="76"/>
       <c r="D66" s="18"/>
@@ -7638,7 +7692,7 @@
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A67" s="123"/>
+      <c r="A67" s="122"/>
       <c r="B67" s="18"/>
       <c r="C67" s="76"/>
       <c r="D67" s="18"/>
@@ -7655,7 +7709,7 @@
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A68" s="121">
+      <c r="A68" s="120">
         <v>46105</v>
       </c>
       <c r="B68" s="18"/>
@@ -7674,7 +7728,7 @@
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A69" s="122"/>
+      <c r="A69" s="121"/>
       <c r="B69" s="18"/>
       <c r="C69" s="76"/>
       <c r="D69" s="18"/>
@@ -7691,7 +7745,7 @@
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A70" s="123"/>
+      <c r="A70" s="122"/>
       <c r="B70" s="18"/>
       <c r="C70" s="76"/>
       <c r="D70" s="18"/>
@@ -7708,7 +7762,7 @@
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A71" s="121">
+      <c r="A71" s="120">
         <v>46106</v>
       </c>
       <c r="B71" s="18"/>
@@ -7727,7 +7781,7 @@
       </c>
     </row>
     <row r="72" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="122"/>
+      <c r="A72" s="121"/>
       <c r="B72" s="18"/>
       <c r="C72" s="76"/>
       <c r="D72" s="18"/>
@@ -7744,7 +7798,7 @@
       </c>
     </row>
     <row r="73" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="122"/>
+      <c r="A73" s="121"/>
       <c r="B73" s="17"/>
       <c r="C73" s="76"/>
       <c r="D73" s="17"/>
@@ -7761,7 +7815,7 @@
       </c>
     </row>
     <row r="74" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="122"/>
+      <c r="A74" s="121"/>
       <c r="B74" s="18"/>
       <c r="C74" s="76"/>
       <c r="D74" s="18"/>
@@ -7778,7 +7832,7 @@
       </c>
     </row>
     <row r="75" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="122"/>
+      <c r="A75" s="121"/>
       <c r="B75" s="18"/>
       <c r="C75" s="76"/>
       <c r="D75" s="18"/>
@@ -7795,7 +7849,7 @@
       </c>
     </row>
     <row r="76" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="122"/>
+      <c r="A76" s="121"/>
       <c r="B76" s="18"/>
       <c r="C76" s="76"/>
       <c r="D76" s="18"/>
@@ -7812,10 +7866,10 @@
       </c>
     </row>
     <row r="77" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="122"/>
-      <c r="B77" s="87"/>
-      <c r="C77" s="88"/>
-      <c r="D77" s="87"/>
+      <c r="A77" s="121"/>
+      <c r="B77" s="84"/>
+      <c r="C77" s="85"/>
+      <c r="D77" s="84"/>
       <c r="E77" s="52" t="s">
         <v>249</v>
       </c>
@@ -7829,7 +7883,7 @@
       </c>
     </row>
     <row r="78" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="133"/>
+      <c r="A78" s="128"/>
       <c r="B78" s="51"/>
       <c r="C78" s="79"/>
       <c r="D78" s="51"/>
@@ -7844,7 +7898,7 @@
         <f>H76+F78-G78</f>
         <v>219</v>
       </c>
-      <c r="I78" s="124" t="s">
+      <c r="I78" s="119" t="s">
         <v>9</v>
       </c>
     </row>
@@ -7866,7 +7920,7 @@
         <f>H78+F79-G79</f>
         <v>-781</v>
       </c>
-      <c r="I79" s="134"/>
+      <c r="I79" s="129"/>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="82">
@@ -7888,7 +7942,7 @@
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A81" s="121">
+      <c r="A81" s="120">
         <v>46111</v>
       </c>
       <c r="B81" s="18"/>
@@ -7907,7 +7961,7 @@
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A82" s="122"/>
+      <c r="A82" s="121"/>
       <c r="B82" s="18"/>
       <c r="C82" s="76"/>
       <c r="D82" s="18"/>
@@ -7924,7 +7978,7 @@
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A83" s="123"/>
+      <c r="A83" s="122"/>
       <c r="B83" s="18"/>
       <c r="C83" s="76"/>
       <c r="D83" s="18"/>
@@ -8341,16 +8395,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A65:A67"/>
-    <mergeCell ref="A68:A70"/>
-    <mergeCell ref="A71:A78"/>
-    <mergeCell ref="A81:A83"/>
-    <mergeCell ref="I78:I79"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A14:A18"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="A25:A34"/>
     <mergeCell ref="A59:A60"/>
     <mergeCell ref="A61:A63"/>
     <mergeCell ref="A35:A38"/>
@@ -8358,6 +8402,16 @@
     <mergeCell ref="A47:A52"/>
     <mergeCell ref="A53:A56"/>
     <mergeCell ref="A57:A58"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A14:A18"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A25:A34"/>
+    <mergeCell ref="A65:A67"/>
+    <mergeCell ref="A68:A70"/>
+    <mergeCell ref="A71:A78"/>
+    <mergeCell ref="A81:A83"/>
+    <mergeCell ref="I78:I79"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="63" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -8380,61 +8434,61 @@
     <col min="2" max="2" width="11.42578125" style="16" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16" style="81" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="45.42578125" style="97" customWidth="1"/>
+    <col min="5" max="5" width="45.42578125" style="93" customWidth="1"/>
     <col min="6" max="6" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.140625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.140625" style="97" customWidth="1"/>
-    <col min="11" max="11" width="13.7109375" style="97" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11" style="97" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" style="93" customWidth="1"/>
+    <col min="11" max="11" width="13.7109375" style="93" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11" style="93" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="20.28515625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17.7109375" style="81" customWidth="1"/>
     <col min="16" max="16" width="20.28515625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="8.85546875" style="1"/>
+    <col min="17" max="17" width="16" style="1" customWidth="1"/>
     <col min="18" max="18" width="17.7109375" style="81" customWidth="1"/>
     <col min="19" max="19" width="20.28515625" style="1" customWidth="1"/>
     <col min="20" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="141" t="s">
+      <c r="A1" s="133" t="s">
         <v>259</v>
       </c>
-      <c r="B1" s="141"/>
-      <c r="C1" s="141"/>
-      <c r="D1" s="141"/>
-      <c r="E1" s="141"/>
-      <c r="F1" s="141"/>
-      <c r="G1" s="141"/>
-      <c r="H1" s="141"/>
-      <c r="J1" s="141" t="s">
+      <c r="B1" s="133"/>
+      <c r="C1" s="133"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="133"/>
+      <c r="F1" s="133"/>
+      <c r="G1" s="133"/>
+      <c r="H1" s="133"/>
+      <c r="J1" s="133" t="s">
         <v>259</v>
       </c>
-      <c r="K1" s="141"/>
-      <c r="L1" s="141"/>
-      <c r="M1" s="141"/>
-      <c r="N1" s="141"/>
-      <c r="O1" s="141"/>
-      <c r="P1" s="141"/>
-      <c r="Q1" s="141"/>
+      <c r="K1" s="133"/>
+      <c r="L1" s="133"/>
+      <c r="M1" s="133"/>
+      <c r="N1" s="133"/>
+      <c r="O1" s="133"/>
+      <c r="P1" s="133"/>
+      <c r="Q1" s="133"/>
       <c r="R1" s="1"/>
     </row>
     <row r="2" spans="1:20" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="139" t="s">
+      <c r="A2" s="138" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="137" t="s">
+      <c r="B2" s="136" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="137" t="s">
+      <c r="C2" s="136" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="137" t="s">
+      <c r="D2" s="136" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="135" t="s">
+      <c r="E2" s="134" t="s">
         <v>6</v>
       </c>
       <c r="F2" s="62" t="s">
@@ -8446,78 +8500,78 @@
       <c r="H2" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="102" t="s">
+      <c r="J2" s="98" t="s">
         <v>308</v>
       </c>
-      <c r="K2" s="100" t="s">
+      <c r="K2" s="96" t="s">
         <v>307</v>
       </c>
-      <c r="L2" s="98" t="s">
+      <c r="L2" s="94" t="s">
         <v>306</v>
       </c>
-      <c r="M2" s="108" t="s">
+      <c r="M2" s="104" t="s">
         <v>304</v>
       </c>
-      <c r="N2" s="108" t="s">
+      <c r="N2" s="104" t="s">
         <v>292</v>
       </c>
-      <c r="O2" s="108" t="s">
+      <c r="O2" s="104" t="s">
         <v>302</v>
       </c>
-      <c r="P2" s="109" t="s">
+      <c r="P2" s="105" t="s">
         <v>305</v>
       </c>
-      <c r="Q2" s="107" t="s">
+      <c r="Q2" s="103" t="s">
         <v>310</v>
       </c>
       <c r="R2" s="1"/>
     </row>
     <row r="3" spans="1:20" s="22" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="140"/>
-      <c r="B3" s="138"/>
-      <c r="C3" s="138"/>
-      <c r="D3" s="138"/>
-      <c r="E3" s="136"/>
+      <c r="A3" s="139"/>
+      <c r="B3" s="137"/>
+      <c r="C3" s="137"/>
+      <c r="D3" s="137"/>
+      <c r="E3" s="135"/>
       <c r="F3" s="64">
         <f>SUM(F4:F268)</f>
-        <v>41071</v>
+        <v>41571</v>
       </c>
       <c r="G3" s="65">
         <f>SUM(G4:G268)</f>
-        <v>36233</v>
+        <v>44859</v>
       </c>
       <c r="H3" s="72">
         <f>+F3-G3</f>
-        <v>4838</v>
-      </c>
-      <c r="J3" s="103">
+        <v>-3288</v>
+      </c>
+      <c r="J3" s="99">
         <f>SUM(J4:J268)</f>
         <v>9200</v>
       </c>
-      <c r="K3" s="101">
+      <c r="K3" s="97">
         <f>SUM(K4:K268)</f>
-        <v>10568</v>
-      </c>
-      <c r="L3" s="99">
+        <v>11224</v>
+      </c>
+      <c r="L3" s="95">
         <f>SUM(L4:L268)</f>
-        <v>2886</v>
-      </c>
-      <c r="M3" s="114">
+        <v>4760</v>
+      </c>
+      <c r="M3" s="110">
         <f>SUM(M4:M268)</f>
-        <v>12773</v>
-      </c>
-      <c r="N3" s="105" t="s">
+        <v>18499</v>
+      </c>
+      <c r="N3" s="101" t="s">
         <v>303</v>
       </c>
-      <c r="O3" s="104">
+      <c r="O3" s="100">
         <f>SUM(O4:O268)</f>
-        <v>38000</v>
-      </c>
-      <c r="P3" s="104">
-        <f>+M3-O3</f>
-        <v>-25227</v>
-      </c>
-      <c r="Q3" s="106"/>
+        <v>54300</v>
+      </c>
+      <c r="P3" s="100">
+        <f>O3-M3</f>
+        <v>35801</v>
+      </c>
+      <c r="Q3" s="102"/>
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
@@ -8527,18 +8581,18 @@
       <c r="B4" s="10"/>
       <c r="C4" s="78"/>
       <c r="D4" s="10"/>
-      <c r="E4" s="92"/>
+      <c r="E4" s="89"/>
       <c r="F4" s="66"/>
       <c r="G4" s="67"/>
       <c r="H4" s="73"/>
       <c r="J4" s="78"/>
       <c r="K4" s="78"/>
       <c r="L4" s="78"/>
-      <c r="M4" s="105">
+      <c r="M4" s="101">
         <f>E4</f>
         <v>0</v>
       </c>
-      <c r="N4" s="105"/>
+      <c r="N4" s="101"/>
       <c r="O4" s="77">
         <v>0</v>
       </c>
@@ -8561,7 +8615,7 @@
       <c r="D5" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="93" t="s">
+      <c r="E5" s="90" t="s">
         <v>108</v>
       </c>
       <c r="F5" s="13">
@@ -8577,11 +8631,11 @@
       <c r="J5" s="78"/>
       <c r="K5" s="78"/>
       <c r="L5" s="78"/>
-      <c r="M5" s="105">
+      <c r="M5" s="101">
         <f>G5</f>
         <v>0</v>
       </c>
-      <c r="N5" s="105"/>
+      <c r="N5" s="101"/>
       <c r="O5" s="77">
         <v>0</v>
       </c>
@@ -8594,7 +8648,7 @@
       <c r="T5" s="1"/>
     </row>
     <row r="6" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="121">
+      <c r="A6" s="120">
         <v>46114</v>
       </c>
       <c r="B6" s="17" t="s">
@@ -8606,7 +8660,7 @@
       <c r="D6" s="17" t="s">
         <v>262</v>
       </c>
-      <c r="E6" s="110" t="s">
+      <c r="E6" s="106" t="s">
         <v>316</v>
       </c>
       <c r="F6" s="13">
@@ -8620,15 +8674,15 @@
         <v>-2581</v>
       </c>
       <c r="J6" s="78"/>
-      <c r="K6" s="100">
+      <c r="K6" s="96">
         <f>G6</f>
         <v>4850</v>
       </c>
       <c r="L6" s="78"/>
-      <c r="M6" s="105">
-        <v>0</v>
-      </c>
-      <c r="N6" s="105"/>
+      <c r="M6" s="101">
+        <v>0</v>
+      </c>
+      <c r="N6" s="101"/>
       <c r="O6" s="77">
         <v>0</v>
       </c>
@@ -8641,7 +8695,7 @@
       <c r="T6" s="1"/>
     </row>
     <row r="7" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="122"/>
+      <c r="A7" s="121"/>
       <c r="B7" s="17" t="s">
         <v>261</v>
       </c>
@@ -8651,7 +8705,7 @@
       <c r="D7" s="17" t="s">
         <v>262</v>
       </c>
-      <c r="E7" s="110" t="s">
+      <c r="E7" s="106" t="s">
         <v>314</v>
       </c>
       <c r="F7" s="24">
@@ -8665,15 +8719,15 @@
         <v>6569</v>
       </c>
       <c r="J7" s="78"/>
-      <c r="K7" s="100">
+      <c r="K7" s="96">
         <f>G7</f>
         <v>850</v>
       </c>
       <c r="L7" s="78"/>
-      <c r="M7" s="105">
-        <v>0</v>
-      </c>
-      <c r="N7" s="105"/>
+      <c r="M7" s="101">
+        <v>0</v>
+      </c>
+      <c r="N7" s="101"/>
       <c r="O7" s="77">
         <v>0</v>
       </c>
@@ -8686,7 +8740,7 @@
       <c r="T7" s="1"/>
     </row>
     <row r="8" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="122"/>
+      <c r="A8" s="121"/>
       <c r="B8" s="17" t="s">
         <v>261</v>
       </c>
@@ -8696,7 +8750,7 @@
       <c r="D8" s="17" t="s">
         <v>262</v>
       </c>
-      <c r="E8" s="110" t="s">
+      <c r="E8" s="106" t="s">
         <v>315</v>
       </c>
       <c r="F8" s="24">
@@ -8710,15 +8764,15 @@
         <v>11469</v>
       </c>
       <c r="J8" s="78"/>
-      <c r="K8" s="100">
+      <c r="K8" s="96">
         <f>G8</f>
         <v>100</v>
       </c>
       <c r="L8" s="78"/>
-      <c r="M8" s="105">
-        <v>0</v>
-      </c>
-      <c r="N8" s="105"/>
+      <c r="M8" s="101">
+        <v>0</v>
+      </c>
+      <c r="N8" s="101"/>
       <c r="O8" s="77">
         <v>0</v>
       </c>
@@ -8731,11 +8785,11 @@
       <c r="T8" s="1"/>
     </row>
     <row r="9" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="122"/>
+      <c r="A9" s="121"/>
       <c r="B9" s="17"/>
       <c r="C9" s="76"/>
       <c r="D9" s="17"/>
-      <c r="E9" s="111" t="s">
+      <c r="E9" s="107" t="s">
         <v>260</v>
       </c>
       <c r="F9" s="24">
@@ -8748,7 +8802,7 @@
         <f t="shared" si="0"/>
         <v>8269</v>
       </c>
-      <c r="J9" s="102">
+      <c r="J9" s="98">
         <f>G9</f>
         <v>3200</v>
       </c>
@@ -8756,10 +8810,10 @@
         <v>0</v>
       </c>
       <c r="L9" s="78"/>
-      <c r="M9" s="105">
-        <v>0</v>
-      </c>
-      <c r="N9" s="105"/>
+      <c r="M9" s="101">
+        <v>0</v>
+      </c>
+      <c r="N9" s="101"/>
       <c r="O9" s="77">
         <v>0</v>
       </c>
@@ -8772,11 +8826,11 @@
       <c r="T9" s="1"/>
     </row>
     <row r="10" spans="1:20" s="15" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A10" s="122"/>
+      <c r="A10" s="121"/>
       <c r="B10" s="18"/>
       <c r="C10" s="76"/>
       <c r="D10" s="17"/>
-      <c r="E10" s="110" t="s">
+      <c r="E10" s="106" t="s">
         <v>313</v>
       </c>
       <c r="F10" s="24"/>
@@ -8788,15 +8842,15 @@
         <v>8019</v>
       </c>
       <c r="J10" s="78"/>
-      <c r="K10" s="100">
+      <c r="K10" s="96">
         <f>G10</f>
         <v>250</v>
       </c>
       <c r="L10" s="78"/>
-      <c r="M10" s="105">
-        <v>0</v>
-      </c>
-      <c r="N10" s="105"/>
+      <c r="M10" s="101">
+        <v>0</v>
+      </c>
+      <c r="N10" s="101"/>
       <c r="O10" s="77">
         <v>0</v>
       </c>
@@ -8809,11 +8863,11 @@
       <c r="T10" s="1"/>
     </row>
     <row r="11" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="123"/>
+      <c r="A11" s="122"/>
       <c r="B11" s="17"/>
       <c r="C11" s="76"/>
       <c r="D11" s="17"/>
-      <c r="E11" s="113" t="s">
+      <c r="E11" s="109" t="s">
         <v>319</v>
       </c>
       <c r="F11" s="24"/>
@@ -8827,32 +8881,32 @@
       <c r="J11" s="78"/>
       <c r="K11" s="78"/>
       <c r="L11" s="78"/>
-      <c r="M11" s="115">
+      <c r="M11" s="111">
         <f>G11</f>
         <v>1475</v>
       </c>
-      <c r="N11" s="105" t="s">
+      <c r="N11" s="101" t="s">
         <v>293</v>
       </c>
       <c r="O11" s="77">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="P11" s="77">
-        <f t="shared" si="1"/>
-        <v>-525</v>
+        <f>O11-M11</f>
+        <v>1525</v>
       </c>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
     <row r="12" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="121">
+      <c r="A12" s="120">
         <v>46115</v>
       </c>
       <c r="B12" s="17"/>
       <c r="C12" s="76"/>
       <c r="D12" s="17"/>
-      <c r="E12" s="110" t="s">
+      <c r="E12" s="106" t="s">
         <v>323</v>
       </c>
       <c r="F12" s="24"/>
@@ -8864,15 +8918,15 @@
         <v>6274</v>
       </c>
       <c r="J12" s="78"/>
-      <c r="K12" s="100">
+      <c r="K12" s="96">
         <f>G12</f>
         <v>270</v>
       </c>
       <c r="L12" s="78"/>
-      <c r="M12" s="105">
-        <v>0</v>
-      </c>
-      <c r="N12" s="105"/>
+      <c r="M12" s="101">
+        <v>0</v>
+      </c>
+      <c r="N12" s="101"/>
       <c r="O12" s="77">
         <v>0</v>
       </c>
@@ -8885,11 +8939,11 @@
       <c r="T12" s="1"/>
     </row>
     <row r="13" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="123"/>
+      <c r="A13" s="122"/>
       <c r="B13" s="18"/>
       <c r="C13" s="76"/>
       <c r="D13" s="17"/>
-      <c r="E13" s="113" t="s">
+      <c r="E13" s="109" t="s">
         <v>322</v>
       </c>
       <c r="F13" s="24"/>
@@ -8901,15 +8955,15 @@
         <v>5774</v>
       </c>
       <c r="J13" s="78"/>
-      <c r="K13" s="100">
+      <c r="K13" s="96">
         <f>G13</f>
         <v>500</v>
       </c>
       <c r="L13" s="78"/>
-      <c r="M13" s="105">
-        <v>0</v>
-      </c>
-      <c r="N13" s="105"/>
+      <c r="M13" s="101">
+        <v>0</v>
+      </c>
+      <c r="N13" s="101"/>
       <c r="O13" s="77">
         <v>0</v>
       </c>
@@ -8922,13 +8976,13 @@
       <c r="T13" s="1"/>
     </row>
     <row r="14" spans="1:20" s="15" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A14" s="121">
+      <c r="A14" s="120">
         <v>46116</v>
       </c>
       <c r="B14" s="17"/>
       <c r="C14" s="76"/>
       <c r="D14" s="17"/>
-      <c r="E14" s="110" t="s">
+      <c r="E14" s="106" t="s">
         <v>312</v>
       </c>
       <c r="F14" s="24">
@@ -8942,15 +8996,15 @@
         <v>5704</v>
       </c>
       <c r="J14" s="78"/>
-      <c r="K14" s="100">
+      <c r="K14" s="96">
         <f>G14</f>
         <v>70</v>
       </c>
       <c r="L14" s="78"/>
-      <c r="M14" s="105">
-        <v>0</v>
-      </c>
-      <c r="N14" s="105"/>
+      <c r="M14" s="101">
+        <v>0</v>
+      </c>
+      <c r="N14" s="101"/>
       <c r="O14" s="77">
         <v>0</v>
       </c>
@@ -8966,11 +9020,11 @@
       <c r="T14" s="1"/>
     </row>
     <row r="15" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="122"/>
+      <c r="A15" s="121"/>
       <c r="B15" s="17"/>
       <c r="C15" s="76"/>
       <c r="D15" s="17"/>
-      <c r="E15" s="113" t="s">
+      <c r="E15" s="109" t="s">
         <v>264</v>
       </c>
       <c r="F15" s="24"/>
@@ -8984,30 +9038,30 @@
       <c r="J15" s="78"/>
       <c r="K15" s="78"/>
       <c r="L15" s="78"/>
-      <c r="M15" s="115">
+      <c r="M15" s="111">
         <f>G15</f>
         <v>400</v>
       </c>
-      <c r="N15" s="105" t="s">
+      <c r="N15" s="101" t="s">
         <v>294</v>
       </c>
       <c r="O15" s="77">
-        <v>2000</v>
+        <v>23000</v>
       </c>
       <c r="P15" s="77">
-        <f t="shared" si="1"/>
-        <v>-1600</v>
+        <f>O15-(M15+M22+M29+M31+M45+M46)</f>
+        <v>19870</v>
       </c>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
     </row>
     <row r="16" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="122"/>
+      <c r="A16" s="121"/>
       <c r="B16" s="17"/>
       <c r="C16" s="76"/>
       <c r="D16" s="17"/>
-      <c r="E16" s="116" t="s">
+      <c r="E16" s="112" t="s">
         <v>320</v>
       </c>
       <c r="F16" s="24"/>
@@ -9021,30 +9075,30 @@
       <c r="J16" s="78"/>
       <c r="K16" s="78"/>
       <c r="L16" s="78"/>
-      <c r="M16" s="115">
+      <c r="M16" s="111">
         <f t="shared" ref="M16:M19" si="2">G16</f>
         <v>111</v>
       </c>
-      <c r="N16" s="105" t="s">
+      <c r="N16" s="101" t="s">
         <v>321</v>
       </c>
       <c r="O16" s="77">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="P16" s="77">
-        <f t="shared" si="1"/>
-        <v>111</v>
+        <f>O16-M16</f>
+        <v>389</v>
       </c>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
     </row>
     <row r="17" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="122"/>
+      <c r="A17" s="121"/>
       <c r="B17" s="17"/>
       <c r="C17" s="76"/>
       <c r="D17" s="17"/>
-      <c r="E17" s="117" t="s">
+      <c r="E17" s="113" t="s">
         <v>337</v>
       </c>
       <c r="F17" s="24"/>
@@ -9058,11 +9112,11 @@
       <c r="J17" s="78"/>
       <c r="K17" s="78"/>
       <c r="L17" s="78"/>
-      <c r="M17" s="115">
+      <c r="M17" s="111">
         <f t="shared" si="2"/>
         <v>70</v>
       </c>
-      <c r="N17" s="105" t="s">
+      <c r="N17" s="101" t="s">
         <v>338</v>
       </c>
       <c r="O17" s="77">
@@ -9077,11 +9131,11 @@
       <c r="T17" s="1"/>
     </row>
     <row r="18" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="123"/>
+      <c r="A18" s="122"/>
       <c r="B18" s="17"/>
       <c r="C18" s="76"/>
       <c r="D18" s="17"/>
-      <c r="E18" s="110" t="s">
+      <c r="E18" s="106" t="s">
         <v>339</v>
       </c>
       <c r="F18" s="24"/>
@@ -9093,15 +9147,15 @@
         <v>4673</v>
       </c>
       <c r="J18" s="78"/>
-      <c r="K18" s="100">
+      <c r="K18" s="96">
         <f>G18</f>
         <v>450</v>
       </c>
       <c r="L18" s="78"/>
-      <c r="M18" s="105">
-        <v>0</v>
-      </c>
-      <c r="N18" s="105"/>
+      <c r="M18" s="101">
+        <v>0</v>
+      </c>
+      <c r="N18" s="101"/>
       <c r="O18" s="77">
         <v>0</v>
       </c>
@@ -9114,13 +9168,13 @@
       <c r="T18" s="1"/>
     </row>
     <row r="19" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="121">
+      <c r="A19" s="120">
         <v>46118</v>
       </c>
       <c r="B19" s="17"/>
       <c r="C19" s="76"/>
       <c r="D19" s="17"/>
-      <c r="E19" s="116" t="s">
+      <c r="E19" s="112" t="s">
         <v>333</v>
       </c>
       <c r="F19" s="24"/>
@@ -9134,30 +9188,30 @@
       <c r="J19" s="78"/>
       <c r="K19" s="78"/>
       <c r="L19" s="78"/>
-      <c r="M19" s="115">
+      <c r="M19" s="111">
         <f t="shared" si="2"/>
         <v>210</v>
       </c>
-      <c r="N19" s="105" t="s">
+      <c r="N19" s="101" t="s">
         <v>334</v>
       </c>
       <c r="O19" s="77">
         <v>2000</v>
       </c>
       <c r="P19" s="77">
-        <f t="shared" si="1"/>
-        <v>-1790</v>
+        <f>O19-M19</f>
+        <v>1790</v>
       </c>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
     </row>
     <row r="20" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="122"/>
+      <c r="A20" s="121"/>
       <c r="B20" s="17"/>
       <c r="C20" s="76"/>
       <c r="D20" s="17"/>
-      <c r="E20" s="113" t="s">
+      <c r="E20" s="109" t="s">
         <v>265</v>
       </c>
       <c r="F20" s="24"/>
@@ -9171,30 +9225,30 @@
       <c r="J20" s="78"/>
       <c r="K20" s="78"/>
       <c r="L20" s="78"/>
-      <c r="M20" s="115">
+      <c r="M20" s="111">
         <f t="shared" ref="M20:M25" si="3">G20</f>
         <v>180</v>
       </c>
-      <c r="N20" s="105" t="s">
+      <c r="N20" s="101" t="s">
         <v>295</v>
       </c>
       <c r="O20" s="77">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="P20" s="77">
-        <f t="shared" si="1"/>
-        <v>-1820</v>
+        <f>O20-M20</f>
+        <v>3820</v>
       </c>
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
     </row>
     <row r="21" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="122"/>
+      <c r="A21" s="121"/>
       <c r="B21" s="17"/>
       <c r="C21" s="76"/>
       <c r="D21" s="17"/>
-      <c r="E21" s="110" t="s">
+      <c r="E21" s="106" t="s">
         <v>324</v>
       </c>
       <c r="F21" s="24"/>
@@ -9206,15 +9260,15 @@
         <v>3963</v>
       </c>
       <c r="J21" s="78"/>
-      <c r="K21" s="100">
+      <c r="K21" s="96">
         <f>G21</f>
         <v>320</v>
       </c>
       <c r="L21" s="78"/>
-      <c r="M21" s="105">
-        <v>0</v>
-      </c>
-      <c r="N21" s="105"/>
+      <c r="M21" s="101">
+        <v>0</v>
+      </c>
+      <c r="N21" s="101"/>
       <c r="O21" s="77">
         <v>0</v>
       </c>
@@ -9227,11 +9281,11 @@
       <c r="T21" s="1"/>
     </row>
     <row r="22" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="122"/>
+      <c r="A22" s="121"/>
       <c r="B22" s="17"/>
       <c r="C22" s="76"/>
       <c r="D22" s="17"/>
-      <c r="E22" s="113" t="s">
+      <c r="E22" s="109" t="s">
         <v>266</v>
       </c>
       <c r="F22" s="24"/>
@@ -9245,30 +9299,29 @@
       <c r="J22" s="78"/>
       <c r="K22" s="78"/>
       <c r="L22" s="78"/>
-      <c r="M22" s="115">
+      <c r="M22" s="111">
         <f t="shared" si="3"/>
         <v>280</v>
       </c>
-      <c r="N22" s="105" t="s">
+      <c r="N22" s="101" t="s">
         <v>294</v>
       </c>
-      <c r="O22" s="77">
-        <v>2000</v>
-      </c>
-      <c r="P22" s="77">
-        <f t="shared" si="1"/>
-        <v>-1720</v>
+      <c r="O22" s="77" t="s">
+        <v>353</v>
+      </c>
+      <c r="P22" s="77" t="s">
+        <v>353</v>
       </c>
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
     </row>
     <row r="23" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="123"/>
+      <c r="A23" s="122"/>
       <c r="B23" s="17"/>
       <c r="C23" s="76"/>
       <c r="D23" s="17"/>
-      <c r="E23" s="110" t="s">
+      <c r="E23" s="106" t="s">
         <v>336</v>
       </c>
       <c r="F23" s="24"/>
@@ -9280,15 +9333,15 @@
         <v>1913</v>
       </c>
       <c r="J23" s="78"/>
-      <c r="K23" s="100">
+      <c r="K23" s="96">
         <f>G23</f>
         <v>1770</v>
       </c>
       <c r="L23" s="78"/>
-      <c r="M23" s="105">
-        <v>0</v>
-      </c>
-      <c r="N23" s="105"/>
+      <c r="M23" s="101">
+        <v>0</v>
+      </c>
+      <c r="N23" s="101"/>
       <c r="O23" s="77">
         <v>0</v>
       </c>
@@ -9301,13 +9354,13 @@
       <c r="T23" s="1"/>
     </row>
     <row r="24" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="121">
+      <c r="A24" s="120">
         <v>46119</v>
       </c>
       <c r="B24" s="17"/>
       <c r="C24" s="76"/>
       <c r="D24" s="17"/>
-      <c r="E24" s="116" t="s">
+      <c r="E24" s="112" t="s">
         <v>325</v>
       </c>
       <c r="F24" s="24">
@@ -9323,30 +9376,30 @@
       <c r="J24" s="78"/>
       <c r="K24" s="78"/>
       <c r="L24" s="78"/>
-      <c r="M24" s="115">
+      <c r="M24" s="111">
         <f t="shared" si="3"/>
         <v>400</v>
       </c>
-      <c r="N24" s="105" t="s">
+      <c r="N24" s="101" t="s">
         <v>328</v>
       </c>
       <c r="O24" s="77">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="P24" s="77">
-        <f t="shared" si="1"/>
-        <v>400</v>
+        <f>O24-(M24+M25)</f>
+        <v>1228</v>
       </c>
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
       <c r="T24" s="1"/>
     </row>
     <row r="25" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="122"/>
+      <c r="A25" s="121"/>
       <c r="B25" s="17"/>
       <c r="C25" s="76"/>
       <c r="D25" s="17"/>
-      <c r="E25" s="116" t="s">
+      <c r="E25" s="112" t="s">
         <v>335</v>
       </c>
       <c r="F25" s="24"/>
@@ -9360,30 +9413,29 @@
       <c r="J25" s="78"/>
       <c r="K25" s="78"/>
       <c r="L25" s="78"/>
-      <c r="M25" s="115">
+      <c r="M25" s="111">
         <f t="shared" si="3"/>
         <v>72</v>
       </c>
-      <c r="N25" s="105" t="s">
+      <c r="N25" s="101" t="s">
         <v>328</v>
       </c>
-      <c r="O25" s="77">
-        <v>0</v>
-      </c>
-      <c r="P25" s="77">
-        <f t="shared" si="1"/>
-        <v>72</v>
+      <c r="O25" s="77" t="s">
+        <v>353</v>
+      </c>
+      <c r="P25" s="77" t="s">
+        <v>353</v>
       </c>
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
       <c r="T25" s="1"/>
     </row>
     <row r="26" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="122"/>
+      <c r="A26" s="121"/>
       <c r="B26" s="17"/>
       <c r="C26" s="76"/>
       <c r="D26" s="17"/>
-      <c r="E26" s="111" t="s">
+      <c r="E26" s="107" t="s">
         <v>267</v>
       </c>
       <c r="F26" s="24"/>
@@ -9394,16 +9446,16 @@
         <f t="shared" si="0"/>
         <v>941</v>
       </c>
-      <c r="J26" s="102">
+      <c r="J26" s="98">
         <f>G26</f>
         <v>500</v>
       </c>
       <c r="K26" s="78"/>
       <c r="L26" s="78"/>
-      <c r="M26" s="105">
-        <v>0</v>
-      </c>
-      <c r="N26" s="105"/>
+      <c r="M26" s="101">
+        <v>0</v>
+      </c>
+      <c r="N26" s="101"/>
       <c r="O26" s="77">
         <v>0</v>
       </c>
@@ -9416,11 +9468,11 @@
       <c r="T26" s="1"/>
     </row>
     <row r="27" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="122"/>
+      <c r="A27" s="121"/>
       <c r="B27" s="17"/>
       <c r="C27" s="76"/>
       <c r="D27" s="17"/>
-      <c r="E27" s="113" t="s">
+      <c r="E27" s="109" t="s">
         <v>326</v>
       </c>
       <c r="F27" s="24"/>
@@ -9434,30 +9486,30 @@
       <c r="J27" s="78"/>
       <c r="K27" s="78"/>
       <c r="L27" s="78"/>
-      <c r="M27" s="115">
+      <c r="M27" s="111">
         <f>G27</f>
         <v>180</v>
       </c>
-      <c r="N27" s="105" t="s">
+      <c r="N27" s="101" t="s">
         <v>296</v>
       </c>
       <c r="O27" s="77">
         <v>2000</v>
       </c>
       <c r="P27" s="77">
-        <f t="shared" si="1"/>
-        <v>-1820</v>
+        <f>O27-M27</f>
+        <v>1820</v>
       </c>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
       <c r="T27" s="1"/>
     </row>
     <row r="28" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="122"/>
+      <c r="A28" s="121"/>
       <c r="B28" s="17"/>
       <c r="C28" s="76"/>
       <c r="D28" s="17"/>
-      <c r="E28" s="110" t="s">
+      <c r="E28" s="106" t="s">
         <v>268</v>
       </c>
       <c r="F28" s="24"/>
@@ -9469,15 +9521,15 @@
         <v>-377</v>
       </c>
       <c r="J28" s="78"/>
-      <c r="K28" s="100">
+      <c r="K28" s="96">
         <f>G28</f>
         <v>1138</v>
       </c>
       <c r="L28" s="78"/>
-      <c r="M28" s="105">
-        <v>0</v>
-      </c>
-      <c r="N28" s="105"/>
+      <c r="M28" s="101">
+        <v>0</v>
+      </c>
+      <c r="N28" s="101"/>
       <c r="O28" s="77">
         <v>0</v>
       </c>
@@ -9490,11 +9542,11 @@
       <c r="T28" s="1"/>
     </row>
     <row r="29" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="123"/>
+      <c r="A29" s="122"/>
       <c r="B29" s="17"/>
       <c r="C29" s="76"/>
       <c r="D29" s="17"/>
-      <c r="E29" s="113" t="s">
+      <c r="E29" s="109" t="s">
         <v>269</v>
       </c>
       <c r="F29" s="24"/>
@@ -9508,32 +9560,31 @@
       <c r="J29" s="78"/>
       <c r="K29" s="78"/>
       <c r="L29" s="78"/>
-      <c r="M29" s="115">
+      <c r="M29" s="111">
         <f>G29</f>
         <v>300</v>
       </c>
-      <c r="N29" s="105" t="s">
+      <c r="N29" s="101" t="s">
         <v>294</v>
       </c>
-      <c r="O29" s="77">
-        <v>2000</v>
-      </c>
-      <c r="P29" s="77">
-        <f t="shared" si="1"/>
-        <v>-1700</v>
+      <c r="O29" s="77" t="s">
+        <v>353</v>
+      </c>
+      <c r="P29" s="77" t="s">
+        <v>353</v>
       </c>
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
       <c r="T29" s="1"/>
     </row>
     <row r="30" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="121">
+      <c r="A30" s="120">
         <v>46120</v>
       </c>
       <c r="B30" s="18"/>
       <c r="C30" s="76"/>
       <c r="D30" s="17"/>
-      <c r="E30" s="112" t="s">
+      <c r="E30" s="108" t="s">
         <v>270</v>
       </c>
       <c r="F30" s="24"/>
@@ -9546,14 +9597,14 @@
       </c>
       <c r="J30" s="78"/>
       <c r="K30" s="78"/>
-      <c r="L30" s="98">
+      <c r="L30" s="94">
         <f>G30</f>
         <v>197</v>
       </c>
-      <c r="M30" s="105">
-        <v>0</v>
-      </c>
-      <c r="N30" s="105"/>
+      <c r="M30" s="101">
+        <v>0</v>
+      </c>
+      <c r="N30" s="101"/>
       <c r="O30" s="77">
         <v>0</v>
       </c>
@@ -9566,11 +9617,11 @@
       <c r="T30" s="1"/>
     </row>
     <row r="31" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="122"/>
+      <c r="A31" s="121"/>
       <c r="B31" s="17"/>
       <c r="C31" s="76"/>
       <c r="D31" s="17"/>
-      <c r="E31" s="113" t="s">
+      <c r="E31" s="109" t="s">
         <v>271</v>
       </c>
       <c r="F31" s="24"/>
@@ -9584,30 +9635,29 @@
       <c r="J31" s="78"/>
       <c r="K31" s="78"/>
       <c r="L31" s="78"/>
-      <c r="M31" s="115">
+      <c r="M31" s="111">
         <f>G31</f>
         <v>550</v>
       </c>
-      <c r="N31" s="105" t="s">
+      <c r="N31" s="101" t="s">
         <v>294</v>
       </c>
-      <c r="O31" s="77">
-        <v>2000</v>
-      </c>
-      <c r="P31" s="77">
-        <f t="shared" si="1"/>
-        <v>-1450</v>
+      <c r="O31" s="77" t="s">
+        <v>353</v>
+      </c>
+      <c r="P31" s="77" t="s">
+        <v>353</v>
       </c>
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
       <c r="T31" s="1"/>
     </row>
     <row r="32" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="122"/>
+      <c r="A32" s="121"/>
       <c r="B32" s="17"/>
       <c r="C32" s="76"/>
       <c r="D32" s="17"/>
-      <c r="E32" s="113" t="s">
+      <c r="E32" s="109" t="s">
         <v>272</v>
       </c>
       <c r="F32" s="24"/>
@@ -9621,30 +9671,30 @@
       <c r="J32" s="78"/>
       <c r="K32" s="78"/>
       <c r="L32" s="78"/>
-      <c r="M32" s="115">
+      <c r="M32" s="111">
         <f>G32</f>
         <v>150</v>
       </c>
-      <c r="N32" s="105" t="s">
+      <c r="N32" s="101" t="s">
         <v>297</v>
       </c>
       <c r="O32" s="77">
         <v>2000</v>
       </c>
       <c r="P32" s="77">
-        <f t="shared" si="1"/>
-        <v>-1850</v>
+        <f>O32-M32</f>
+        <v>1850</v>
       </c>
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
       <c r="T32" s="1"/>
     </row>
     <row r="33" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="123"/>
+      <c r="A33" s="122"/>
       <c r="B33" s="17"/>
       <c r="C33" s="76"/>
       <c r="D33" s="17"/>
-      <c r="E33" s="113" t="s">
+      <c r="E33" s="109" t="s">
         <v>327</v>
       </c>
       <c r="F33" s="24"/>
@@ -9658,32 +9708,32 @@
       <c r="J33" s="78"/>
       <c r="K33" s="78"/>
       <c r="L33" s="78"/>
-      <c r="M33" s="115">
+      <c r="M33" s="111">
         <f>G33</f>
         <v>290</v>
       </c>
-      <c r="N33" s="105" t="s">
+      <c r="N33" s="101" t="s">
         <v>298</v>
       </c>
       <c r="O33" s="77">
-        <v>2000</v>
+        <v>5600</v>
       </c>
       <c r="P33" s="77">
-        <f t="shared" si="1"/>
-        <v>-1710</v>
+        <f>O33-(M33+M38)</f>
+        <v>4960</v>
       </c>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
       <c r="T33" s="1"/>
     </row>
     <row r="34" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="121">
+      <c r="A34" s="120">
         <v>46121</v>
       </c>
       <c r="B34" s="17"/>
       <c r="C34" s="76"/>
       <c r="D34" s="17"/>
-      <c r="E34" s="119" t="s">
+      <c r="E34" s="115" t="s">
         <v>274</v>
       </c>
       <c r="F34" s="24"/>
@@ -9696,14 +9746,14 @@
       </c>
       <c r="J34" s="78"/>
       <c r="K34" s="78"/>
-      <c r="L34" s="98">
+      <c r="L34" s="94">
         <f>G34</f>
         <v>224</v>
       </c>
-      <c r="M34" s="105">
-        <v>0</v>
-      </c>
-      <c r="N34" s="105"/>
+      <c r="M34" s="101">
+        <v>0</v>
+      </c>
+      <c r="N34" s="101"/>
       <c r="O34" s="77">
         <v>0</v>
       </c>
@@ -9716,11 +9766,11 @@
       <c r="T34" s="1"/>
     </row>
     <row r="35" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="123"/>
+      <c r="A35" s="122"/>
       <c r="B35" s="17"/>
       <c r="C35" s="76"/>
       <c r="D35" s="17"/>
-      <c r="E35" s="113" t="s">
+      <c r="E35" s="109" t="s">
         <v>332</v>
       </c>
       <c r="F35" s="24"/>
@@ -9734,10 +9784,10 @@
       <c r="J35" s="78"/>
       <c r="K35" s="78"/>
       <c r="L35" s="78"/>
-      <c r="M35" s="105">
-        <v>0</v>
-      </c>
-      <c r="N35" s="105"/>
+      <c r="M35" s="101">
+        <v>0</v>
+      </c>
+      <c r="N35" s="101"/>
       <c r="O35" s="77">
         <v>0</v>
       </c>
@@ -9762,7 +9812,7 @@
       <c r="D36" s="17" t="s">
         <v>262</v>
       </c>
-      <c r="E36" s="119" t="s">
+      <c r="E36" s="115" t="s">
         <v>273</v>
       </c>
       <c r="F36" s="24">
@@ -9777,14 +9827,14 @@
       </c>
       <c r="J36" s="78"/>
       <c r="K36" s="78"/>
-      <c r="L36" s="98">
+      <c r="L36" s="94">
         <f>G36</f>
         <v>192</v>
       </c>
-      <c r="M36" s="105">
-        <v>0</v>
-      </c>
-      <c r="N36" s="105"/>
+      <c r="M36" s="101">
+        <v>0</v>
+      </c>
+      <c r="N36" s="101"/>
       <c r="O36" s="77">
         <v>0</v>
       </c>
@@ -9797,13 +9847,13 @@
       <c r="T36" s="1"/>
     </row>
     <row r="37" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="121">
+      <c r="A37" s="120">
         <v>46123</v>
       </c>
       <c r="B37" s="17"/>
       <c r="C37" s="76"/>
       <c r="D37" s="17"/>
-      <c r="E37" s="119" t="s">
+      <c r="E37" s="115" t="s">
         <v>270</v>
       </c>
       <c r="F37" s="24"/>
@@ -9816,14 +9866,14 @@
       </c>
       <c r="J37" s="78"/>
       <c r="K37" s="78"/>
-      <c r="L37" s="98">
+      <c r="L37" s="94">
         <f>G37</f>
         <v>704</v>
       </c>
-      <c r="M37" s="105">
-        <v>0</v>
-      </c>
-      <c r="N37" s="105"/>
+      <c r="M37" s="101">
+        <v>0</v>
+      </c>
+      <c r="N37" s="101"/>
       <c r="O37" s="77">
         <v>0</v>
       </c>
@@ -9836,11 +9886,11 @@
       <c r="T37" s="1"/>
     </row>
     <row r="38" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="122"/>
+      <c r="A38" s="121"/>
       <c r="B38" s="17"/>
       <c r="C38" s="76"/>
       <c r="D38" s="17"/>
-      <c r="E38" s="113" t="s">
+      <c r="E38" s="109" t="s">
         <v>275</v>
       </c>
       <c r="F38" s="24"/>
@@ -9854,30 +9904,29 @@
       <c r="J38" s="78"/>
       <c r="K38" s="78"/>
       <c r="L38" s="78"/>
-      <c r="M38" s="115">
+      <c r="M38" s="111">
         <f>G38</f>
         <v>350</v>
       </c>
-      <c r="N38" s="105" t="s">
+      <c r="N38" s="101" t="s">
         <v>298</v>
       </c>
-      <c r="O38" s="77">
-        <v>2000</v>
-      </c>
-      <c r="P38" s="77">
-        <f t="shared" si="1"/>
-        <v>-1650</v>
+      <c r="O38" s="77" t="s">
+        <v>353</v>
+      </c>
+      <c r="P38" s="77" t="s">
+        <v>353</v>
       </c>
       <c r="R38" s="1"/>
       <c r="S38" s="1"/>
       <c r="T38" s="1"/>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A39" s="123"/>
+      <c r="A39" s="122"/>
       <c r="B39" s="25"/>
       <c r="C39" s="77"/>
       <c r="D39" s="11"/>
-      <c r="E39" s="116" t="s">
+      <c r="E39" s="112" t="s">
         <v>329</v>
       </c>
       <c r="F39" s="24"/>
@@ -9891,19 +9940,19 @@
       <c r="J39" s="78"/>
       <c r="K39" s="78"/>
       <c r="L39" s="78"/>
-      <c r="M39" s="115">
+      <c r="M39" s="111">
         <f>G39</f>
         <v>400</v>
       </c>
-      <c r="N39" s="105" t="s">
+      <c r="N39" s="101" t="s">
         <v>301</v>
       </c>
       <c r="O39" s="77">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="P39" s="77">
-        <f t="shared" si="1"/>
-        <v>400</v>
+        <f>O39-(M39:M56)</f>
+        <v>1100</v>
       </c>
       <c r="R39" s="1"/>
     </row>
@@ -9914,7 +9963,7 @@
       <c r="B40" s="18"/>
       <c r="C40" s="76"/>
       <c r="D40" s="17"/>
-      <c r="E40" s="113" t="s">
+      <c r="E40" s="109" t="s">
         <v>330</v>
       </c>
       <c r="F40" s="24"/>
@@ -9928,18 +9977,18 @@
       <c r="J40" s="78"/>
       <c r="K40" s="78"/>
       <c r="L40" s="78"/>
-      <c r="M40" s="105">
-        <v>0</v>
-      </c>
-      <c r="N40" s="105" t="s">
+      <c r="M40" s="111">
+        <f>G40</f>
+        <v>130</v>
+      </c>
+      <c r="N40" s="101" t="s">
         <v>301</v>
       </c>
-      <c r="O40" s="77">
-        <v>0</v>
-      </c>
-      <c r="P40" s="77">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="O40" s="77" t="s">
+        <v>353</v>
+      </c>
+      <c r="P40" s="77" t="s">
+        <v>353</v>
       </c>
       <c r="R40" s="1"/>
     </row>
@@ -9950,7 +9999,7 @@
       <c r="B41" s="25"/>
       <c r="C41" s="77"/>
       <c r="D41" s="11"/>
-      <c r="E41" s="119" t="s">
+      <c r="E41" s="115" t="s">
         <v>270</v>
       </c>
       <c r="F41" s="24"/>
@@ -9963,14 +10012,14 @@
       </c>
       <c r="J41" s="78"/>
       <c r="K41" s="78"/>
-      <c r="L41" s="98">
+      <c r="L41" s="94">
         <f>G41</f>
         <v>167</v>
       </c>
-      <c r="M41" s="105">
-        <v>0</v>
-      </c>
-      <c r="N41" s="105"/>
+      <c r="M41" s="101">
+        <v>0</v>
+      </c>
+      <c r="N41" s="101"/>
       <c r="O41" s="77">
         <v>0</v>
       </c>
@@ -9981,7 +10030,7 @@
       <c r="R41" s="1"/>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A42" s="121">
+      <c r="A42" s="120">
         <v>46126</v>
       </c>
       <c r="B42" s="25" t="s">
@@ -9993,7 +10042,7 @@
       <c r="D42" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="E42" s="113" t="s">
+      <c r="E42" s="109" t="s">
         <v>276</v>
       </c>
       <c r="F42" s="24">
@@ -10009,11 +10058,11 @@
       <c r="J42" s="78"/>
       <c r="K42" s="78"/>
       <c r="L42" s="78"/>
-      <c r="M42" s="115">
+      <c r="M42" s="111">
         <f>G42</f>
         <v>320</v>
       </c>
-      <c r="N42" s="105" t="s">
+      <c r="N42" s="101" t="s">
         <v>299</v>
       </c>
       <c r="O42" s="77">
@@ -10026,11 +10075,11 @@
       <c r="R42" s="1"/>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A43" s="122"/>
+      <c r="A43" s="121"/>
       <c r="B43" s="25"/>
       <c r="C43" s="77"/>
       <c r="D43" s="11"/>
-      <c r="E43" s="113" t="s">
+      <c r="E43" s="109" t="s">
         <v>331</v>
       </c>
       <c r="F43" s="24"/>
@@ -10044,28 +10093,28 @@
       <c r="J43" s="78"/>
       <c r="K43" s="78"/>
       <c r="L43" s="78"/>
-      <c r="M43" s="115">
+      <c r="M43" s="111">
         <f>G43</f>
         <v>2080</v>
       </c>
-      <c r="N43" s="105" t="s">
+      <c r="N43" s="101" t="s">
         <v>277</v>
       </c>
       <c r="O43" s="77">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="P43" s="77">
-        <f t="shared" si="1"/>
-        <v>80</v>
+        <f>O43-(M43)</f>
+        <v>920</v>
       </c>
       <c r="R43" s="1"/>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A44" s="122"/>
+      <c r="A44" s="121"/>
       <c r="B44" s="17"/>
       <c r="C44" s="76"/>
       <c r="D44" s="17"/>
-      <c r="E44" s="113" t="s">
+      <c r="E44" s="109" t="s">
         <v>278</v>
       </c>
       <c r="F44" s="24"/>
@@ -10079,28 +10128,28 @@
       <c r="J44" s="78"/>
       <c r="K44" s="78"/>
       <c r="L44" s="78"/>
-      <c r="M44" s="115">
+      <c r="M44" s="111">
         <f t="shared" ref="M44:M46" si="4">G44</f>
         <v>390</v>
       </c>
-      <c r="N44" s="105" t="s">
+      <c r="N44" s="101" t="s">
         <v>300</v>
       </c>
       <c r="O44" s="77">
         <v>2000</v>
       </c>
       <c r="P44" s="77">
-        <f t="shared" si="1"/>
-        <v>-1610</v>
+        <f>O44-M44</f>
+        <v>1610</v>
       </c>
       <c r="R44" s="1"/>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A45" s="122"/>
+      <c r="A45" s="121"/>
       <c r="B45" s="17"/>
       <c r="C45" s="76"/>
       <c r="D45" s="17"/>
-      <c r="E45" s="113" t="s">
+      <c r="E45" s="109" t="s">
         <v>279</v>
       </c>
       <c r="F45" s="24"/>
@@ -10114,28 +10163,27 @@
       <c r="J45" s="78"/>
       <c r="K45" s="78"/>
       <c r="L45" s="78"/>
-      <c r="M45" s="115">
+      <c r="M45" s="111">
         <f t="shared" si="4"/>
         <v>700</v>
       </c>
-      <c r="N45" s="105" t="s">
+      <c r="N45" s="101" t="s">
         <v>294</v>
       </c>
-      <c r="O45" s="77">
-        <v>2000</v>
-      </c>
-      <c r="P45" s="77">
-        <f t="shared" si="1"/>
-        <v>-1300</v>
+      <c r="O45" s="77" t="s">
+        <v>353</v>
+      </c>
+      <c r="P45" s="77" t="s">
+        <v>353</v>
       </c>
       <c r="R45" s="1"/>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A46" s="122"/>
+      <c r="A46" s="121"/>
       <c r="B46" s="17"/>
       <c r="C46" s="77"/>
       <c r="D46" s="11"/>
-      <c r="E46" s="113" t="s">
+      <c r="E46" s="109" t="s">
         <v>271</v>
       </c>
       <c r="F46" s="24"/>
@@ -10149,30 +10197,29 @@
       <c r="J46" s="78"/>
       <c r="K46" s="78"/>
       <c r="L46" s="78"/>
-      <c r="M46" s="115">
+      <c r="M46" s="111">
         <f t="shared" si="4"/>
         <v>900</v>
       </c>
-      <c r="N46" s="105" t="s">
+      <c r="N46" s="101" t="s">
         <v>294</v>
       </c>
-      <c r="O46" s="77">
-        <v>2000</v>
-      </c>
-      <c r="P46" s="77">
-        <f t="shared" si="1"/>
-        <v>-1100</v>
+      <c r="O46" s="77" t="s">
+        <v>353</v>
+      </c>
+      <c r="P46" s="77" t="s">
+        <v>353</v>
       </c>
       <c r="R46" s="1"/>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A47" s="122"/>
+      <c r="A47" s="121"/>
       <c r="B47" s="17"/>
       <c r="C47" s="77"/>
       <c r="D47" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="E47" s="110" t="s">
+      <c r="E47" s="106" t="s">
         <v>280</v>
       </c>
       <c r="F47" s="24"/>
@@ -10183,16 +10230,16 @@
         <f t="shared" si="0"/>
         <v>5589</v>
       </c>
-      <c r="J47" s="102">
+      <c r="J47" s="98">
         <f>G47</f>
         <v>730</v>
       </c>
       <c r="K47" s="78"/>
       <c r="L47" s="78"/>
-      <c r="M47" s="105">
-        <v>0</v>
-      </c>
-      <c r="N47" s="105"/>
+      <c r="M47" s="101">
+        <v>0</v>
+      </c>
+      <c r="N47" s="101"/>
       <c r="O47" s="77">
         <v>0</v>
       </c>
@@ -10203,20 +10250,20 @@
       <c r="R47" s="1"/>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A48" s="122"/>
-      <c r="B48" s="89" t="s">
+      <c r="A48" s="121"/>
+      <c r="B48" s="86" t="s">
         <v>282</v>
       </c>
-      <c r="C48" s="90" t="s">
+      <c r="C48" s="87" t="s">
         <v>7</v>
       </c>
       <c r="D48" s="57" t="s">
         <v>283</v>
       </c>
-      <c r="E48" s="111" t="s">
+      <c r="E48" s="107" t="s">
         <v>289</v>
       </c>
-      <c r="F48" s="91">
+      <c r="F48" s="88">
         <v>1000</v>
       </c>
       <c r="G48" s="32">
@@ -10226,16 +10273,16 @@
         <f t="shared" si="0"/>
         <v>5869</v>
       </c>
-      <c r="J48" s="102">
+      <c r="J48" s="98">
         <f>G48</f>
         <v>720</v>
       </c>
       <c r="K48" s="78"/>
       <c r="L48" s="78"/>
-      <c r="M48" s="105">
-        <v>0</v>
-      </c>
-      <c r="N48" s="105"/>
+      <c r="M48" s="101">
+        <v>0</v>
+      </c>
+      <c r="N48" s="101"/>
       <c r="O48" s="77">
         <v>0</v>
       </c>
@@ -10246,15 +10293,15 @@
       <c r="R48" s="1"/>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A49" s="123"/>
+      <c r="A49" s="122"/>
       <c r="B49" s="18"/>
       <c r="C49" s="76"/>
       <c r="D49" s="18"/>
-      <c r="E49" s="93" t="s">
+      <c r="E49" s="90" t="s">
         <v>340</v>
       </c>
       <c r="F49" s="24"/>
-      <c r="G49" s="118">
+      <c r="G49" s="114">
         <v>124</v>
       </c>
       <c r="H49" s="47">
@@ -10264,10 +10311,10 @@
       <c r="J49" s="78"/>
       <c r="K49" s="78"/>
       <c r="L49" s="78"/>
-      <c r="M49" s="105">
-        <v>0</v>
-      </c>
-      <c r="N49" s="105"/>
+      <c r="M49" s="101">
+        <v>0</v>
+      </c>
+      <c r="N49" s="101"/>
       <c r="O49" s="77">
         <v>0</v>
       </c>
@@ -10284,7 +10331,7 @@
       <c r="B50" s="18"/>
       <c r="C50" s="76"/>
       <c r="D50" s="18"/>
-      <c r="E50" s="119" t="s">
+      <c r="E50" s="115" t="s">
         <v>311</v>
       </c>
       <c r="F50" s="24"/>
@@ -10297,14 +10344,14 @@
       </c>
       <c r="J50" s="78"/>
       <c r="K50" s="78"/>
-      <c r="L50" s="98">
+      <c r="L50" s="94">
         <f t="shared" ref="L50:L51" si="5">G50</f>
         <v>1000</v>
       </c>
-      <c r="M50" s="105">
-        <v>0</v>
-      </c>
-      <c r="N50" s="105"/>
+      <c r="M50" s="101">
+        <v>0</v>
+      </c>
+      <c r="N50" s="101"/>
       <c r="O50" s="77">
         <v>0</v>
       </c>
@@ -10315,13 +10362,13 @@
       <c r="R50" s="1"/>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A51" s="121">
+      <c r="A51" s="120">
         <v>46128</v>
       </c>
       <c r="B51" s="17"/>
       <c r="C51" s="76"/>
       <c r="D51" s="18"/>
-      <c r="E51" s="119" t="s">
+      <c r="E51" s="115" t="s">
         <v>317</v>
       </c>
       <c r="F51" s="24"/>
@@ -10334,14 +10381,14 @@
       </c>
       <c r="J51" s="78"/>
       <c r="K51" s="78"/>
-      <c r="L51" s="98">
+      <c r="L51" s="94">
         <f t="shared" si="5"/>
         <v>168</v>
       </c>
-      <c r="M51" s="105">
-        <v>0</v>
-      </c>
-      <c r="N51" s="105"/>
+      <c r="M51" s="101">
+        <v>0</v>
+      </c>
+      <c r="N51" s="101"/>
       <c r="O51" s="77">
         <v>0</v>
       </c>
@@ -10352,11 +10399,11 @@
       <c r="R51" s="1"/>
     </row>
     <row r="52" spans="1:18" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A52" s="122"/>
+      <c r="A52" s="121"/>
       <c r="B52" s="18"/>
       <c r="C52" s="76"/>
       <c r="D52" s="18"/>
-      <c r="E52" s="111" t="s">
+      <c r="E52" s="107" t="s">
         <v>281</v>
       </c>
       <c r="F52" s="24"/>
@@ -10367,16 +10414,16 @@
         <f t="shared" si="0"/>
         <v>2477</v>
       </c>
-      <c r="J52" s="102">
+      <c r="J52" s="98">
         <f>G52</f>
         <v>2100</v>
       </c>
       <c r="K52" s="78"/>
       <c r="L52" s="78"/>
-      <c r="M52" s="105">
-        <v>0</v>
-      </c>
-      <c r="N52" s="105"/>
+      <c r="M52" s="101">
+        <v>0</v>
+      </c>
+      <c r="N52" s="101"/>
       <c r="O52" s="77">
         <v>0</v>
       </c>
@@ -10387,11 +10434,11 @@
       <c r="R52" s="1"/>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A53" s="122"/>
+      <c r="A53" s="121"/>
       <c r="B53" s="18"/>
       <c r="C53" s="76"/>
       <c r="D53" s="18"/>
-      <c r="E53" s="119" t="s">
+      <c r="E53" s="115" t="s">
         <v>290</v>
       </c>
       <c r="F53" s="24"/>
@@ -10404,14 +10451,14 @@
       </c>
       <c r="J53" s="78"/>
       <c r="K53" s="78"/>
-      <c r="L53" s="98">
+      <c r="L53" s="94">
         <f>G53</f>
         <v>30</v>
       </c>
-      <c r="M53" s="105">
-        <v>0</v>
-      </c>
-      <c r="N53" s="105"/>
+      <c r="M53" s="101">
+        <v>0</v>
+      </c>
+      <c r="N53" s="101"/>
       <c r="O53" s="77">
         <v>0</v>
       </c>
@@ -10422,11 +10469,11 @@
       <c r="R53" s="1"/>
     </row>
     <row r="54" spans="1:18" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A54" s="122"/>
+      <c r="A54" s="121"/>
       <c r="B54" s="17"/>
       <c r="C54" s="76"/>
       <c r="D54" s="17"/>
-      <c r="E54" s="94" t="s">
+      <c r="E54" s="91" t="s">
         <v>284</v>
       </c>
       <c r="F54" s="31">
@@ -10442,10 +10489,10 @@
       <c r="J54" s="78"/>
       <c r="K54" s="78"/>
       <c r="L54" s="78"/>
-      <c r="M54" s="105">
-        <v>0</v>
-      </c>
-      <c r="N54" s="105"/>
+      <c r="M54" s="101">
+        <v>0</v>
+      </c>
+      <c r="N54" s="101"/>
       <c r="O54" s="77">
         <v>0</v>
       </c>
@@ -10456,13 +10503,13 @@
       <c r="R54" s="1"/>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A55" s="121">
+      <c r="A55" s="120">
         <v>46130</v>
       </c>
       <c r="B55" s="18"/>
       <c r="C55" s="76"/>
       <c r="D55" s="18"/>
-      <c r="E55" s="113" t="s">
+      <c r="E55" s="109" t="s">
         <v>285</v>
       </c>
       <c r="F55" s="24"/>
@@ -10476,28 +10523,27 @@
       <c r="J55" s="78"/>
       <c r="K55" s="78"/>
       <c r="L55" s="78"/>
-      <c r="M55" s="115">
+      <c r="M55" s="111">
         <f t="shared" ref="M55:M56" si="6">G55</f>
         <v>1200</v>
       </c>
-      <c r="N55" s="105" t="s">
+      <c r="N55" s="101" t="s">
         <v>301</v>
       </c>
-      <c r="O55" s="77">
-        <v>2000</v>
-      </c>
-      <c r="P55" s="77">
-        <f t="shared" si="1"/>
-        <v>-800</v>
+      <c r="O55" s="77" t="s">
+        <v>353</v>
+      </c>
+      <c r="P55" s="77" t="s">
+        <v>353</v>
       </c>
       <c r="R55" s="1"/>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A56" s="122"/>
+      <c r="A56" s="121"/>
       <c r="B56" s="17"/>
       <c r="C56" s="76"/>
       <c r="D56" s="17"/>
-      <c r="E56" s="113" t="s">
+      <c r="E56" s="109" t="s">
         <v>286</v>
       </c>
       <c r="F56" s="24"/>
@@ -10511,36 +10557,35 @@
       <c r="J56" s="78"/>
       <c r="K56" s="78"/>
       <c r="L56" s="78"/>
-      <c r="M56" s="115">
+      <c r="M56" s="111">
         <f t="shared" si="6"/>
         <v>450</v>
       </c>
-      <c r="N56" s="105" t="s">
+      <c r="N56" s="101" t="s">
         <v>301</v>
       </c>
-      <c r="O56" s="77">
-        <v>2000</v>
-      </c>
-      <c r="P56" s="77">
-        <f t="shared" si="1"/>
-        <v>-1550</v>
+      <c r="O56" s="77" t="s">
+        <v>353</v>
+      </c>
+      <c r="P56" s="77" t="s">
+        <v>353</v>
       </c>
       <c r="R56" s="1"/>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A57" s="122"/>
+      <c r="A57" s="121"/>
       <c r="B57" s="18"/>
       <c r="C57" s="76"/>
       <c r="D57" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="E57" s="93" t="s">
+      <c r="E57" s="90" t="s">
         <v>287</v>
       </c>
       <c r="F57" s="24">
         <v>0</v>
       </c>
-      <c r="G57" s="120">
+      <c r="G57" s="116">
         <v>104</v>
       </c>
       <c r="H57" s="47">
@@ -10550,10 +10595,10 @@
       <c r="J57" s="78"/>
       <c r="K57" s="78"/>
       <c r="L57" s="78"/>
-      <c r="M57" s="105">
-        <v>0</v>
-      </c>
-      <c r="N57" s="105"/>
+      <c r="M57" s="101">
+        <v>0</v>
+      </c>
+      <c r="N57" s="101"/>
       <c r="O57" s="77">
         <v>0</v>
       </c>
@@ -10564,11 +10609,11 @@
       <c r="R57" s="1"/>
     </row>
     <row r="58" spans="1:18" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A58" s="122"/>
+      <c r="A58" s="121"/>
       <c r="B58" s="17"/>
       <c r="C58" s="76"/>
       <c r="D58" s="17"/>
-      <c r="E58" s="111" t="s">
+      <c r="E58" s="107" t="s">
         <v>288</v>
       </c>
       <c r="F58" s="24">
@@ -10581,16 +10626,16 @@
         <f t="shared" si="0"/>
         <v>1545</v>
       </c>
-      <c r="J58" s="102">
+      <c r="J58" s="98">
         <f>G58</f>
         <v>1950</v>
       </c>
       <c r="K58" s="78"/>
       <c r="L58" s="78"/>
-      <c r="M58" s="105">
-        <v>0</v>
-      </c>
-      <c r="N58" s="105"/>
+      <c r="M58" s="101">
+        <v>0</v>
+      </c>
+      <c r="N58" s="101"/>
       <c r="O58" s="77">
         <v>0</v>
       </c>
@@ -10601,13 +10646,13 @@
       <c r="R58" s="1"/>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A59" s="84">
+      <c r="A59" s="83">
         <v>46131</v>
       </c>
       <c r="B59" s="18"/>
       <c r="C59" s="76"/>
       <c r="D59" s="18"/>
-      <c r="E59" s="119" t="s">
+      <c r="E59" s="115" t="s">
         <v>309</v>
       </c>
       <c r="F59" s="24"/>
@@ -10620,14 +10665,14 @@
       </c>
       <c r="J59" s="78"/>
       <c r="K59" s="78"/>
-      <c r="L59" s="98">
+      <c r="L59" s="94">
         <f>G59</f>
         <v>64</v>
       </c>
-      <c r="M59" s="105">
-        <v>0</v>
-      </c>
-      <c r="N59" s="105"/>
+      <c r="M59" s="101">
+        <v>0</v>
+      </c>
+      <c r="N59" s="101"/>
       <c r="O59" s="77">
         <v>0</v>
       </c>
@@ -10638,7 +10683,7 @@
       <c r="R59" s="1"/>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A60" s="121">
+      <c r="A60" s="120">
         <v>46132</v>
       </c>
       <c r="B60" s="25" t="s">
@@ -10650,7 +10695,7 @@
       <c r="D60" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="E60" s="119" t="s">
+      <c r="E60" s="115" t="s">
         <v>318</v>
       </c>
       <c r="F60" s="24">
@@ -10666,10 +10711,10 @@
       <c r="J60" s="78"/>
       <c r="K60" s="78"/>
       <c r="L60" s="78"/>
-      <c r="M60" s="105">
-        <v>0</v>
-      </c>
-      <c r="N60" s="105"/>
+      <c r="M60" s="101">
+        <v>0</v>
+      </c>
+      <c r="N60" s="101"/>
       <c r="O60" s="77">
         <v>0</v>
       </c>
@@ -10680,11 +10725,11 @@
       <c r="R60" s="1"/>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A61" s="122"/>
+      <c r="A61" s="121"/>
       <c r="B61" s="18"/>
       <c r="C61" s="76"/>
       <c r="D61" s="18"/>
-      <c r="E61" s="113" t="s">
+      <c r="E61" s="109" t="s">
         <v>347</v>
       </c>
       <c r="F61" s="24"/>
@@ -10698,11 +10743,11 @@
       <c r="J61" s="78"/>
       <c r="K61" s="78"/>
       <c r="L61" s="78"/>
-      <c r="M61" s="115">
+      <c r="M61" s="111">
         <f t="shared" ref="M61" si="7">G61</f>
         <v>152</v>
       </c>
-      <c r="N61" s="105" t="s">
+      <c r="N61" s="101" t="s">
         <v>343</v>
       </c>
       <c r="O61" s="77">
@@ -10715,11 +10760,11 @@
       <c r="R61" s="1"/>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A62" s="122"/>
+      <c r="A62" s="121"/>
       <c r="B62" s="10"/>
       <c r="C62" s="78"/>
       <c r="D62" s="10"/>
-      <c r="E62" s="113" t="s">
+      <c r="E62" s="109" t="s">
         <v>345</v>
       </c>
       <c r="F62" s="24"/>
@@ -10733,11 +10778,11 @@
       <c r="J62" s="78"/>
       <c r="K62" s="78"/>
       <c r="L62" s="78"/>
-      <c r="M62" s="115">
-        <f t="shared" ref="M62:M67" si="8">G62</f>
+      <c r="M62" s="111">
+        <f t="shared" ref="M62:M80" si="8">G62</f>
         <v>447</v>
       </c>
-      <c r="N62" s="105" t="s">
+      <c r="N62" s="101" t="s">
         <v>344</v>
       </c>
       <c r="O62" s="77">
@@ -10750,11 +10795,11 @@
       <c r="R62" s="1"/>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A63" s="122"/>
+      <c r="A63" s="121"/>
       <c r="B63" s="10"/>
       <c r="C63" s="78"/>
       <c r="D63" s="10"/>
-      <c r="E63" s="113" t="s">
+      <c r="E63" s="109" t="s">
         <v>346</v>
       </c>
       <c r="F63" s="24"/>
@@ -10768,11 +10813,11 @@
       <c r="J63" s="78"/>
       <c r="K63" s="78"/>
       <c r="L63" s="78"/>
-      <c r="M63" s="115">
+      <c r="M63" s="111">
         <f t="shared" si="8"/>
         <v>74</v>
       </c>
-      <c r="N63" s="105"/>
+      <c r="N63" s="101"/>
       <c r="O63" s="77">
         <v>0</v>
       </c>
@@ -10783,11 +10828,11 @@
       <c r="R63" s="1"/>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A64" s="122"/>
+      <c r="A64" s="121"/>
       <c r="B64" s="10"/>
       <c r="C64" s="78"/>
       <c r="D64" s="10"/>
-      <c r="E64" s="94" t="s">
+      <c r="E64" s="91" t="s">
         <v>341</v>
       </c>
       <c r="F64" s="24"/>
@@ -10800,14 +10845,14 @@
       </c>
       <c r="J64" s="78"/>
       <c r="K64" s="78"/>
-      <c r="L64" s="98">
+      <c r="L64" s="94">
         <f>G64</f>
         <v>140</v>
       </c>
-      <c r="M64" s="105">
-        <v>0</v>
-      </c>
-      <c r="N64" s="105" t="s">
+      <c r="M64" s="101">
+        <v>0</v>
+      </c>
+      <c r="N64" s="101" t="s">
         <v>342</v>
       </c>
       <c r="O64" s="77">
@@ -10820,11 +10865,11 @@
       <c r="R64" s="1"/>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A65" s="122"/>
+      <c r="A65" s="121"/>
       <c r="B65" s="10"/>
       <c r="C65" s="78"/>
       <c r="D65" s="10"/>
-      <c r="E65" s="113" t="s">
+      <c r="E65" s="109" t="s">
         <v>348</v>
       </c>
       <c r="F65" s="24"/>
@@ -10838,29 +10883,28 @@
       <c r="J65" s="78"/>
       <c r="K65" s="78"/>
       <c r="L65" s="78"/>
-      <c r="M65" s="115">
+      <c r="M65" s="111">
         <f t="shared" si="8"/>
         <v>340</v>
       </c>
-      <c r="N65" s="105" t="s">
+      <c r="N65" s="101" t="s">
         <v>294</v>
       </c>
-      <c r="O65" s="77">
-        <v>0</v>
-      </c>
-      <c r="P65" s="77">
-        <f t="shared" si="1"/>
-        <v>340</v>
+      <c r="O65" s="77" t="s">
+        <v>353</v>
+      </c>
+      <c r="P65" s="77" t="s">
+        <v>353</v>
       </c>
       <c r="R65" s="1"/>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A66" s="122"/>
+      <c r="A66" s="121"/>
       <c r="B66" s="10"/>
       <c r="C66" s="78"/>
       <c r="D66" s="10"/>
-      <c r="E66" s="113" t="s">
-        <v>353</v>
+      <c r="E66" s="109" t="s">
+        <v>352</v>
       </c>
       <c r="F66" s="24"/>
       <c r="G66" s="23">
@@ -10873,11 +10917,11 @@
       <c r="J66" s="78"/>
       <c r="K66" s="78"/>
       <c r="L66" s="78"/>
-      <c r="M66" s="115">
+      <c r="M66" s="111">
         <f t="shared" si="8"/>
         <v>157</v>
       </c>
-      <c r="N66" s="105" t="s">
+      <c r="N66" s="101" t="s">
         <v>350</v>
       </c>
       <c r="O66" s="77">
@@ -10890,13 +10934,13 @@
       <c r="R66" s="1"/>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A67" s="84">
+      <c r="A67" s="121">
         <v>46133</v>
       </c>
       <c r="B67" s="18"/>
       <c r="C67" s="76"/>
       <c r="D67" s="18"/>
-      <c r="E67" s="113" t="s">
+      <c r="E67" s="109" t="s">
         <v>349</v>
       </c>
       <c r="F67" s="24"/>
@@ -10910,11 +10954,11 @@
       <c r="J67" s="78"/>
       <c r="K67" s="78"/>
       <c r="L67" s="78"/>
-      <c r="M67" s="115">
+      <c r="M67" s="111">
         <f t="shared" si="8"/>
         <v>145</v>
       </c>
-      <c r="N67" s="105" t="s">
+      <c r="N67" s="101" t="s">
         <v>342</v>
       </c>
       <c r="O67" s="77">
@@ -10927,188 +10971,208 @@
       <c r="R67" s="1"/>
     </row>
     <row r="68" spans="1:18" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A68" s="84"/>
+      <c r="A68" s="121"/>
       <c r="B68" s="18"/>
       <c r="C68" s="76"/>
       <c r="D68" s="18"/>
-      <c r="E68" s="143" t="s">
-        <v>352</v>
-      </c>
-      <c r="F68" s="142"/>
+      <c r="E68" s="118" t="s">
+        <v>351</v>
+      </c>
+      <c r="F68" s="117"/>
       <c r="G68" s="23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H68" s="47">
         <f t="shared" si="0"/>
-        <v>4994</v>
+        <v>3994</v>
       </c>
       <c r="J68" s="78"/>
       <c r="K68" s="78"/>
       <c r="L68" s="78"/>
-      <c r="M68" s="105">
-        <v>0</v>
+      <c r="M68" s="111">
+        <f t="shared" si="8"/>
+        <v>1000</v>
       </c>
       <c r="N68" s="78" t="s">
-        <v>351</v>
+        <v>370</v>
       </c>
       <c r="O68" s="77">
         <v>0</v>
       </c>
       <c r="P68" s="77">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="R68" s="1"/>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A69" s="83"/>
+      <c r="A69" s="121"/>
       <c r="B69" s="18"/>
       <c r="C69" s="76"/>
       <c r="D69" s="18"/>
-      <c r="E69" s="94" t="s">
-        <v>291</v>
+      <c r="E69" s="118" t="s">
+        <v>354</v>
       </c>
       <c r="F69" s="24"/>
       <c r="G69" s="23">
-        <v>156</v>
+        <v>800</v>
       </c>
       <c r="H69" s="47">
         <f t="shared" si="0"/>
-        <v>4838</v>
+        <v>3194</v>
       </c>
       <c r="J69" s="78"/>
       <c r="K69" s="78"/>
       <c r="L69" s="78"/>
-      <c r="M69" s="105">
-        <v>0</v>
-      </c>
-      <c r="N69" s="105"/>
+      <c r="M69" s="111">
+        <f t="shared" si="8"/>
+        <v>800</v>
+      </c>
+      <c r="N69" s="101" t="s">
+        <v>294</v>
+      </c>
       <c r="O69" s="77">
         <v>0</v>
       </c>
       <c r="P69" s="77">
         <f t="shared" ref="P69:P112" si="9">+M69-O69</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="R69" s="1"/>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A70" s="85"/>
+      <c r="A70" s="121"/>
       <c r="B70" s="18"/>
       <c r="C70" s="76"/>
       <c r="D70" s="18"/>
-      <c r="E70" s="92"/>
+      <c r="E70" s="118" t="s">
+        <v>355</v>
+      </c>
       <c r="F70" s="24"/>
       <c r="G70" s="23">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H70" s="47">
         <f t="shared" ref="H70:H112" si="10">H69+F70-G70</f>
-        <v>4838</v>
+        <v>3181</v>
       </c>
       <c r="J70" s="78"/>
       <c r="K70" s="78"/>
       <c r="L70" s="78"/>
-      <c r="M70" s="105">
-        <f t="shared" ref="M66:M72" si="11">E70</f>
-        <v>0</v>
-      </c>
-      <c r="N70" s="105"/>
+      <c r="M70" s="111">
+        <f t="shared" si="8"/>
+        <v>13</v>
+      </c>
+      <c r="N70" s="101" t="s">
+        <v>356</v>
+      </c>
       <c r="O70" s="77">
         <v>0</v>
       </c>
       <c r="P70" s="77">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="R70" s="1"/>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A71" s="84"/>
+      <c r="A71" s="121"/>
       <c r="B71" s="18"/>
       <c r="C71" s="76"/>
       <c r="D71" s="18"/>
-      <c r="E71" s="92"/>
+      <c r="E71" s="118" t="s">
+        <v>355</v>
+      </c>
       <c r="F71" s="24"/>
       <c r="G71" s="23">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H71" s="47">
         <f t="shared" si="10"/>
-        <v>4838</v>
+        <v>3061</v>
       </c>
       <c r="J71" s="78"/>
       <c r="K71" s="78"/>
       <c r="L71" s="78"/>
-      <c r="M71" s="105">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="N71" s="105"/>
+      <c r="M71" s="111">
+        <f t="shared" si="8"/>
+        <v>120</v>
+      </c>
+      <c r="N71" s="101" t="s">
+        <v>356</v>
+      </c>
       <c r="O71" s="77">
         <v>0</v>
       </c>
       <c r="P71" s="77">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="R71" s="1"/>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A72" s="83"/>
+      <c r="A72" s="121"/>
       <c r="B72" s="18"/>
       <c r="C72" s="76"/>
       <c r="D72" s="18"/>
-      <c r="E72" s="92"/>
+      <c r="E72" s="118" t="s">
+        <v>358</v>
+      </c>
       <c r="F72" s="24"/>
       <c r="G72" s="23">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="H72" s="47">
         <f t="shared" si="10"/>
-        <v>4838</v>
+        <v>2716</v>
       </c>
       <c r="J72" s="78"/>
       <c r="K72" s="78"/>
       <c r="L72" s="78"/>
-      <c r="M72" s="105">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="N72" s="105" t="s">
-        <v>342</v>
+      <c r="M72" s="111">
+        <f t="shared" si="8"/>
+        <v>345</v>
+      </c>
+      <c r="N72" s="101" t="s">
+        <v>357</v>
       </c>
       <c r="O72" s="77">
         <v>0</v>
       </c>
       <c r="P72" s="77">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="R72" s="1"/>
     </row>
     <row r="73" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="85"/>
+      <c r="A73" s="121">
+        <v>46134</v>
+      </c>
       <c r="B73" s="18"/>
       <c r="C73" s="76"/>
       <c r="D73" s="18"/>
-      <c r="E73" s="92"/>
+      <c r="E73" s="115" t="s">
+        <v>270</v>
+      </c>
       <c r="F73" s="24"/>
       <c r="G73" s="23">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="H73" s="47">
         <f t="shared" si="10"/>
-        <v>4838</v>
+        <v>2506</v>
       </c>
       <c r="J73" s="78"/>
       <c r="K73" s="78"/>
-      <c r="L73" s="78"/>
-      <c r="M73" s="105">
-        <f t="shared" ref="M73:M78" si="12">E73</f>
-        <v>0</v>
-      </c>
-      <c r="N73" s="105"/>
+      <c r="L73" s="94">
+        <f>G73</f>
+        <v>210</v>
+      </c>
+      <c r="M73" s="101">
+        <v>0</v>
+      </c>
+      <c r="N73" s="101"/>
       <c r="O73" s="77">
         <v>0</v>
       </c>
@@ -11119,120 +11183,150 @@
       <c r="R73" s="1"/>
     </row>
     <row r="74" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="85"/>
+      <c r="A74" s="122"/>
       <c r="B74" s="17"/>
       <c r="C74" s="76"/>
-      <c r="D74" s="17"/>
-      <c r="E74" s="92"/>
+      <c r="D74" s="86" t="s">
+        <v>283</v>
+      </c>
+      <c r="E74" s="118" t="s">
+        <v>368</v>
+      </c>
       <c r="F74" s="24"/>
       <c r="G74" s="23">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="H74" s="47">
         <f t="shared" si="10"/>
-        <v>4838</v>
+        <v>1206</v>
       </c>
       <c r="J74" s="78"/>
       <c r="K74" s="78"/>
       <c r="L74" s="78"/>
-      <c r="M74" s="105">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="N74" s="105"/>
+      <c r="M74" s="111">
+        <f t="shared" si="8"/>
+        <v>1300</v>
+      </c>
+      <c r="N74" s="101" t="s">
+        <v>369</v>
+      </c>
       <c r="O74" s="77">
         <v>0</v>
       </c>
       <c r="P74" s="77">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="R74" s="1"/>
     </row>
     <row r="75" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="85"/>
-      <c r="B75" s="18"/>
-      <c r="C75" s="76"/>
-      <c r="D75" s="18"/>
-      <c r="E75" s="93"/>
-      <c r="F75" s="24"/>
+      <c r="A75" s="120">
+        <v>46135</v>
+      </c>
+      <c r="B75" s="18" t="s">
+        <v>375</v>
+      </c>
+      <c r="C75" s="76" t="s">
+        <v>7</v>
+      </c>
+      <c r="D75" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="E75" s="118" t="s">
+        <v>366</v>
+      </c>
+      <c r="F75" s="24">
+        <v>500</v>
+      </c>
       <c r="G75" s="23">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="H75" s="47">
         <f t="shared" si="10"/>
-        <v>4838</v>
+        <v>1579</v>
       </c>
       <c r="J75" s="78"/>
       <c r="K75" s="78"/>
       <c r="L75" s="78"/>
-      <c r="M75" s="105">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="N75" s="105"/>
+      <c r="M75" s="111">
+        <f t="shared" si="8"/>
+        <v>127</v>
+      </c>
+      <c r="N75" s="101" t="s">
+        <v>367</v>
+      </c>
       <c r="O75" s="77">
         <v>0</v>
       </c>
       <c r="P75" s="77">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="R75" s="1"/>
     </row>
     <row r="76" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="85"/>
+      <c r="A76" s="121"/>
       <c r="B76" s="18"/>
       <c r="C76" s="76"/>
       <c r="D76" s="18"/>
-      <c r="E76" s="92"/>
+      <c r="E76" s="118" t="s">
+        <v>359</v>
+      </c>
       <c r="F76" s="24"/>
       <c r="G76" s="23">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="H76" s="47">
         <f t="shared" si="10"/>
-        <v>4838</v>
+        <v>1389</v>
       </c>
       <c r="J76" s="78"/>
       <c r="K76" s="78"/>
       <c r="L76" s="78"/>
-      <c r="M76" s="105">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="N76" s="105"/>
+      <c r="M76" s="111">
+        <f t="shared" si="8"/>
+        <v>190</v>
+      </c>
+      <c r="N76" s="101" t="s">
+        <v>360</v>
+      </c>
       <c r="O76" s="77">
         <v>0</v>
       </c>
       <c r="P76" s="77">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="R76" s="1"/>
     </row>
-    <row r="77" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="85"/>
+    <row r="77" spans="1:18" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="83">
+        <v>46136</v>
+      </c>
       <c r="B77" s="18"/>
-      <c r="C77" s="76"/>
+      <c r="C77" s="18"/>
       <c r="D77" s="18"/>
-      <c r="E77" s="92"/>
-      <c r="F77" s="24"/>
-      <c r="G77" s="23">
-        <v>0</v>
+      <c r="E77" s="115" t="s">
+        <v>361</v>
+      </c>
+      <c r="F77" s="75"/>
+      <c r="G77" s="54">
+        <v>82</v>
       </c>
       <c r="H77" s="47">
         <f t="shared" si="10"/>
-        <v>4838</v>
+        <v>1307</v>
       </c>
       <c r="J77" s="78"/>
       <c r="K77" s="78"/>
-      <c r="L77" s="78"/>
-      <c r="M77" s="105">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="N77" s="105"/>
+      <c r="L77" s="94">
+        <f>G77</f>
+        <v>82</v>
+      </c>
+      <c r="M77" s="101">
+        <v>0</v>
+      </c>
+      <c r="N77" s="101"/>
       <c r="O77" s="77">
         <v>0</v>
       </c>
@@ -11243,59 +11337,66 @@
       <c r="R77" s="1"/>
     </row>
     <row r="78" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="86"/>
+      <c r="A78" s="120">
+        <v>46136</v>
+      </c>
       <c r="B78" s="51"/>
       <c r="C78" s="79"/>
       <c r="D78" s="51"/>
-      <c r="E78" s="95"/>
+      <c r="E78" s="115" t="s">
+        <v>362</v>
+      </c>
       <c r="F78" s="75"/>
       <c r="G78" s="54">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="H78" s="55">
         <f t="shared" si="10"/>
-        <v>4838</v>
-      </c>
-      <c r="I78" s="124" t="s">
+        <v>657</v>
+      </c>
+      <c r="I78" s="119" t="s">
         <v>9</v>
       </c>
       <c r="J78" s="78"/>
       <c r="K78" s="78"/>
       <c r="L78" s="78"/>
-      <c r="M78" s="105">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="N78" s="105"/>
+      <c r="M78" s="111">
+        <f t="shared" si="8"/>
+        <v>650</v>
+      </c>
+      <c r="N78" s="101"/>
       <c r="O78" s="77">
         <v>0</v>
       </c>
       <c r="P78" s="77">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="R78" s="1"/>
     </row>
     <row r="79" spans="1:18" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="82"/>
+      <c r="A79" s="121"/>
       <c r="B79" s="59"/>
       <c r="C79" s="80"/>
       <c r="D79" s="59"/>
-      <c r="E79" s="96"/>
+      <c r="E79" s="118" t="s">
+        <v>363</v>
+      </c>
       <c r="F79" s="68"/>
       <c r="G79" s="61">
-        <v>0</v>
+        <v>451</v>
       </c>
       <c r="H79" s="60">
         <f t="shared" si="10"/>
-        <v>4838</v>
-      </c>
-      <c r="I79" s="134"/>
-      <c r="J79" s="96"/>
-      <c r="K79" s="96"/>
-      <c r="L79" s="96"/>
-      <c r="M79" s="77">
-        <v>0</v>
+        <v>206</v>
+      </c>
+      <c r="I79" s="129"/>
+      <c r="J79" s="92"/>
+      <c r="K79" s="92"/>
+      <c r="L79" s="92"/>
+      <c r="M79" s="111">
+        <f t="shared" si="8"/>
+        <v>451</v>
       </c>
       <c r="N79" s="7"/>
       <c r="O79" s="77">
@@ -11303,57 +11404,69 @@
       </c>
       <c r="P79" s="77">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>451</v>
       </c>
       <c r="R79" s="1"/>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A80" s="82"/>
+      <c r="A80" s="122"/>
       <c r="B80" s="18"/>
       <c r="C80" s="76"/>
       <c r="D80" s="18"/>
-      <c r="E80" s="92"/>
+      <c r="E80" s="118" t="s">
+        <v>364</v>
+      </c>
       <c r="F80" s="24"/>
       <c r="G80" s="23">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H80" s="24">
         <f t="shared" si="10"/>
-        <v>4838</v>
-      </c>
-      <c r="J80" s="92"/>
-      <c r="K80" s="92"/>
-      <c r="L80" s="92"/>
-      <c r="M80" s="77">
-        <v>0</v>
-      </c>
-      <c r="N80" s="11"/>
+        <v>-394</v>
+      </c>
+      <c r="J80" s="89"/>
+      <c r="K80" s="89"/>
+      <c r="L80" s="89"/>
+      <c r="M80" s="111">
+        <f t="shared" si="8"/>
+        <v>600</v>
+      </c>
+      <c r="N80" s="11" t="s">
+        <v>365</v>
+      </c>
       <c r="O80" s="77">
         <v>0</v>
       </c>
       <c r="P80" s="77">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="R80" s="1"/>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A81" s="83"/>
+      <c r="A81" s="83">
+        <v>46137</v>
+      </c>
       <c r="B81" s="18"/>
       <c r="C81" s="76"/>
       <c r="D81" s="18"/>
-      <c r="E81" s="92"/>
+      <c r="E81" s="115" t="s">
+        <v>361</v>
+      </c>
       <c r="F81" s="24"/>
       <c r="G81" s="23">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="H81" s="24">
         <f t="shared" si="10"/>
-        <v>4838</v>
-      </c>
-      <c r="J81" s="92"/>
-      <c r="K81" s="92"/>
-      <c r="L81" s="92"/>
+        <v>-522</v>
+      </c>
+      <c r="J81" s="89"/>
+      <c r="K81" s="89"/>
+      <c r="L81" s="94">
+        <f>G81</f>
+        <v>128</v>
+      </c>
       <c r="M81" s="77">
         <v>0</v>
       </c>
@@ -11368,22 +11481,29 @@
       <c r="R81" s="1"/>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A82" s="85"/>
+      <c r="A82" s="83">
+        <v>46139</v>
+      </c>
       <c r="B82" s="18"/>
       <c r="C82" s="76"/>
       <c r="D82" s="18"/>
-      <c r="E82" s="92"/>
+      <c r="E82" s="115" t="s">
+        <v>361</v>
+      </c>
       <c r="F82" s="24"/>
       <c r="G82" s="23">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="H82" s="24">
         <f t="shared" si="10"/>
-        <v>4838</v>
-      </c>
-      <c r="J82" s="92"/>
-      <c r="K82" s="92"/>
-      <c r="L82" s="92"/>
+        <v>-705</v>
+      </c>
+      <c r="J82" s="89"/>
+      <c r="K82" s="89"/>
+      <c r="L82" s="94">
+        <f>G82</f>
+        <v>183</v>
+      </c>
       <c r="M82" s="77">
         <v>0</v>
       </c>
@@ -11397,23 +11517,30 @@
       </c>
       <c r="R82" s="1"/>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A83" s="84"/>
+    <row r="83" spans="1:18" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A83" s="83" t="s">
+        <v>9</v>
+      </c>
       <c r="B83" s="18"/>
       <c r="C83" s="76"/>
       <c r="D83" s="18"/>
-      <c r="E83" s="92"/>
+      <c r="E83" s="106" t="s">
+        <v>371</v>
+      </c>
       <c r="F83" s="24"/>
       <c r="G83" s="23">
-        <v>0</v>
+        <v>656</v>
       </c>
       <c r="H83" s="24">
         <f t="shared" si="10"/>
-        <v>4838</v>
-      </c>
-      <c r="J83" s="92"/>
-      <c r="K83" s="92"/>
-      <c r="L83" s="92"/>
+        <v>-1361</v>
+      </c>
+      <c r="J83" s="89"/>
+      <c r="K83" s="96">
+        <f>G83</f>
+        <v>656</v>
+      </c>
+      <c r="L83" s="89"/>
       <c r="M83" s="77">
         <v>0</v>
       </c>
@@ -11424,6 +11551,9 @@
       <c r="P83" s="77">
         <f t="shared" si="9"/>
         <v>0</v>
+      </c>
+      <c r="Q83" s="93" t="s">
+        <v>373</v>
       </c>
       <c r="R83" s="1"/>
     </row>
@@ -11432,18 +11562,23 @@
       <c r="B84" s="18"/>
       <c r="C84" s="76"/>
       <c r="D84" s="18"/>
-      <c r="E84" s="92"/>
+      <c r="E84" s="115" t="s">
+        <v>372</v>
+      </c>
       <c r="F84" s="24"/>
       <c r="G84" s="23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H84" s="24">
         <f t="shared" si="10"/>
-        <v>4838</v>
-      </c>
-      <c r="J84" s="92"/>
-      <c r="K84" s="92"/>
-      <c r="L84" s="92"/>
+        <v>-2361</v>
+      </c>
+      <c r="J84" s="89"/>
+      <c r="K84" s="89"/>
+      <c r="L84" s="94">
+        <f>G84</f>
+        <v>1000</v>
+      </c>
       <c r="M84" s="77">
         <v>0</v>
       </c>
@@ -11462,18 +11597,23 @@
       <c r="B85" s="18"/>
       <c r="C85" s="76"/>
       <c r="D85" s="18"/>
-      <c r="E85" s="92"/>
+      <c r="E85" s="115" t="s">
+        <v>374</v>
+      </c>
       <c r="F85" s="24"/>
       <c r="G85" s="23">
-        <v>0</v>
+        <v>271</v>
       </c>
       <c r="H85" s="24">
         <f t="shared" si="10"/>
-        <v>4838</v>
-      </c>
-      <c r="J85" s="92"/>
-      <c r="K85" s="92"/>
-      <c r="L85" s="92"/>
+        <v>-2632</v>
+      </c>
+      <c r="J85" s="89"/>
+      <c r="K85" s="89"/>
+      <c r="L85" s="94">
+        <f>G85</f>
+        <v>271</v>
+      </c>
       <c r="M85" s="77">
         <v>0</v>
       </c>
@@ -11492,18 +11632,20 @@
       <c r="B86" s="18"/>
       <c r="C86" s="76"/>
       <c r="D86" s="18"/>
-      <c r="E86" s="92"/>
+      <c r="E86" s="91" t="s">
+        <v>291</v>
+      </c>
       <c r="F86" s="24"/>
       <c r="G86" s="23">
-        <v>0</v>
+        <v>656</v>
       </c>
       <c r="H86" s="24">
         <f t="shared" si="10"/>
-        <v>4838</v>
-      </c>
-      <c r="J86" s="92"/>
-      <c r="K86" s="92"/>
-      <c r="L86" s="92"/>
+        <v>-3288</v>
+      </c>
+      <c r="J86" s="89"/>
+      <c r="K86" s="89"/>
+      <c r="L86" s="89"/>
       <c r="M86" s="77">
         <v>0</v>
       </c>
@@ -11522,18 +11664,18 @@
       <c r="B87" s="18"/>
       <c r="C87" s="76"/>
       <c r="D87" s="18"/>
-      <c r="E87" s="92"/>
+      <c r="E87" s="89"/>
       <c r="F87" s="24"/>
       <c r="G87" s="23">
         <v>0</v>
       </c>
       <c r="H87" s="24">
         <f t="shared" si="10"/>
-        <v>4838</v>
-      </c>
-      <c r="J87" s="92"/>
-      <c r="K87" s="92"/>
-      <c r="L87" s="92"/>
+        <v>-3288</v>
+      </c>
+      <c r="J87" s="89"/>
+      <c r="K87" s="89"/>
+      <c r="L87" s="89"/>
       <c r="M87" s="77">
         <v>0</v>
       </c>
@@ -11552,18 +11694,18 @@
       <c r="B88" s="18"/>
       <c r="C88" s="76"/>
       <c r="D88" s="18"/>
-      <c r="E88" s="92"/>
+      <c r="E88" s="89"/>
       <c r="F88" s="24"/>
       <c r="G88" s="23">
         <v>0</v>
       </c>
       <c r="H88" s="24">
         <f t="shared" si="10"/>
-        <v>4838</v>
-      </c>
-      <c r="J88" s="92"/>
-      <c r="K88" s="92"/>
-      <c r="L88" s="92"/>
+        <v>-3288</v>
+      </c>
+      <c r="J88" s="89"/>
+      <c r="K88" s="89"/>
+      <c r="L88" s="89"/>
       <c r="M88" s="77">
         <v>0</v>
       </c>
@@ -11582,18 +11724,18 @@
       <c r="B89" s="18"/>
       <c r="C89" s="76"/>
       <c r="D89" s="18"/>
-      <c r="E89" s="92"/>
+      <c r="E89" s="89"/>
       <c r="F89" s="24"/>
       <c r="G89" s="23">
         <v>0</v>
       </c>
       <c r="H89" s="24">
         <f t="shared" si="10"/>
-        <v>4838</v>
-      </c>
-      <c r="J89" s="92"/>
-      <c r="K89" s="92"/>
-      <c r="L89" s="92"/>
+        <v>-3288</v>
+      </c>
+      <c r="J89" s="89"/>
+      <c r="K89" s="89"/>
+      <c r="L89" s="89"/>
       <c r="M89" s="77">
         <v>0</v>
       </c>
@@ -11612,18 +11754,18 @@
       <c r="B90" s="18"/>
       <c r="C90" s="76"/>
       <c r="D90" s="18"/>
-      <c r="E90" s="92"/>
+      <c r="E90" s="89"/>
       <c r="F90" s="24"/>
       <c r="G90" s="23">
         <v>0</v>
       </c>
       <c r="H90" s="24">
         <f t="shared" si="10"/>
-        <v>4838</v>
-      </c>
-      <c r="J90" s="92"/>
-      <c r="K90" s="92"/>
-      <c r="L90" s="92"/>
+        <v>-3288</v>
+      </c>
+      <c r="J90" s="89"/>
+      <c r="K90" s="89"/>
+      <c r="L90" s="89"/>
       <c r="M90" s="77">
         <v>0</v>
       </c>
@@ -11642,16 +11784,16 @@
       <c r="B91" s="18"/>
       <c r="C91" s="76"/>
       <c r="D91" s="18"/>
-      <c r="E91" s="92"/>
+      <c r="E91" s="89"/>
       <c r="F91" s="24"/>
       <c r="G91" s="23"/>
       <c r="H91" s="24">
         <f t="shared" si="10"/>
-        <v>4838</v>
-      </c>
-      <c r="J91" s="92"/>
-      <c r="K91" s="92"/>
-      <c r="L91" s="92"/>
+        <v>-3288</v>
+      </c>
+      <c r="J91" s="89"/>
+      <c r="K91" s="89"/>
+      <c r="L91" s="89"/>
       <c r="M91" s="77">
         <v>0</v>
       </c>
@@ -11670,16 +11812,16 @@
       <c r="B92" s="18"/>
       <c r="C92" s="76"/>
       <c r="D92" s="18"/>
-      <c r="E92" s="92"/>
+      <c r="E92" s="89"/>
       <c r="F92" s="24"/>
       <c r="G92" s="23"/>
       <c r="H92" s="24">
         <f t="shared" si="10"/>
-        <v>4838</v>
-      </c>
-      <c r="J92" s="92"/>
-      <c r="K92" s="92"/>
-      <c r="L92" s="92"/>
+        <v>-3288</v>
+      </c>
+      <c r="J92" s="89"/>
+      <c r="K92" s="89"/>
+      <c r="L92" s="89"/>
       <c r="M92" s="77">
         <v>0</v>
       </c>
@@ -11698,16 +11840,16 @@
       <c r="B93" s="18"/>
       <c r="C93" s="76"/>
       <c r="D93" s="18"/>
-      <c r="E93" s="92"/>
+      <c r="E93" s="89"/>
       <c r="F93" s="24"/>
       <c r="G93" s="23"/>
       <c r="H93" s="24">
         <f t="shared" si="10"/>
-        <v>4838</v>
-      </c>
-      <c r="J93" s="92"/>
-      <c r="K93" s="92"/>
-      <c r="L93" s="92"/>
+        <v>-3288</v>
+      </c>
+      <c r="J93" s="89"/>
+      <c r="K93" s="89"/>
+      <c r="L93" s="89"/>
       <c r="M93" s="77">
         <v>0</v>
       </c>
@@ -11726,16 +11868,16 @@
       <c r="B94" s="18"/>
       <c r="C94" s="76"/>
       <c r="D94" s="18"/>
-      <c r="E94" s="92"/>
+      <c r="E94" s="89"/>
       <c r="F94" s="24"/>
       <c r="G94" s="23"/>
       <c r="H94" s="24">
         <f t="shared" si="10"/>
-        <v>4838</v>
-      </c>
-      <c r="J94" s="92"/>
-      <c r="K94" s="92"/>
-      <c r="L94" s="92"/>
+        <v>-3288</v>
+      </c>
+      <c r="J94" s="89"/>
+      <c r="K94" s="89"/>
+      <c r="L94" s="89"/>
       <c r="M94" s="77">
         <v>0</v>
       </c>
@@ -11754,16 +11896,16 @@
       <c r="B95" s="18"/>
       <c r="C95" s="76"/>
       <c r="D95" s="18"/>
-      <c r="E95" s="92"/>
+      <c r="E95" s="89"/>
       <c r="F95" s="24"/>
       <c r="G95" s="23"/>
       <c r="H95" s="24">
         <f t="shared" si="10"/>
-        <v>4838</v>
-      </c>
-      <c r="J95" s="92"/>
-      <c r="K95" s="92"/>
-      <c r="L95" s="92"/>
+        <v>-3288</v>
+      </c>
+      <c r="J95" s="89"/>
+      <c r="K95" s="89"/>
+      <c r="L95" s="89"/>
       <c r="M95" s="77">
         <v>0</v>
       </c>
@@ -11782,16 +11924,16 @@
       <c r="B96" s="18"/>
       <c r="C96" s="76"/>
       <c r="D96" s="18"/>
-      <c r="E96" s="92"/>
+      <c r="E96" s="89"/>
       <c r="F96" s="24"/>
       <c r="G96" s="23"/>
       <c r="H96" s="24">
         <f t="shared" si="10"/>
-        <v>4838</v>
-      </c>
-      <c r="J96" s="92"/>
-      <c r="K96" s="92"/>
-      <c r="L96" s="92"/>
+        <v>-3288</v>
+      </c>
+      <c r="J96" s="89"/>
+      <c r="K96" s="89"/>
+      <c r="L96" s="89"/>
       <c r="M96" s="77">
         <v>0</v>
       </c>
@@ -11810,16 +11952,16 @@
       <c r="B97" s="18"/>
       <c r="C97" s="76"/>
       <c r="D97" s="18"/>
-      <c r="E97" s="92"/>
+      <c r="E97" s="89"/>
       <c r="F97" s="24"/>
       <c r="G97" s="23"/>
       <c r="H97" s="24">
         <f t="shared" si="10"/>
-        <v>4838</v>
-      </c>
-      <c r="J97" s="92"/>
-      <c r="K97" s="92"/>
-      <c r="L97" s="92"/>
+        <v>-3288</v>
+      </c>
+      <c r="J97" s="89"/>
+      <c r="K97" s="89"/>
+      <c r="L97" s="89"/>
       <c r="M97" s="77">
         <v>0</v>
       </c>
@@ -11838,16 +11980,16 @@
       <c r="B98" s="18"/>
       <c r="C98" s="76"/>
       <c r="D98" s="18"/>
-      <c r="E98" s="92"/>
+      <c r="E98" s="89"/>
       <c r="F98" s="24"/>
       <c r="G98" s="23"/>
       <c r="H98" s="24">
         <f t="shared" si="10"/>
-        <v>4838</v>
-      </c>
-      <c r="J98" s="92"/>
-      <c r="K98" s="92"/>
-      <c r="L98" s="92"/>
+        <v>-3288</v>
+      </c>
+      <c r="J98" s="89"/>
+      <c r="K98" s="89"/>
+      <c r="L98" s="89"/>
       <c r="M98" s="77">
         <v>0</v>
       </c>
@@ -11866,16 +12008,16 @@
       <c r="B99" s="18"/>
       <c r="C99" s="76"/>
       <c r="D99" s="18"/>
-      <c r="E99" s="92"/>
+      <c r="E99" s="89"/>
       <c r="F99" s="24"/>
       <c r="G99" s="23"/>
       <c r="H99" s="24">
         <f t="shared" si="10"/>
-        <v>4838</v>
-      </c>
-      <c r="J99" s="92"/>
-      <c r="K99" s="92"/>
-      <c r="L99" s="92"/>
+        <v>-3288</v>
+      </c>
+      <c r="J99" s="89"/>
+      <c r="K99" s="89"/>
+      <c r="L99" s="89"/>
       <c r="M99" s="77">
         <v>0</v>
       </c>
@@ -11894,16 +12036,16 @@
       <c r="B100" s="18"/>
       <c r="C100" s="76"/>
       <c r="D100" s="18"/>
-      <c r="E100" s="92"/>
+      <c r="E100" s="89"/>
       <c r="F100" s="24"/>
       <c r="G100" s="23"/>
       <c r="H100" s="24">
         <f t="shared" si="10"/>
-        <v>4838</v>
-      </c>
-      <c r="J100" s="92"/>
-      <c r="K100" s="92"/>
-      <c r="L100" s="92"/>
+        <v>-3288</v>
+      </c>
+      <c r="J100" s="89"/>
+      <c r="K100" s="89"/>
+      <c r="L100" s="89"/>
       <c r="M100" s="77">
         <v>0</v>
       </c>
@@ -11922,16 +12064,16 @@
       <c r="B101" s="18"/>
       <c r="C101" s="76"/>
       <c r="D101" s="18"/>
-      <c r="E101" s="92"/>
+      <c r="E101" s="89"/>
       <c r="F101" s="24"/>
       <c r="G101" s="23"/>
       <c r="H101" s="24">
         <f t="shared" si="10"/>
-        <v>4838</v>
-      </c>
-      <c r="J101" s="92"/>
-      <c r="K101" s="92"/>
-      <c r="L101" s="92"/>
+        <v>-3288</v>
+      </c>
+      <c r="J101" s="89"/>
+      <c r="K101" s="89"/>
+      <c r="L101" s="89"/>
       <c r="M101" s="77">
         <v>0</v>
       </c>
@@ -11950,16 +12092,16 @@
       <c r="B102" s="18"/>
       <c r="C102" s="76"/>
       <c r="D102" s="18"/>
-      <c r="E102" s="92"/>
+      <c r="E102" s="89"/>
       <c r="F102" s="24"/>
       <c r="G102" s="23"/>
       <c r="H102" s="24">
         <f t="shared" si="10"/>
-        <v>4838</v>
-      </c>
-      <c r="J102" s="92"/>
-      <c r="K102" s="92"/>
-      <c r="L102" s="92"/>
+        <v>-3288</v>
+      </c>
+      <c r="J102" s="89"/>
+      <c r="K102" s="89"/>
+      <c r="L102" s="89"/>
       <c r="M102" s="77">
         <v>0</v>
       </c>
@@ -11978,16 +12120,16 @@
       <c r="B103" s="18"/>
       <c r="C103" s="76"/>
       <c r="D103" s="18"/>
-      <c r="E103" s="92"/>
+      <c r="E103" s="89"/>
       <c r="F103" s="24"/>
       <c r="G103" s="23"/>
       <c r="H103" s="24">
         <f t="shared" si="10"/>
-        <v>4838</v>
-      </c>
-      <c r="J103" s="92"/>
-      <c r="K103" s="92"/>
-      <c r="L103" s="92"/>
+        <v>-3288</v>
+      </c>
+      <c r="J103" s="89"/>
+      <c r="K103" s="89"/>
+      <c r="L103" s="89"/>
       <c r="M103" s="77">
         <v>0</v>
       </c>
@@ -12006,16 +12148,16 @@
       <c r="B104" s="18"/>
       <c r="C104" s="76"/>
       <c r="D104" s="18"/>
-      <c r="E104" s="92"/>
+      <c r="E104" s="89"/>
       <c r="F104" s="24"/>
       <c r="G104" s="23"/>
       <c r="H104" s="24">
         <f t="shared" si="10"/>
-        <v>4838</v>
-      </c>
-      <c r="J104" s="92"/>
-      <c r="K104" s="92"/>
-      <c r="L104" s="92"/>
+        <v>-3288</v>
+      </c>
+      <c r="J104" s="89"/>
+      <c r="K104" s="89"/>
+      <c r="L104" s="89"/>
       <c r="M104" s="77">
         <v>0</v>
       </c>
@@ -12034,16 +12176,16 @@
       <c r="B105" s="18"/>
       <c r="C105" s="76"/>
       <c r="D105" s="18"/>
-      <c r="E105" s="92"/>
+      <c r="E105" s="89"/>
       <c r="F105" s="24"/>
       <c r="G105" s="23"/>
       <c r="H105" s="24">
         <f t="shared" si="10"/>
-        <v>4838</v>
-      </c>
-      <c r="J105" s="92"/>
-      <c r="K105" s="92"/>
-      <c r="L105" s="92"/>
+        <v>-3288</v>
+      </c>
+      <c r="J105" s="89"/>
+      <c r="K105" s="89"/>
+      <c r="L105" s="89"/>
       <c r="M105" s="77">
         <v>0</v>
       </c>
@@ -12062,16 +12204,16 @@
       <c r="B106" s="18"/>
       <c r="C106" s="76"/>
       <c r="D106" s="18"/>
-      <c r="E106" s="92"/>
+      <c r="E106" s="89"/>
       <c r="F106" s="24"/>
       <c r="G106" s="23"/>
       <c r="H106" s="24">
         <f t="shared" si="10"/>
-        <v>4838</v>
-      </c>
-      <c r="J106" s="92"/>
-      <c r="K106" s="92"/>
-      <c r="L106" s="92"/>
+        <v>-3288</v>
+      </c>
+      <c r="J106" s="89"/>
+      <c r="K106" s="89"/>
+      <c r="L106" s="89"/>
       <c r="M106" s="77">
         <v>0</v>
       </c>
@@ -12090,16 +12232,16 @@
       <c r="B107" s="18"/>
       <c r="C107" s="76"/>
       <c r="D107" s="18"/>
-      <c r="E107" s="92"/>
+      <c r="E107" s="89"/>
       <c r="F107" s="24"/>
       <c r="G107" s="23"/>
       <c r="H107" s="24">
         <f t="shared" si="10"/>
-        <v>4838</v>
-      </c>
-      <c r="J107" s="92"/>
-      <c r="K107" s="92"/>
-      <c r="L107" s="92"/>
+        <v>-3288</v>
+      </c>
+      <c r="J107" s="89"/>
+      <c r="K107" s="89"/>
+      <c r="L107" s="89"/>
       <c r="M107" s="77">
         <v>0</v>
       </c>
@@ -12118,16 +12260,16 @@
       <c r="B108" s="18"/>
       <c r="C108" s="76"/>
       <c r="D108" s="18"/>
-      <c r="E108" s="92"/>
+      <c r="E108" s="89"/>
       <c r="F108" s="24"/>
       <c r="G108" s="23"/>
       <c r="H108" s="24">
         <f t="shared" si="10"/>
-        <v>4838</v>
-      </c>
-      <c r="J108" s="92"/>
-      <c r="K108" s="92"/>
-      <c r="L108" s="92"/>
+        <v>-3288</v>
+      </c>
+      <c r="J108" s="89"/>
+      <c r="K108" s="89"/>
+      <c r="L108" s="89"/>
       <c r="M108" s="77">
         <v>0</v>
       </c>
@@ -12146,16 +12288,16 @@
       <c r="B109" s="18"/>
       <c r="C109" s="76"/>
       <c r="D109" s="18"/>
-      <c r="E109" s="92"/>
+      <c r="E109" s="89"/>
       <c r="F109" s="24"/>
       <c r="G109" s="23"/>
       <c r="H109" s="24">
         <f t="shared" si="10"/>
-        <v>4838</v>
-      </c>
-      <c r="J109" s="92"/>
-      <c r="K109" s="92"/>
-      <c r="L109" s="92"/>
+        <v>-3288</v>
+      </c>
+      <c r="J109" s="89"/>
+      <c r="K109" s="89"/>
+      <c r="L109" s="89"/>
       <c r="M109" s="77">
         <v>0</v>
       </c>
@@ -12174,16 +12316,16 @@
       <c r="B110" s="18"/>
       <c r="C110" s="76"/>
       <c r="D110" s="18"/>
-      <c r="E110" s="92"/>
+      <c r="E110" s="89"/>
       <c r="F110" s="24"/>
       <c r="G110" s="23"/>
       <c r="H110" s="24">
         <f t="shared" si="10"/>
-        <v>4838</v>
-      </c>
-      <c r="J110" s="92"/>
-      <c r="K110" s="92"/>
-      <c r="L110" s="92"/>
+        <v>-3288</v>
+      </c>
+      <c r="J110" s="89"/>
+      <c r="K110" s="89"/>
+      <c r="L110" s="89"/>
       <c r="M110" s="77">
         <v>0</v>
       </c>
@@ -12202,16 +12344,16 @@
       <c r="B111" s="18"/>
       <c r="C111" s="76"/>
       <c r="D111" s="18"/>
-      <c r="E111" s="92"/>
+      <c r="E111" s="89"/>
       <c r="F111" s="24"/>
       <c r="G111" s="23"/>
       <c r="H111" s="24">
         <f t="shared" si="10"/>
-        <v>4838</v>
-      </c>
-      <c r="J111" s="92"/>
-      <c r="K111" s="92"/>
-      <c r="L111" s="92"/>
+        <v>-3288</v>
+      </c>
+      <c r="J111" s="89"/>
+      <c r="K111" s="89"/>
+      <c r="L111" s="89"/>
       <c r="M111" s="77">
         <v>0</v>
       </c>
@@ -12230,16 +12372,16 @@
       <c r="B112" s="18"/>
       <c r="C112" s="76"/>
       <c r="D112" s="18"/>
-      <c r="E112" s="92"/>
+      <c r="E112" s="89"/>
       <c r="F112" s="24"/>
       <c r="G112" s="23"/>
       <c r="H112" s="24">
         <f t="shared" si="10"/>
-        <v>4838</v>
-      </c>
-      <c r="J112" s="92"/>
-      <c r="K112" s="92"/>
-      <c r="L112" s="92"/>
+        <v>-3288</v>
+      </c>
+      <c r="J112" s="89"/>
+      <c r="K112" s="89"/>
+      <c r="L112" s="89"/>
       <c r="M112" s="77">
         <v>0</v>
       </c>
@@ -12257,7 +12399,16 @@
       <c r="R113" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <autoFilter ref="N1:N113" xr:uid="{78EB2AAE-1BD7-400D-A761-4D5DA9FAB287}"/>
+  <mergeCells count="24">
+    <mergeCell ref="A73:A74"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="A78:A80"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A67:A72"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="J1:Q1"/>
     <mergeCell ref="I78:I79"/>
@@ -12274,16 +12425,15 @@
     <mergeCell ref="A55:A58"/>
     <mergeCell ref="A60:A66"/>
     <mergeCell ref="E2:E3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A2:A3"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="35" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="34" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <colBreaks count="1" manualBreakCount="1">
-    <brk id="8" max="77" man="1"/>
+    <brk id="8" max="88" man="1"/>
   </colBreaks>
+  <ignoredErrors>
+    <ignoredError sqref="P11 P15 P20 P33 P43 P27" formula="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>